--- a/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
+++ b/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="696">
   <si>
     <t xml:space="preserve">Nibbl AI — Master Requirements Tracker</t>
   </si>
@@ -179,72 +179,75 @@
     <t xml:space="preserve">Date range — default Last 30 Days, selectable</t>
   </si>
   <si>
-    <t xml:space="preserve">Snapshots and table use the last 30 days.</t>
+    <t xml:space="preserve">Date range selector (7 / 30 / 90 days / 12 months) drives both snapshots and the Campaign Performance table.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Dashboard + Backend / API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dashboard → Date range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch the range; snapshot titles and table results update.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebate snapshot: claims, redemptions, redemption rate, Total Brand Cost + cost per redemption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As specified, no mini charts/badges.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare with Redemptions for 30 days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1, #28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review snapshot: invitations, completed, completion rate, Total Brand Cost + cost per review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As specified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare with Review Management.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign Performance table (incl. ended; type filter; spend; results)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebate + review campaigns; results = claims / redemptions or invitations / completed reviews for the selected range.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dashboard → Campaign Performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter by type; check review results.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page controls: product count + Add Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count and Add Product button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Product Library.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product cards: image, name/flavor/size, rating, category, Product ID, receipt alias count, Edit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cards with image, details, rating, Edit.</t>
   </si>
   <si>
     <t xml:space="preserve">In Progress</t>
   </si>
   <si>
-    <t xml:space="preserve">Check the snapshot period.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date-range selector (other ranges) not built; fixed to 30 days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebate snapshot: claims, redemptions, redemption rate, Total Brand Cost + cost per redemption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As specified, no mini charts/badges.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare with Redemptions for 30 days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#1, #28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review snapshot: invitations, completed, completion rate, Total Brand Cost + cost per review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As specified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare with Review Management.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign Performance table (incl. ended; type filter; spend; results)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebate + review campaigns with results and type filter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dashboard → Campaign Performance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter by type; ended campaigns listed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page controls: product count + Add Product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count and Add Product button.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Product Library.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product cards: image, name/flavor/size, rating, category, Product ID, receipt alias count, Edit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cards with image, details, rating, Edit.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Compare a card with the Master mockup.</t>
   </si>
   <si>
@@ -257,9 +260,6 @@
     <t xml:space="preserve">Flavor, format, size fields; ID assigned on save.</t>
   </si>
   <si>
-    <t xml:space="preserve">Brand Dashboard + Backend / API</t>
-  </si>
-  <si>
     <t xml:space="preserve">Add / Edit Product</t>
   </si>
   <si>
@@ -383,7 +383,10 @@
     <t xml:space="preserve">'X of Y active campaigns used — Upgrade' banner</t>
   </si>
   <si>
-    <t xml:space="preserve">Usage banner with upgrade link not built (the limit itself is enforced on activation).</t>
+    <t xml:space="preserve">Usage bar with plan name and Upgrade button to Plans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activate campaigns up to the limit; click Upgrade.</t>
   </si>
   <si>
     <t xml:space="preserve">#34</t>
@@ -953,13 +956,10 @@
     <t xml:space="preserve">③ Search &amp; filters (campaign, product, status, submitted date)</t>
   </si>
   <si>
-    <t xml:space="preserve">Search and status tabs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search by customer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign / product / date filters not built.</t>
+    <t xml:space="preserve">Search, campaign, product (via campaign products), status tabs, date range.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter by campaign and product.</t>
   </si>
   <si>
     <t xml:space="preserve">⑥ Pagination &amp; Export CSV</t>
@@ -986,472 +986,469 @@
     <t xml:space="preserve">KPIs: total, pending 1–3★ response, average rating, review spend, cost per review</t>
   </si>
   <si>
-    <t xml:space="preserve">Total, awaiting response, average rating.</t>
+    <t xml:space="preserve">All five KPIs; spend from the wallet ledger.</t>
   </si>
   <si>
     <t xml:space="preserve">Reviews → Review Management</t>
   </si>
   <si>
+    <t xml:space="preserve">Compare spend with the Wallet ledger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabs (All, Published, 7-Day Hold, Flagged, Removed) + date range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabs with counts + date range + keyword search.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filters: rating, retailer, product, region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All four (retailer from the receipt, region from the shopper's state).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter by retailer and region.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review details: answers, final text, receipt evidence + gating summary, customer contact for service recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side panel with answers, receipt, gating summary, masked email + copy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Management → review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#26, #33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low-rating response: countdown, Contact Customer, Add Brand Response, Flag for Removal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live countdown, Contact Customer (email), response, flag.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a 2★ held review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flag reasons per Master (wrong product, unrelated, spam/fraud, PII, profanity, prohibited claim, other) + audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master's 7 reasons, 500-char details, audit log.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Management → Flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flag a review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Export: Download CSV + Download Reviews; API integration Coming Soon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSV + readable reviews file, both with disclosure; API Coming Soon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Management → Export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Download both.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create Review Campaign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basics (required image), eligible products, controls, locked rules &amp; cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviews → Create</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a review campaign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand question pool: add, suggest, Test Review Chat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add + suggest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review campaign page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add and suggest questions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Test Review Chat' not built.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save Draft / Submit for Nibbl Review (published after review)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brands activate review campaigns directly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nibbl approval for review campaigns not built.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live shopper preview (mobile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not built.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper Review Opportunity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Offers: Review Rewards card (Claim $1, Save for Later)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review cards in the carousel and My Rewards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get a receipt verified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Confirmed · Multiple Matches · Missing Consent · Share Your Voice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These screens aren't built on the website (chat opens directly).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer rules: scan all lines, 0/1/many opportunities, cooldown per shopper+product, $1 reserve, no second verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Chat Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product context loaded; rotating brand question; generated title &amp; review; edit; regenerate; final approval; $1 at any rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → review chat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete a review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five adaptive product questions with suggested answer chips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed AI questions today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adaptive questions wait on the AI service endpoint; suggested-answer chips not built.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separate 'recommend' and 'purchase again' questions; title 100 / body 500 limits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One combined recommend question.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Split recommend vs repurchase; enforce 100/500 character limits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratings &amp; Reviews Display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratings per product in campaign details; all reviews with sorting; review details + brand response; helpful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → offer → reviews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort and mark helpful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviews overview: rating, breakdown, % recommend, % would buy again, AI summary (positives + improvement)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rating, breakdown, % recommend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open an offer with reviews.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'% would buy again' not built; AI summary waits on the AI service.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost &amp; Results · Customer &amp; Conversion · Campaign Performance (25-hour cycles)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare cost with the ledger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary, search &amp; filters, download opted-in, integrations Coming Soon, consent withdrawal rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter and download.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table: brand activity, site activity, open claims, cooldowns, last active, status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer table.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Customers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site-activity and cooldown columns to match the mockup.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header (opt-in badges, status) + Ban Customer with reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suspend from brand exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers → profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suspend a customer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profile header/ban dialog per mockup.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relationship with brand · Nibbl activity totals · Recent activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Older profile layout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a profile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebuild to the Master layout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open claims · Cooldowns with Remove (confirmation + audit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redemption history: full receipt 30 days, then matching line only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt retention / cleanup rule not built.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Wallet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balances: Available, Reserved, Promotional (definitions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check balances.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign Funding: 7-day need vs Available, funded status, reservations split</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet → Campaign Funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activate a campaign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatic refill (Stripe): trigger 25%, fixed amount, recommendation, failure alert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet → Auto-refill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable auto-refill.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production still on Stripe test keys — switch to the live keys received from the client, then retest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending Overview + Weekly Statements + detailed ledger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Download a statement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request Refund (Available Cash refundable; reserved/promo not)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Owner requests up to Available Cash; Nibbl reviews in Admin → Refunds, refunds in Stripe, marks refunded (ledger refund entry) or rejects with a note.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Dashboard + Admin Dashboard + Backend / API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet → Request Refund; Admin → Refunds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request, then mark refunded in Admin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money is returned manually in Stripe, then recorded here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current plan, recommendation, plan options, scheduled changes, downgrade campaign choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedule and cancel a change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#33, #35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feature comparison table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side-by-side table (capacity, fees, review cost, identity, CSV, integrations, account manager, early access).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plans → Feature Comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Plans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan entitlement enforcement (campaign limits, customer identity, CSV, review cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limits, fees, CSV and identity enforced; Starter reviews show first name + last initial and email only on 1–3★.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered by tests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#33, #34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Profile (name, website, support email, time zone)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings → Brand Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change time zone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team &amp; Permissions (Owner / Admin / Viewer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings → Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invite a Viewer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notifications per member (Email + SMS): wallet below 25%, auto-refill failed, campaign paused, exhausted early, new negative review, weekly summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-member toggles for campaign approvals, receipts to review, low-rating reviews, refill failed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings → Notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toggle and trigger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align the list with the Master (add wallet below 25%, campaign paused, exhausted early, weekly summary). SMS sending waits on Klaviyo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking &amp; Attribution (Meta Pixel; Google/TikTok Coming Soon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings → Tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save a Pixel ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security: passwordless sign-in, active sessions, last sign-in, sign out others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sessions + sign out others + last sign-in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings → Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign out another device.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passwordless (magic-link) sign-in not built — brands use a password.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account &amp; Support (Contact Nibbl Support, Owner-only closure, Klaviyo Coming Soon — Scale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log in as Owner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tag Generator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Static Coming Soon page (example artwork)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Open the page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Spend and Cost per Review tiles not on this page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabs (All, Published, 7-Day Hold, Flagged, Removed) + date range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filters: rating, retailer, product, region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rating, product, dates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter by rating.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retailer and region filters not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review details: answers, final text, receipt evidence + gating summary, customer contact for service recovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Answers, text, receipt, email.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Management → review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gating summary not shown; Starter plans must see the email only for negative-review service recovery (masked).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#26, #33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low-rating response: countdown, Contact Customer, Add Brand Response, Flag for Removal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public response + flag; held 7 days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Respond to a 2★ review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Countdown and 'Contact Customer' button not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flag reasons per Master (wrong product, unrelated, spam/fraud, PII, profanity, prohibited claim, other) + audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flag with reason; admin decides.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Management → Flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flag a review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reason list differs from the Master — align.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Export: Download CSV + Download Reviews; API integration Coming Soon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSV export with disclosure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Management → Export</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Export CSV.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Download Reviews' format and API Coming Soon card not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create Review Campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basics (required image), eligible products, controls, locked rules &amp; cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviews → Create</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a review campaign.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand question pool: add, suggest, Test Review Chat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add + suggest.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review campaign page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add and suggest questions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Test Review Chat' not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save Draft / Submit for Nibbl Review (published after review)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brands activate review campaigns directly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nibbl approval for review campaigns not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live shopper preview (mobile)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper Review Opportunity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Offers: Review Rewards card (Claim $1, Save for Later)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review cards in the carousel and My Rewards.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Get a receipt verified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Confirmed · Multiple Matches · Missing Consent · Share Your Voice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">These screens aren't built on the website (chat opens directly).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer rules: scan all lines, 0/1/many opportunities, cooldown per shopper+product, $1 reserve, no second verification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Chat Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product context loaded; rotating brand question; generated title &amp; review; edit; regenerate; final approval; $1 at any rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → review chat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete a review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Five adaptive product questions with suggested answer chips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed AI questions today.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adaptive questions wait on the AI service endpoint; suggested-answer chips not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Separate 'recommend' and 'purchase again' questions; title 100 / body 500 limits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One combined recommend question.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Split recommend vs repurchase; enforce 100/500 character limits.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratings &amp; Reviews Display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratings per product in campaign details; all reviews with sorting; review details + brand response; helpful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → offer → reviews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sort and mark helpful.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviews overview: rating, breakdown, % recommend, % would buy again, AI summary (positives + improvement)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rating, breakdown, % recommend.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open an offer with reviews.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'% would buy again' not built; AI summary waits on the AI service.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost &amp; Results · Customer &amp; Conversion · Campaign Performance (25-hour cycles)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare cost with the ledger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary, search &amp; filters, download opted-in, integrations Coming Soon, consent withdrawal rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter and download.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table: brand activity, site activity, open claims, cooldowns, last active, status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer table.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Customers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site-activity and cooldown columns to match the mockup.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header (opt-in badges, status) + Ban Customer with reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suspend from brand exists.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customers → profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suspend a customer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profile header/ban dialog per mockup.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relationship with brand · Nibbl activity totals · Recent activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Older profile layout.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a profile.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebuild to the Master layout.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open claims · Cooldowns with Remove (confirmation + audit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redemption history: full receipt 30 days, then matching line only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipt retention / cleanup rule not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Wallet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balances: Available, Reserved, Promotional (definitions)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check balances.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign Funding: 7-day need vs Available, funded status, reservations split</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet → Campaign Funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activate a campaign.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatic refill (Stripe): trigger 25%, fixed amount, recommendation, failure alert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet → Auto-refill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable auto-refill.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production still on Stripe test keys — switch to the live keys received from the client, then retest.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending Overview + Weekly Statements + detailed ledger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Download a statement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request Refund (Available Cash refundable; reserved/promo not)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refund request flow not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current plan, recommendation, plan options, scheduled changes, downgrade campaign choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schedule and cancel a change.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#33, #35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feature comparison table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan cards list features.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Plans.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Side-by-side comparison table not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan entitlement enforcement (campaign limits, customer identity, CSV, review cost)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limits, data access and fees enforced.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered by tests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starter: customer email should appear only for negative-review service recovery (Review Management shows it on all plans).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#33, #34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Profile (name, website, support email, time zone)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings → Brand Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change time zone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team &amp; Permissions (Owner / Admin / Viewer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings → Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invite a Viewer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications per member (Email + SMS): wallet below 25%, auto-refill failed, campaign paused, exhausted early, new negative review, weekly summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-member toggles for campaign approvals, receipts to review, low-rating reviews, refill failed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings → Notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toggle and trigger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align the list with the Master (add wallet below 25%, campaign paused, exhausted early, weekly summary). SMS sending waits on Klaviyo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking &amp; Attribution (Meta Pixel; Google/TikTok Coming Soon)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings → Tracking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save a Pixel ID.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security: passwordless sign-in, active sessions, last sign-in, sign out others</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sessions + sign out others + last sign-in.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings → Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sign out another device.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passwordless (magic-link) sign-in not built — brands use a password.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account &amp; Support (Contact Nibbl Support, Owner-only closure, Klaviyo Coming Soon — Scale)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log in as Owner.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tag Generator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Static Coming Soon page (example artwork)</t>
   </si>
   <si>
     <t xml:space="preserve">#37</t>
@@ -2976,11 +2973,11 @@
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Completed")</f>
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Progress")</f>
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Review")</f>
@@ -2988,11 +2985,11 @@
       </c>
       <c r="G5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Planned")</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H5" s="5" t="n">
         <f aca="false">IF(C5&gt;0,D5/C5,0)</f>
-        <v>0.533333333333333</v>
+        <v>0.613333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3190,7 +3187,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="9" t="n">
         <v>5</v>
       </c>
@@ -3204,23 +3201,21 @@
         <v>50</v>
       </c>
       <c r="F13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>30</v>
-      </c>
       <c r="H13" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="K13" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="K13" s="10"/>
       <c r="L13" s="12"/>
       <c r="M13" s="13" t="s">
         <v>34</v>
@@ -3294,7 +3289,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="9" t="n">
         <v>8</v>
       </c>
@@ -3311,7 +3306,7 @@
         <v>29</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>31</v>
@@ -3376,7 +3371,7 @@
         <v>71</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>30</v>
@@ -3388,10 +3383,10 @@
         <v>65</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="13" t="s">
@@ -3406,16 +3401,16 @@
         <v>65</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F19" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>31</v>
@@ -3451,7 +3446,7 @@
         <v>29</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>31</v>
@@ -3552,10 +3547,10 @@
         <v>93</v>
       </c>
       <c r="F23" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="H23" s="10" t="s">
         <v>31</v>
@@ -3721,10 +3716,10 @@
         <v>117</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>30</v>
@@ -3733,17 +3728,15 @@
         <v>31</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>118</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="K28" s="10"/>
       <c r="L28" s="12"/>
       <c r="M28" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3754,10 +3747,10 @@
         <v>111</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>29</v>
@@ -3772,12 +3765,12 @@
         <v>114</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K29" s="10"/>
       <c r="L29" s="12"/>
       <c r="M29" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3785,10 +3778,10 @@
         <v>22</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>59</v>
@@ -3803,15 +3796,15 @@
         <v>31</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K30" s="10"/>
       <c r="L30" s="12"/>
       <c r="M30" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3819,13 +3812,13 @@
         <v>23</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>29</v>
@@ -3837,15 +3830,15 @@
         <v>31</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K31" s="10"/>
       <c r="L31" s="12"/>
       <c r="M31" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3853,33 +3846,33 @@
         <v>24</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K32" s="10"/>
       <c r="L32" s="12"/>
       <c r="M32" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3887,13 +3880,13 @@
         <v>25</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>29</v>
@@ -3905,15 +3898,15 @@
         <v>31</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K33" s="10"/>
       <c r="L33" s="12"/>
       <c r="M33" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3921,13 +3914,13 @@
         <v>26</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>29</v>
@@ -3939,15 +3932,15 @@
         <v>31</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K34" s="10"/>
       <c r="L34" s="12"/>
       <c r="M34" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3955,33 +3948,33 @@
         <v>27</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K35" s="10"/>
       <c r="L35" s="12"/>
       <c r="M35" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3989,33 +3982,33 @@
         <v>28</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K36" s="10"/>
       <c r="L36" s="12"/>
       <c r="M36" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4023,33 +4016,33 @@
         <v>29</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K37" s="10"/>
       <c r="L37" s="12"/>
       <c r="M37" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4057,33 +4050,33 @@
         <v>30</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K38" s="10"/>
       <c r="L38" s="12"/>
       <c r="M38" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4091,35 +4084,35 @@
         <v>31</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L39" s="12"/>
       <c r="M39" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4127,13 +4120,13 @@
         <v>32</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>29</v>
@@ -4145,15 +4138,15 @@
         <v>31</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K40" s="10"/>
       <c r="L40" s="12"/>
       <c r="M40" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4161,13 +4154,13 @@
         <v>33</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>29</v>
@@ -4179,15 +4172,15 @@
         <v>31</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K41" s="10"/>
       <c r="L41" s="12"/>
       <c r="M41" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4195,33 +4188,33 @@
         <v>34</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H42" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K42" s="10"/>
       <c r="L42" s="12"/>
       <c r="M42" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4229,10 +4222,10 @@
         <v>35</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>59</v>
@@ -4241,21 +4234,21 @@
         <v>29</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K43" s="10"/>
       <c r="L43" s="12"/>
       <c r="M43" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4263,13 +4256,13 @@
         <v>36</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>29</v>
@@ -4281,10 +4274,10 @@
         <v>31</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K44" s="10"/>
       <c r="L44" s="12"/>
@@ -4297,13 +4290,13 @@
         <v>37</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>29</v>
@@ -4315,15 +4308,15 @@
         <v>31</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K45" s="10"/>
       <c r="L45" s="12"/>
       <c r="M45" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4331,10 +4324,10 @@
         <v>38</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>59</v>
@@ -4343,21 +4336,21 @@
         <v>29</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H46" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K46" s="10"/>
       <c r="L46" s="12"/>
       <c r="M46" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4365,10 +4358,10 @@
         <v>39</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>59</v>
@@ -4377,21 +4370,21 @@
         <v>29</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K47" s="10"/>
       <c r="L47" s="12"/>
       <c r="M47" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4399,10 +4392,10 @@
         <v>40</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>31</v>
@@ -4411,7 +4404,7 @@
         <v>86</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H48" s="10" t="s">
         <v>31</v>
@@ -4423,7 +4416,7 @@
         <v>31</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L48" s="12"/>
       <c r="M48" s="13" t="s">
@@ -4435,33 +4428,33 @@
         <v>41</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K49" s="10"/>
       <c r="L49" s="12"/>
       <c r="M49" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4469,33 +4462,33 @@
         <v>42</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K50" s="10"/>
       <c r="L50" s="12"/>
       <c r="M50" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4503,10 +4496,10 @@
         <v>43</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>59</v>
@@ -4515,21 +4508,21 @@
         <v>29</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K51" s="10"/>
       <c r="L51" s="12"/>
       <c r="M51" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4537,35 +4530,35 @@
         <v>44</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L52" s="12"/>
       <c r="M52" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4573,10 +4566,10 @@
         <v>45</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>59</v>
@@ -4585,21 +4578,21 @@
         <v>29</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H53" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K53" s="10"/>
       <c r="L53" s="12"/>
       <c r="M53" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4607,10 +4600,10 @@
         <v>46</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>59</v>
@@ -4619,21 +4612,21 @@
         <v>29</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K54" s="10"/>
       <c r="L54" s="12"/>
       <c r="M54" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4641,10 +4634,10 @@
         <v>47</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>59</v>
@@ -4653,21 +4646,21 @@
         <v>29</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K55" s="10"/>
       <c r="L55" s="12"/>
       <c r="M55" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4675,33 +4668,33 @@
         <v>48</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K56" s="10"/>
       <c r="L56" s="12"/>
       <c r="M56" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4709,35 +4702,35 @@
         <v>49</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K57" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L57" s="12"/>
       <c r="M57" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4745,35 +4738,35 @@
         <v>50</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K58" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L58" s="12"/>
       <c r="M58" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4781,33 +4774,33 @@
         <v>51</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H59" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K59" s="10"/>
       <c r="L59" s="12"/>
       <c r="M59" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4815,10 +4808,10 @@
         <v>52</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>59</v>
@@ -4827,21 +4820,21 @@
         <v>29</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K60" s="10"/>
       <c r="L60" s="12"/>
       <c r="M60" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4849,10 +4842,10 @@
         <v>53</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>59</v>
@@ -4861,16 +4854,16 @@
         <v>29</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K61" s="10"/>
       <c r="L61" s="12"/>
@@ -4881,35 +4874,35 @@
         <v>54</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L62" s="12"/>
       <c r="M62" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4917,35 +4910,35 @@
         <v>55</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K63" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L63" s="12"/>
       <c r="M63" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4953,10 +4946,10 @@
         <v>56</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>59</v>
@@ -4965,23 +4958,23 @@
         <v>29</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H64" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L64" s="12"/>
       <c r="M64" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4989,10 +4982,10 @@
         <v>57</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>59</v>
@@ -5001,21 +4994,21 @@
         <v>29</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H65" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K65" s="10"/>
       <c r="L65" s="12"/>
       <c r="M65" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5023,10 +5016,10 @@
         <v>58</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>31</v>
@@ -5035,10 +5028,10 @@
         <v>86</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I66" s="10" t="s">
         <v>31</v>
@@ -5047,11 +5040,11 @@
         <v>31</v>
       </c>
       <c r="K66" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L66" s="12"/>
       <c r="M66" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5059,35 +5052,35 @@
         <v>59</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J67" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K67" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L67" s="12"/>
       <c r="M67" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5095,10 +5088,10 @@
         <v>60</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>59</v>
@@ -5107,21 +5100,21 @@
         <v>29</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K68" s="10"/>
       <c r="L68" s="12"/>
       <c r="M68" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5129,10 +5122,10 @@
         <v>61</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>31</v>
@@ -5141,10 +5134,10 @@
         <v>86</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I69" s="10" t="s">
         <v>31</v>
@@ -5153,11 +5146,11 @@
         <v>31</v>
       </c>
       <c r="K69" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L69" s="12"/>
       <c r="M69" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5165,22 +5158,22 @@
         <v>62</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I70" s="10" t="s">
         <v>31</v>
@@ -5189,7 +5182,7 @@
         <v>31</v>
       </c>
       <c r="K70" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L70" s="12"/>
       <c r="M70" s="13" t="s">
@@ -5201,10 +5194,10 @@
         <v>63</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>59</v>
@@ -5219,15 +5212,15 @@
         <v>31</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J71" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K71" s="10"/>
       <c r="L71" s="12"/>
       <c r="M71" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5235,10 +5228,10 @@
         <v>64</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>59</v>
@@ -5253,15 +5246,15 @@
         <v>31</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K72" s="10"/>
       <c r="L72" s="12"/>
       <c r="M72" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5269,10 +5262,10 @@
         <v>65</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>59</v>
@@ -5287,7 +5280,7 @@
         <v>31</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J73" s="10" t="s">
         <v>115</v>
@@ -5295,7 +5288,7 @@
       <c r="K73" s="10"/>
       <c r="L73" s="12"/>
       <c r="M73" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5303,16 +5296,16 @@
         <v>66</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="G74" s="10" t="s">
         <v>30</v>
@@ -5321,17 +5314,15 @@
         <v>31</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="K74" s="10" t="s">
         <v>310</v>
       </c>
+      <c r="K74" s="10"/>
       <c r="L74" s="12"/>
       <c r="M74" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5339,7 +5330,7 @@
         <v>67</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>311</v>
@@ -5365,7 +5356,7 @@
       <c r="K75" s="10"/>
       <c r="L75" s="12"/>
       <c r="M75" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5373,7 +5364,7 @@
         <v>68</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>314</v>
@@ -5385,13 +5376,13 @@
         <v>29</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H76" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J76" s="10" t="s">
         <v>315</v>
@@ -5416,10 +5407,10 @@
         <v>319</v>
       </c>
       <c r="F77" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G77" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="G77" s="10" t="s">
-        <v>30</v>
       </c>
       <c r="H77" s="10" t="s">
         <v>31</v>
@@ -5430,12 +5421,10 @@
       <c r="J77" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="K77" s="10" t="s">
-        <v>322</v>
-      </c>
+      <c r="K77" s="10"/>
       <c r="L77" s="12"/>
       <c r="M77" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5446,10 +5435,10 @@
         <v>317</v>
       </c>
       <c r="D78" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="E78" s="10" t="s">
         <v>324</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>29</v>
@@ -5469,10 +5458,10 @@
       <c r="K78" s="10"/>
       <c r="L78" s="12"/>
       <c r="M78" s="13" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="9" t="n">
         <v>71</v>
       </c>
@@ -5486,10 +5475,10 @@
         <v>326</v>
       </c>
       <c r="F79" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G79" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="G79" s="10" t="s">
-        <v>30</v>
       </c>
       <c r="H79" s="10" t="s">
         <v>31</v>
@@ -5500,12 +5489,10 @@
       <c r="J79" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="K79" s="10" t="s">
-        <v>328</v>
-      </c>
+      <c r="K79" s="10"/>
       <c r="L79" s="12"/>
       <c r="M79" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5516,32 +5503,30 @@
         <v>317</v>
       </c>
       <c r="D80" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="E80" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="E80" s="10" t="s">
+      <c r="F80" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I80" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="F80" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H80" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I80" s="10" t="s">
+      <c r="J80" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="J80" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="K80" s="10" t="s">
-        <v>333</v>
-      </c>
+      <c r="K80" s="10"/>
       <c r="L80" s="12"/>
       <c r="M80" s="13" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5552,13 +5537,13 @@
         <v>317</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="G81" s="10" t="s">
         <v>30</v>
@@ -5570,14 +5555,12 @@
         <v>317</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="K81" s="10" t="s">
-        <v>338</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="K81" s="10"/>
       <c r="L81" s="12"/>
       <c r="M81" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5588,13 +5571,13 @@
         <v>317</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="G82" s="10" t="s">
         <v>87</v>
@@ -5603,17 +5586,15 @@
         <v>31</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="K82" s="10" t="s">
-        <v>343</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="K82" s="10"/>
       <c r="L82" s="12"/>
       <c r="M82" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5624,13 +5605,13 @@
         <v>317</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>30</v>
@@ -5639,17 +5620,15 @@
         <v>31</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="K83" s="10" t="s">
-        <v>348</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="K83" s="10"/>
       <c r="L83" s="12"/>
       <c r="M83" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5657,10 +5636,10 @@
         <v>76</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>59</v>
@@ -5675,15 +5654,15 @@
         <v>31</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="K84" s="10"/>
       <c r="L84" s="12"/>
       <c r="M84" s="13" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5691,16 +5670,16 @@
         <v>77</v>
       </c>
       <c r="C85" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="D85" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="D85" s="10" t="s">
-        <v>354</v>
-      </c>
       <c r="E85" s="10" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G85" s="10" t="s">
         <v>30</v>
@@ -5709,17 +5688,17 @@
         <v>31</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="K85" s="10" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="L85" s="12"/>
       <c r="M85" s="13" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5727,13 +5706,13 @@
         <v>78</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>86</v>
@@ -5751,11 +5730,11 @@
         <v>31</v>
       </c>
       <c r="K86" s="10" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="L86" s="12"/>
       <c r="M86" s="13" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5763,10 +5742,10 @@
         <v>79</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>31</v>
@@ -5787,11 +5766,11 @@
         <v>31</v>
       </c>
       <c r="K87" s="10" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L87" s="12"/>
       <c r="M87" s="13" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5799,33 +5778,33 @@
         <v>80</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F88" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="K88" s="10"/>
       <c r="L88" s="12"/>
       <c r="M88" s="13" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5833,10 +5812,10 @@
         <v>81</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>31</v>
@@ -5845,10 +5824,10 @@
         <v>86</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I89" s="10" t="s">
         <v>31</v>
@@ -5857,11 +5836,11 @@
         <v>31</v>
       </c>
       <c r="K89" s="10" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="L89" s="12"/>
       <c r="M89" s="13" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5869,10 +5848,10 @@
         <v>82</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>59</v>
@@ -5881,21 +5860,21 @@
         <v>29</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H90" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J90" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K90" s="10"/>
       <c r="L90" s="12"/>
       <c r="M90" s="13" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5903,10 +5882,10 @@
         <v>83</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>59</v>
@@ -5915,21 +5894,21 @@
         <v>29</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="K91" s="10"/>
       <c r="L91" s="12"/>
       <c r="M91" s="13" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5937,22 +5916,22 @@
         <v>84</v>
       </c>
       <c r="C92" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="D92" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="D92" s="10" t="s">
-        <v>377</v>
-      </c>
       <c r="E92" s="10" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I92" s="10" t="s">
         <v>31</v>
@@ -5961,11 +5940,11 @@
         <v>31</v>
       </c>
       <c r="K92" s="10" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="L92" s="12"/>
       <c r="M92" s="13" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5973,35 +5952,35 @@
         <v>85</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="K93" s="10" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="L93" s="12"/>
       <c r="M93" s="13" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6009,10 +5988,10 @@
         <v>86</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>59</v>
@@ -6021,21 +6000,21 @@
         <v>29</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="K94" s="10"/>
       <c r="L94" s="12"/>
       <c r="M94" s="13" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6043,35 +6022,35 @@
         <v>87</v>
       </c>
       <c r="C95" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="D95" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="D95" s="10" t="s">
-        <v>388</v>
-      </c>
       <c r="E95" s="10" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I95" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="J95" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="J95" s="10" t="s">
-        <v>390</v>
-      </c>
       <c r="K95" s="10" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="L95" s="12"/>
       <c r="M95" s="13" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6079,10 +6058,10 @@
         <v>88</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>59</v>
@@ -6097,15 +6076,15 @@
         <v>31</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="K96" s="10"/>
       <c r="L96" s="12"/>
       <c r="M96" s="13" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6113,10 +6092,10 @@
         <v>89</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>59</v>
@@ -6131,15 +6110,15 @@
         <v>31</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="K97" s="10"/>
       <c r="L97" s="12"/>
       <c r="M97" s="13" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6147,16 +6126,16 @@
         <v>90</v>
       </c>
       <c r="C98" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="E98" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="D98" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>402</v>
-      </c>
       <c r="F98" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G98" s="10" t="s">
         <v>30</v>
@@ -6165,17 +6144,17 @@
         <v>31</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="K98" s="10" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="L98" s="12"/>
       <c r="M98" s="13" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6183,16 +6162,16 @@
         <v>91</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G99" s="10" t="s">
         <v>30</v>
@@ -6201,17 +6180,17 @@
         <v>31</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="K99" s="10" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="L99" s="12"/>
       <c r="M99" s="13" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6219,16 +6198,16 @@
         <v>92</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G100" s="10" t="s">
         <v>30</v>
@@ -6237,17 +6216,17 @@
         <v>31</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="K100" s="10" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="L100" s="12"/>
       <c r="M100" s="13" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6255,10 +6234,10 @@
         <v>93</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>31</v>
@@ -6267,7 +6246,7 @@
         <v>86</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>31</v>
@@ -6279,11 +6258,11 @@
         <v>31</v>
       </c>
       <c r="K101" s="10" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L101" s="12"/>
       <c r="M101" s="13" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6291,10 +6270,10 @@
         <v>94</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="E102" s="10" t="s">
         <v>31</v>
@@ -6303,7 +6282,7 @@
         <v>86</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H102" s="10" t="s">
         <v>31</v>
@@ -6315,11 +6294,11 @@
         <v>31</v>
       </c>
       <c r="K102" s="10" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="L102" s="12"/>
       <c r="M102" s="13" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6327,10 +6306,10 @@
         <v>95</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>59</v>
@@ -6345,15 +6324,15 @@
         <v>31</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="K103" s="10"/>
       <c r="L103" s="12"/>
       <c r="M103" s="13" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6361,10 +6340,10 @@
         <v>96</v>
       </c>
       <c r="C104" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="D104" s="10" t="s">
         <v>419</v>
-      </c>
-      <c r="D104" s="10" t="s">
-        <v>424</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>59</v>
@@ -6379,15 +6358,15 @@
         <v>31</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="J104" s="10" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="K104" s="10"/>
       <c r="L104" s="12"/>
       <c r="M104" s="13" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6395,35 +6374,35 @@
         <v>97</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>59</v>
       </c>
       <c r="F105" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G105" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G105" s="10" t="s">
-        <v>76</v>
-      </c>
       <c r="H105" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="J105" s="10" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="K105" s="10" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="L105" s="12"/>
       <c r="M105" s="13" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6431,10 +6410,10 @@
         <v>98</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>59</v>
@@ -6449,47 +6428,47 @@
         <v>31</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="K106" s="10"/>
       <c r="L106" s="12"/>
       <c r="M106" s="13" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B107" s="9" t="n">
         <v>99</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D107" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="F107" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I107" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="J107" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="K107" s="10" t="s">
         <v>435</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F107" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I107" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J107" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K107" s="10" t="s">
-        <v>436</v>
       </c>
       <c r="L107" s="12"/>
       <c r="M107" s="13" t="s">
@@ -6501,10 +6480,10 @@
         <v>100</v>
       </c>
       <c r="C108" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="D108" s="10" t="s">
         <v>437</v>
-      </c>
-      <c r="D108" s="10" t="s">
-        <v>438</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>59</v>
@@ -6519,32 +6498,32 @@
         <v>31</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K108" s="10"/>
       <c r="L108" s="12"/>
       <c r="M108" s="13" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B109" s="9" t="n">
         <v>101</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D109" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="E109" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="E109" s="10" t="s">
-        <v>442</v>
-      </c>
       <c r="F109" s="11" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="G109" s="10" t="s">
         <v>30</v>
@@ -6553,14 +6532,12 @@
         <v>31</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="J109" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="K109" s="10" t="s">
-        <v>444</v>
-      </c>
+      <c r="K109" s="10"/>
       <c r="L109" s="12"/>
       <c r="M109" s="13" t="s">
         <v>44</v>
@@ -6571,35 +6548,33 @@
         <v>102</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D110" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="E110" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="E110" s="10" t="s">
+      <c r="F110" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H110" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I110" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="J110" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="F110" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G110" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="H110" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I110" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="J110" s="10" t="s">
-        <v>447</v>
-      </c>
-      <c r="K110" s="10" t="s">
-        <v>448</v>
-      </c>
+      <c r="K110" s="10"/>
       <c r="L110" s="12"/>
       <c r="M110" s="13" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6607,10 +6582,10 @@
         <v>103</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>59</v>
@@ -6625,15 +6600,15 @@
         <v>31</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K111" s="10"/>
       <c r="L111" s="12"/>
       <c r="M111" s="13" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6641,10 +6616,10 @@
         <v>104</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>59</v>
@@ -6659,15 +6634,15 @@
         <v>31</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J112" s="10" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K112" s="10"/>
       <c r="L112" s="12"/>
       <c r="M112" s="13" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6675,35 +6650,35 @@
         <v>105</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D113" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="F113" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G113" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I113" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="E113" s="10" t="s">
+      <c r="J113" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="F113" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G113" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I113" s="10" t="s">
+      <c r="K113" s="10" t="s">
         <v>460</v>
-      </c>
-      <c r="J113" s="10" t="s">
-        <v>461</v>
-      </c>
-      <c r="K113" s="10" t="s">
-        <v>462</v>
       </c>
       <c r="L113" s="12"/>
       <c r="M113" s="13" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6711,10 +6686,10 @@
         <v>106</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>59</v>
@@ -6729,15 +6704,15 @@
         <v>31</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="K114" s="10"/>
       <c r="L114" s="12"/>
       <c r="M114" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6745,35 +6720,35 @@
         <v>107</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D115" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="F115" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G115" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I115" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="E115" s="10" t="s">
+      <c r="J115" s="10" t="s">
         <v>467</v>
       </c>
-      <c r="F115" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G115" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I115" s="10" t="s">
+      <c r="K115" s="10" t="s">
         <v>468</v>
-      </c>
-      <c r="J115" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="K115" s="10" t="s">
-        <v>470</v>
       </c>
       <c r="L115" s="12"/>
       <c r="M115" s="13" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6781,10 +6756,10 @@
         <v>108</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>59</v>
@@ -6799,15 +6774,15 @@
         <v>31</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K116" s="10"/>
       <c r="L116" s="12"/>
       <c r="M116" s="13" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6815,10 +6790,10 @@
         <v>109</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>59</v>
@@ -6833,15 +6808,15 @@
         <v>31</v>
       </c>
       <c r="I117" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="J117" s="10" t="s">
         <v>473</v>
-      </c>
-      <c r="J117" s="10" t="s">
-        <v>321</v>
       </c>
       <c r="K117" s="10"/>
       <c r="L117" s="12"/>
       <c r="M117" s="13" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6849,10 +6824,10 @@
         <v>110</v>
       </c>
       <c r="C118" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="D118" s="10" t="s">
         <v>476</v>
-      </c>
-      <c r="D118" s="10" t="s">
-        <v>477</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>31</v>
@@ -6873,11 +6848,11 @@
         <v>31</v>
       </c>
       <c r="K118" s="10" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L118" s="12"/>
       <c r="M118" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6885,16 +6860,16 @@
         <v>111</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D119" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="E119" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="E119" s="10" t="s">
-        <v>480</v>
-      </c>
       <c r="F119" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G119" s="10" t="s">
         <v>30</v>
@@ -6903,17 +6878,17 @@
         <v>31</v>
       </c>
       <c r="I119" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="J119" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="J119" s="10" t="s">
+      <c r="K119" s="10" t="s">
         <v>482</v>
-      </c>
-      <c r="K119" s="10" t="s">
-        <v>483</v>
       </c>
       <c r="L119" s="12"/>
       <c r="M119" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6921,33 +6896,33 @@
         <v>112</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D120" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="E120" s="10" t="s">
         <v>484</v>
-      </c>
-      <c r="E120" s="10" t="s">
-        <v>485</v>
       </c>
       <c r="F120" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G120" s="10" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H120" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I120" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="J120" s="10" t="s">
         <v>486</v>
-      </c>
-      <c r="J120" s="10" t="s">
-        <v>487</v>
       </c>
       <c r="K120" s="10"/>
       <c r="L120" s="12"/>
       <c r="M120" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6955,35 +6930,35 @@
         <v>113</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D121" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="E121" s="10" t="s">
         <v>488</v>
       </c>
-      <c r="E121" s="10" t="s">
+      <c r="F121" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G121" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H121" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I121" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="F121" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G121" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I121" s="10" t="s">
+      <c r="J121" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="J121" s="10" t="s">
+      <c r="K121" s="10" t="s">
         <v>491</v>
-      </c>
-      <c r="K121" s="10" t="s">
-        <v>492</v>
       </c>
       <c r="L121" s="12"/>
       <c r="M121" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6991,35 +6966,35 @@
         <v>114</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D122" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="E122" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="E122" s="10" t="s">
+      <c r="F122" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G122" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H122" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I122" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="F122" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G122" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H122" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I122" s="10" t="s">
+      <c r="J122" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="J122" s="10" t="s">
+      <c r="K122" s="10" t="s">
         <v>496</v>
-      </c>
-      <c r="K122" s="10" t="s">
-        <v>497</v>
       </c>
       <c r="L122" s="12"/>
       <c r="M122" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7027,16 +7002,16 @@
         <v>115</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D123" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="E123" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="E123" s="10" t="s">
-        <v>499</v>
-      </c>
       <c r="F123" s="11" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G123" s="10" t="s">
         <v>30</v>
@@ -7048,14 +7023,14 @@
         <v>32</v>
       </c>
       <c r="J123" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="K123" s="10" t="s">
         <v>500</v>
-      </c>
-      <c r="K123" s="10" t="s">
-        <v>501</v>
       </c>
       <c r="L123" s="12"/>
       <c r="M123" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7063,10 +7038,10 @@
         <v>116</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>31</v>
@@ -7075,7 +7050,7 @@
         <v>86</v>
       </c>
       <c r="G124" s="10" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H124" s="10" t="s">
         <v>31</v>
@@ -7087,11 +7062,11 @@
         <v>31</v>
       </c>
       <c r="K124" s="10" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L124" s="12"/>
       <c r="M124" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7099,10 +7074,10 @@
         <v>117</v>
       </c>
       <c r="C125" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="D125" s="10" t="s">
         <v>504</v>
-      </c>
-      <c r="D125" s="10" t="s">
-        <v>505</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>59</v>
@@ -7111,21 +7086,21 @@
         <v>29</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="K125" s="10"/>
       <c r="L125" s="12"/>
       <c r="M125" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7133,35 +7108,35 @@
         <v>118</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D126" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="E126" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="E126" s="10" t="s">
+      <c r="F126" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G126" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="H126" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="I126" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="J126" s="10" t="s">
         <v>509</v>
       </c>
-      <c r="F126" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G126" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="H126" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="I126" s="10" t="s">
-        <v>506</v>
-      </c>
-      <c r="J126" s="10" t="s">
+      <c r="K126" s="10" t="s">
         <v>510</v>
-      </c>
-      <c r="K126" s="10" t="s">
-        <v>511</v>
       </c>
       <c r="L126" s="12"/>
       <c r="M126" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7169,10 +7144,10 @@
         <v>119</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>31</v>
@@ -7181,10 +7156,10 @@
         <v>86</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I127" s="10" t="s">
         <v>31</v>
@@ -7193,11 +7168,11 @@
         <v>31</v>
       </c>
       <c r="K127" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L127" s="12"/>
       <c r="M127" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7205,10 +7180,10 @@
         <v>120</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>59</v>
@@ -7217,21 +7192,21 @@
         <v>29</v>
       </c>
       <c r="G128" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H128" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K128" s="10"/>
       <c r="L128" s="12"/>
       <c r="M128" s="13" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7239,35 +7214,35 @@
         <v>121</v>
       </c>
       <c r="C129" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="D129" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="D129" s="10" t="s">
+      <c r="E129" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="E129" s="10" t="s">
+      <c r="F129" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G129" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H129" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="I129" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="F129" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G129" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="I129" s="10" t="s">
+      <c r="J129" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="J129" s="10" t="s">
+      <c r="K129" s="10" t="s">
         <v>521</v>
-      </c>
-      <c r="K129" s="10" t="s">
-        <v>522</v>
       </c>
       <c r="L129" s="12"/>
       <c r="M129" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7275,35 +7250,35 @@
         <v>122</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D130" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="E130" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="E130" s="10" t="s">
+      <c r="F130" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G130" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="H130" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="I130" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="J130" s="10" t="s">
         <v>524</v>
       </c>
-      <c r="F130" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G130" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="H130" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="I130" s="10" t="s">
-        <v>506</v>
-      </c>
-      <c r="J130" s="10" t="s">
+      <c r="K130" s="10" t="s">
         <v>525</v>
-      </c>
-      <c r="K130" s="10" t="s">
-        <v>526</v>
       </c>
       <c r="L130" s="12"/>
       <c r="M130" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7311,35 +7286,35 @@
         <v>123</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D131" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="E131" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="E131" s="10" t="s">
+      <c r="F131" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G131" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H131" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I131" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="J131" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="F131" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G131" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I131" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="J131" s="10" t="s">
+      <c r="K131" s="10" t="s">
         <v>529</v>
-      </c>
-      <c r="K131" s="10" t="s">
-        <v>530</v>
       </c>
       <c r="L131" s="12"/>
       <c r="M131" s="13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7347,35 +7322,35 @@
         <v>124</v>
       </c>
       <c r="C132" s="10" t="s">
+        <v>531</v>
+      </c>
+      <c r="D132" s="10" t="s">
         <v>532</v>
       </c>
-      <c r="D132" s="10" t="s">
+      <c r="E132" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="E132" s="10" t="s">
+      <c r="F132" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G132" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H132" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="I132" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="J132" s="10" t="s">
         <v>534</v>
       </c>
-      <c r="F132" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G132" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="H132" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="I132" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="J132" s="10" t="s">
+      <c r="K132" s="10" t="s">
         <v>535</v>
-      </c>
-      <c r="K132" s="10" t="s">
-        <v>536</v>
       </c>
       <c r="L132" s="12"/>
       <c r="M132" s="13" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7383,35 +7358,35 @@
         <v>125</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D133" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="E133" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="E133" s="10" t="s">
+      <c r="F133" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G133" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H133" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="I133" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="J133" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="K133" s="10" t="s">
         <v>539</v>
-      </c>
-      <c r="F133" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G133" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="I133" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="J133" s="10" t="s">
-        <v>447</v>
-      </c>
-      <c r="K133" s="10" t="s">
-        <v>540</v>
       </c>
       <c r="L133" s="12"/>
       <c r="M133" s="13" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7419,35 +7394,35 @@
         <v>126</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D134" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="E134" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="E134" s="10" t="s">
+      <c r="F134" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G134" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="H134" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="I134" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="J134" s="10" t="s">
         <v>542</v>
       </c>
-      <c r="F134" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G134" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="H134" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="I134" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="J134" s="10" t="s">
+      <c r="K134" s="10" t="s">
         <v>543</v>
-      </c>
-      <c r="K134" s="10" t="s">
-        <v>544</v>
       </c>
       <c r="L134" s="12"/>
       <c r="M134" s="13" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7455,10 +7430,10 @@
         <v>127</v>
       </c>
       <c r="C135" s="10" t="s">
+        <v>544</v>
+      </c>
+      <c r="D135" s="10" t="s">
         <v>545</v>
-      </c>
-      <c r="D135" s="10" t="s">
-        <v>546</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>59</v>
@@ -7467,21 +7442,21 @@
         <v>29</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J135" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K135" s="10"/>
       <c r="L135" s="12"/>
       <c r="M135" s="13" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7489,22 +7464,22 @@
         <v>128</v>
       </c>
       <c r="C136" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="D136" s="10" t="s">
         <v>548</v>
       </c>
-      <c r="D136" s="10" t="s">
+      <c r="E136" s="10" t="s">
         <v>549</v>
-      </c>
-      <c r="E136" s="10" t="s">
-        <v>550</v>
       </c>
       <c r="F136" s="11" t="s">
         <v>86</v>
       </c>
       <c r="G136" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H136" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I136" s="10" t="s">
         <v>31</v>
@@ -7513,7 +7488,7 @@
         <v>31</v>
       </c>
       <c r="K136" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L136" s="12"/>
       <c r="M136" s="13" t="s">
@@ -7525,35 +7500,35 @@
         <v>129</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D137" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="E137" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="E137" s="10" t="s">
+      <c r="F137" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G137" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H137" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="I137" s="10" t="s">
         <v>553</v>
       </c>
-      <c r="F137" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G137" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="H137" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="I137" s="10" t="s">
+      <c r="J137" s="10" t="s">
         <v>554</v>
       </c>
-      <c r="J137" s="10" t="s">
+      <c r="K137" s="10" t="s">
         <v>555</v>
-      </c>
-      <c r="K137" s="10" t="s">
-        <v>556</v>
       </c>
       <c r="L137" s="12"/>
       <c r="M137" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7561,35 +7536,35 @@
         <v>130</v>
       </c>
       <c r="C138" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="D138" s="10" t="s">
         <v>557</v>
       </c>
-      <c r="D138" s="10" t="s">
+      <c r="E138" s="10" t="s">
         <v>558</v>
       </c>
-      <c r="E138" s="10" t="s">
+      <c r="F138" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G138" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="F138" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G138" s="10" t="s">
+      <c r="H138" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I138" s="10" t="s">
         <v>560</v>
       </c>
-      <c r="H138" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I138" s="10" t="s">
+      <c r="J138" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="J138" s="10" t="s">
+      <c r="K138" s="10" t="s">
         <v>562</v>
-      </c>
-      <c r="K138" s="10" t="s">
-        <v>563</v>
       </c>
       <c r="L138" s="12"/>
       <c r="M138" s="13" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7597,35 +7572,35 @@
         <v>131</v>
       </c>
       <c r="C139" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="D139" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="D139" s="10" t="s">
+      <c r="E139" s="10" t="s">
         <v>566</v>
       </c>
-      <c r="E139" s="10" t="s">
+      <c r="F139" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G139" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="H139" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I139" s="10" t="s">
         <v>567</v>
       </c>
-      <c r="F139" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G139" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="H139" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I139" s="10" t="s">
+      <c r="J139" s="10" t="s">
         <v>568</v>
       </c>
-      <c r="J139" s="10" t="s">
+      <c r="K139" s="10" t="s">
         <v>569</v>
-      </c>
-      <c r="K139" s="10" t="s">
-        <v>570</v>
       </c>
       <c r="L139" s="12"/>
       <c r="M139" s="13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7633,10 +7608,10 @@
         <v>132</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E140" s="10" t="s">
         <v>59</v>
@@ -7645,21 +7620,21 @@
         <v>29</v>
       </c>
       <c r="G140" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H140" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I140" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="J140" s="10" t="s">
         <v>572</v>
-      </c>
-      <c r="J140" s="10" t="s">
-        <v>573</v>
       </c>
       <c r="K140" s="10"/>
       <c r="L140" s="12"/>
       <c r="M140" s="13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7667,10 +7642,10 @@
         <v>133</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>31</v>
@@ -7679,7 +7654,7 @@
         <v>86</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H141" s="10" t="s">
         <v>31</v>
@@ -7691,11 +7666,11 @@
         <v>31</v>
       </c>
       <c r="K141" s="10" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L141" s="12"/>
       <c r="M141" s="13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7703,10 +7678,10 @@
         <v>134</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E142" s="10" t="s">
         <v>59</v>
@@ -7715,21 +7690,21 @@
         <v>29</v>
       </c>
       <c r="G142" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H142" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I142" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="J142" s="10" t="s">
         <v>576</v>
-      </c>
-      <c r="J142" s="10" t="s">
-        <v>577</v>
       </c>
       <c r="K142" s="10"/>
       <c r="L142" s="12"/>
       <c r="M142" s="13" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7737,35 +7712,35 @@
         <v>135</v>
       </c>
       <c r="C143" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="D143" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="D143" s="10" t="s">
+      <c r="E143" s="10" t="s">
         <v>580</v>
       </c>
-      <c r="E143" s="10" t="s">
+      <c r="F143" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G143" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="H143" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I143" s="10" t="s">
         <v>581</v>
       </c>
-      <c r="F143" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G143" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I143" s="10" t="s">
+      <c r="J143" s="10" t="s">
         <v>582</v>
       </c>
-      <c r="J143" s="10" t="s">
+      <c r="K143" s="10" t="s">
         <v>583</v>
-      </c>
-      <c r="K143" s="10" t="s">
-        <v>584</v>
       </c>
       <c r="L143" s="12"/>
       <c r="M143" s="13" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7773,35 +7748,35 @@
         <v>136</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D144" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="E144" s="10" t="s">
         <v>586</v>
       </c>
-      <c r="E144" s="10" t="s">
+      <c r="F144" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G144" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="H144" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I144" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="J144" s="10" t="s">
         <v>587</v>
       </c>
-      <c r="F144" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G144" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="H144" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I144" s="10" t="s">
-        <v>582</v>
-      </c>
-      <c r="J144" s="10" t="s">
+      <c r="K144" s="10" t="s">
         <v>588</v>
-      </c>
-      <c r="K144" s="10" t="s">
-        <v>589</v>
       </c>
       <c r="L144" s="12"/>
       <c r="M144" s="13" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7809,10 +7784,10 @@
         <v>137</v>
       </c>
       <c r="C145" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="D145" s="10" t="s">
         <v>591</v>
-      </c>
-      <c r="D145" s="10" t="s">
-        <v>592</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>59</v>
@@ -7821,21 +7796,21 @@
         <v>29</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I145" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="J145" s="10" t="s">
         <v>593</v>
-      </c>
-      <c r="J145" s="10" t="s">
-        <v>594</v>
       </c>
       <c r="K145" s="10"/>
       <c r="L145" s="12"/>
       <c r="M145" s="13" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7843,10 +7818,10 @@
         <v>138</v>
       </c>
       <c r="C146" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="D146" s="10" t="s">
         <v>596</v>
-      </c>
-      <c r="D146" s="10" t="s">
-        <v>597</v>
       </c>
       <c r="E146" s="10" t="s">
         <v>59</v>
@@ -7855,21 +7830,21 @@
         <v>29</v>
       </c>
       <c r="G146" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H146" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I146" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="J146" s="10" t="s">
         <v>598</v>
-      </c>
-      <c r="J146" s="10" t="s">
-        <v>599</v>
       </c>
       <c r="K146" s="10"/>
       <c r="L146" s="12"/>
       <c r="M146" s="13" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7877,35 +7852,35 @@
         <v>139</v>
       </c>
       <c r="C147" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="D147" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="D147" s="10" t="s">
+      <c r="E147" s="10" t="s">
         <v>601</v>
       </c>
-      <c r="E147" s="10" t="s">
+      <c r="F147" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G147" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="H147" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I147" s="10" t="s">
         <v>602</v>
       </c>
-      <c r="F147" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G147" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="H147" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I147" s="10" t="s">
+      <c r="J147" s="10" t="s">
         <v>603</v>
       </c>
-      <c r="J147" s="10" t="s">
+      <c r="K147" s="10" t="s">
         <v>604</v>
-      </c>
-      <c r="K147" s="10" t="s">
-        <v>605</v>
       </c>
       <c r="L147" s="12"/>
       <c r="M147" s="13" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7913,35 +7888,35 @@
         <v>140</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D148" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="E148" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="E148" s="10" t="s">
+      <c r="F148" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G148" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="H148" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I148" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="F148" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G148" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="H148" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I148" s="10" t="s">
+      <c r="J148" s="10" t="s">
         <v>608</v>
       </c>
-      <c r="J148" s="10" t="s">
+      <c r="K148" s="10" t="s">
         <v>609</v>
-      </c>
-      <c r="K148" s="10" t="s">
-        <v>610</v>
       </c>
       <c r="L148" s="12"/>
       <c r="M148" s="13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7949,35 +7924,35 @@
         <v>141</v>
       </c>
       <c r="C149" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="D149" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="D149" s="10" t="s">
+      <c r="E149" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="E149" s="10" t="s">
+      <c r="F149" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G149" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="H149" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I149" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J149" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K149" s="10" t="s">
         <v>614</v>
-      </c>
-      <c r="F149" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G149" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="H149" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I149" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J149" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K149" s="10" t="s">
-        <v>615</v>
       </c>
       <c r="L149" s="12"/>
       <c r="M149" s="13" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7985,10 +7960,10 @@
         <v>142</v>
       </c>
       <c r="C150" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="D150" s="10" t="s">
         <v>616</v>
-      </c>
-      <c r="D150" s="10" t="s">
-        <v>617</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>59</v>
@@ -7997,21 +7972,21 @@
         <v>29</v>
       </c>
       <c r="G150" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H150" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I150" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="J150" s="10" t="s">
         <v>618</v>
-      </c>
-      <c r="J150" s="10" t="s">
-        <v>619</v>
       </c>
       <c r="K150" s="10"/>
       <c r="L150" s="12"/>
       <c r="M150" s="13" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8019,35 +7994,35 @@
         <v>143</v>
       </c>
       <c r="C151" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D151" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="D151" s="10" t="s">
+      <c r="E151" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="E151" s="10" t="s">
+      <c r="F151" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G151" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="H151" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I151" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="J151" s="10" t="s">
         <v>623</v>
       </c>
-      <c r="F151" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G151" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="H151" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I151" s="10" t="s">
-        <v>561</v>
-      </c>
-      <c r="J151" s="10" t="s">
+      <c r="K151" s="10" t="s">
         <v>624</v>
-      </c>
-      <c r="K151" s="10" t="s">
-        <v>625</v>
       </c>
       <c r="L151" s="12"/>
       <c r="M151" s="13" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8055,10 +8030,10 @@
         <v>144</v>
       </c>
       <c r="C152" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="D152" s="10" t="s">
         <v>627</v>
-      </c>
-      <c r="D152" s="10" t="s">
-        <v>628</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>59</v>
@@ -8067,23 +8042,23 @@
         <v>29</v>
       </c>
       <c r="G152" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H152" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I152" s="10" t="s">
+        <v>628</v>
+      </c>
+      <c r="J152" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="J152" s="10" t="s">
+      <c r="K152" s="10" t="s">
         <v>630</v>
-      </c>
-      <c r="K152" s="10" t="s">
-        <v>631</v>
       </c>
       <c r="L152" s="12"/>
       <c r="M152" s="13" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8091,10 +8066,10 @@
         <v>145</v>
       </c>
       <c r="C153" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="D153" s="10" t="s">
         <v>633</v>
-      </c>
-      <c r="D153" s="10" t="s">
-        <v>634</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>59</v>
@@ -8103,21 +8078,21 @@
         <v>29</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H153" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I153" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="K153" s="10"/>
       <c r="L153" s="12"/>
       <c r="M153" s="13" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8125,35 +8100,35 @@
         <v>146</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D154" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="E154" s="10" t="s">
         <v>637</v>
       </c>
-      <c r="E154" s="10" t="s">
+      <c r="F154" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G154" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="H154" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I154" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="J154" s="10" t="s">
         <v>638</v>
       </c>
-      <c r="F154" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G154" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="H154" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I154" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="J154" s="10" t="s">
+      <c r="K154" s="10" t="s">
         <v>639</v>
-      </c>
-      <c r="K154" s="10" t="s">
-        <v>640</v>
       </c>
       <c r="L154" s="12"/>
       <c r="M154" s="13" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8161,10 +8136,10 @@
         <v>147</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>31</v>
@@ -8173,7 +8148,7 @@
         <v>86</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H155" s="10" t="s">
         <v>31</v>
@@ -8185,11 +8160,11 @@
         <v>31</v>
       </c>
       <c r="K155" s="10" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L155" s="12"/>
       <c r="M155" s="13" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8197,10 +8172,10 @@
         <v>148</v>
       </c>
       <c r="C156" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="D156" s="10" t="s">
         <v>643</v>
-      </c>
-      <c r="D156" s="10" t="s">
-        <v>644</v>
       </c>
       <c r="E156" s="10" t="s">
         <v>59</v>
@@ -8209,23 +8184,23 @@
         <v>29</v>
       </c>
       <c r="G156" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H156" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I156" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="J156" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="K156" s="10" t="s">
         <v>645</v>
-      </c>
-      <c r="K156" s="10" t="s">
-        <v>646</v>
       </c>
       <c r="L156" s="12"/>
       <c r="M156" s="13" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8233,10 +8208,10 @@
         <v>149</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>31</v>
@@ -8245,7 +8220,7 @@
         <v>86</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H157" s="10" t="s">
         <v>31</v>
@@ -8257,7 +8232,7 @@
         <v>31</v>
       </c>
       <c r="K157" s="10" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L157" s="12"/>
       <c r="M157" s="13" t="s">
@@ -8269,19 +8244,19 @@
         <v>150</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D158" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="E158" s="10" t="s">
         <v>649</v>
-      </c>
-      <c r="E158" s="10" t="s">
-        <v>650</v>
       </c>
       <c r="F158" s="11" t="s">
         <v>86</v>
       </c>
       <c r="G158" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H158" s="10" t="s">
         <v>31</v>
@@ -8293,7 +8268,7 @@
         <v>31</v>
       </c>
       <c r="K158" s="10" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="L158" s="12"/>
       <c r="M158" s="13" t="s">
@@ -8350,7 +8325,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8358,22 +8333,22 @@
         <v>15</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>86</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8386,11 +8361,11 @@
       </c>
       <c r="D5" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B5,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B5,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B5,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -8402,7 +8377,7 @@
       </c>
       <c r="H5" s="19" t="n">
         <f aca="false">IF(C5&gt;0,D5/C5,0)</f>
-        <v>0.875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8444,7 +8419,7 @@
       </c>
       <c r="D7" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B7,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B7,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
@@ -8456,16 +8431,16 @@
       </c>
       <c r="G7" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B7,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="19" t="n">
         <f aca="false">IF(C7&gt;0,D7/C7,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B8)</f>
@@ -8494,7 +8469,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C9" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B9)</f>
@@ -8523,7 +8498,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C10" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B10)</f>
@@ -8552,7 +8527,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C11" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B11)</f>
@@ -8581,7 +8556,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C12" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B12)</f>
@@ -8610,7 +8585,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C13" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B13)</f>
@@ -8639,7 +8614,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C14" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B14)</f>
@@ -8668,7 +8643,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C15" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B15)</f>
@@ -8697,7 +8672,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C16" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B16)</f>
@@ -8726,7 +8701,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B17)</f>
@@ -8755,7 +8730,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="17" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B18)</f>
@@ -8784,7 +8759,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C19" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B19)</f>
@@ -8792,11 +8767,11 @@
       </c>
       <c r="D19" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B19,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B19,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B19,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -8808,7 +8783,7 @@
       </c>
       <c r="H19" s="19" t="n">
         <f aca="false">IF(C19&gt;0,D19/C19,0)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8821,11 +8796,11 @@
       </c>
       <c r="D20" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B20,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E20" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B20,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F20" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B20,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -8837,12 +8812,12 @@
       </c>
       <c r="H20" s="19" t="n">
         <f aca="false">IF(C20&gt;0,D20/C20,0)</f>
-        <v>0.142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="17" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B21)</f>
@@ -8871,7 +8846,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="17" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B22)</f>
@@ -8900,7 +8875,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="17" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B23)</f>
@@ -8929,7 +8904,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="17" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B24)</f>
@@ -8958,7 +8933,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="17" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C25" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B25)</f>
@@ -8987,7 +8962,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="17" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B26)</f>
@@ -9016,7 +8991,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="17" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C27" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B27)</f>
@@ -9045,7 +9020,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="17" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C28" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B28)</f>
@@ -9053,7 +9028,7 @@
       </c>
       <c r="D28" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B28,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B28,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
@@ -9065,16 +9040,16 @@
       </c>
       <c r="G28" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B28,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="19" t="n">
         <f aca="false">IF(C28&gt;0,D28/C28,0)</f>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C29" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B29)</f>
@@ -9082,11 +9057,11 @@
       </c>
       <c r="D29" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B29,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B29,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F29" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B29,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9098,12 +9073,12 @@
       </c>
       <c r="H29" s="19" t="n">
         <f aca="false">IF(C29&gt;0,D29/C29,0)</f>
-        <v>0.333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="17" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C30" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B30)</f>
@@ -9132,7 +9107,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C31" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B31)</f>
@@ -9161,7 +9136,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="17" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C32" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B32)</f>
@@ -9190,7 +9165,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="17" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C33" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B33)</f>
@@ -9219,7 +9194,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="17" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C34" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B34)</f>
@@ -9248,7 +9223,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="17" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C35" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B35)</f>
@@ -9277,7 +9252,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="17" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C36" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B36)</f>
@@ -9306,7 +9281,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="17" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C37" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B37)</f>
@@ -9335,7 +9310,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="17" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C38" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B38)</f>
@@ -9364,7 +9339,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="17" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C39" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B39)</f>
@@ -9393,7 +9368,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="17" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C40" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B40)</f>
@@ -9422,7 +9397,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="17" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C41" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B41)</f>
@@ -9451,7 +9426,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="17" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C42" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B42)</f>
@@ -9480,7 +9455,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C43" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B43)</f>
@@ -9509,7 +9484,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="17" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C44" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B44)</f>
@@ -9538,7 +9513,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="17" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C45" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B45)</f>
@@ -9567,7 +9542,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="17" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C46" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B46)</f>
@@ -9596,7 +9571,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="17" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C47" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B47)</f>
@@ -9625,7 +9600,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="17" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C48" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B48)</f>
@@ -9654,7 +9629,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="17" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C49" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B49)</f>
@@ -9683,7 +9658,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="20" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C50" s="21" t="n">
         <f aca="false">SUM(C5:C49)</f>
@@ -9691,11 +9666,11 @@
       </c>
       <c r="D50" s="21" t="n">
         <f aca="false">SUM(D5:D49)</f>
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">SUM(E5:E49)</f>
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F50" s="21" t="n">
         <f aca="false">SUM(F5:F49)</f>
@@ -9703,11 +9678,11 @@
       </c>
       <c r="G50" s="21" t="n">
         <f aca="false">SUM(G5:G49)</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H50" s="22" t="n">
         <f aca="false">IF(C50&gt;0,D50/C50,0)</f>
-        <v>0.533333333333333</v>
+        <v>0.613333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -9738,18 +9713,18 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="23" t="s">
+        <v>655</v>
+      </c>
+      <c r="C4" s="23" t="s">
         <v>656</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="D4" s="23" t="s">
         <v>657</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>658</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>18</v>
@@ -9757,83 +9732,83 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
+        <v>658</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>659</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="D5" s="24" t="s">
         <v>660</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>661</v>
-      </c>
       <c r="E5" s="25" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="24" t="s">
+        <v>661</v>
+      </c>
+      <c r="C6" s="24" t="s">
         <v>662</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="D6" s="24" t="s">
         <v>663</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>664</v>
-      </c>
       <c r="E6" s="25" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="24" t="s">
+        <v>664</v>
+      </c>
+      <c r="C7" s="24" t="s">
         <v>665</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="D7" s="24" t="s">
         <v>666</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>667</v>
-      </c>
       <c r="E7" s="25" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
+        <v>667</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>668</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="D8" s="24" t="s">
         <v>669</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>670</v>
-      </c>
       <c r="E8" s="25" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="24" t="s">
+        <v>670</v>
+      </c>
+      <c r="C9" s="24" t="s">
         <v>671</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="D9" s="24" t="s">
         <v>672</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>673</v>
-      </c>
       <c r="E9" s="25" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
+        <v>673</v>
+      </c>
+      <c r="C10" s="24" t="s">
         <v>674</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="D10" s="24" t="s">
         <v>675</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>676</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>86</v>
@@ -9841,13 +9816,13 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
+        <v>676</v>
+      </c>
+      <c r="C11" s="24" t="s">
         <v>677</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="D11" s="24" t="s">
         <v>678</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>679</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>86</v>
@@ -9855,13 +9830,13 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
+        <v>679</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>680</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="D12" s="24" t="s">
         <v>681</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>682</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>86</v>
@@ -9913,15 +9888,15 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="26" t="s">
+        <v>683</v>
+      </c>
+      <c r="C4" s="27" t="s">
         <v>684</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9929,23 +9904,23 @@
         <v>29</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="26" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="26" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9953,7 +9928,7 @@
         <v>86</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9961,7 +9936,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9969,15 +9944,15 @@
         <v>22</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="26" t="s">
+        <v>691</v>
+      </c>
+      <c r="C11" s="27" t="s">
         <v>692</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9985,15 +9960,15 @@
         <v>20</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="26" t="s">
+        <v>694</v>
+      </c>
+      <c r="C13" s="27" t="s">
         <v>695</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>696</v>
       </c>
     </row>
   </sheetData>

--- a/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
+++ b/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="704">
   <si>
     <t xml:space="preserve">Nibbl AI — Master Requirements Tracker</t>
   </si>
@@ -770,13 +770,13 @@
     <t xml:space="preserve">Confirm Reservation screen: slot X of 5, exact deadline, Confirm &amp; Reserve (slot consumed only here)</t>
   </si>
   <si>
-    <t xml:space="preserve">Claim reserves directly after the consent step.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim an offer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Separate confirmation screen showing slot use + exact deadline before reserving not built on the website.</t>
+    <t xml:space="preserve">Slot use shown on Reserve Offer; separate Confirm screen with product, retailer, reward, exact deadline and resulting slot use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → offer → Continue → Confirm &amp; Reserve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim an offer; check the deadline is 7 days out.</t>
   </si>
   <si>
     <t xml:space="preserve">#18</t>
@@ -1553,19 +1553,22 @@
     <t xml:space="preserve">Wallet activity with filters (rebates, reviews, referrals, withdrawals) + statuses</t>
   </si>
   <si>
-    <t xml:space="preserve">Activity list.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open activity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter tabs not built.</t>
+    <t xml:space="preserve">New /wallet/activity/: All / Rebates / Reviews / Referrals / Withdrawals tabs, grouped Pending / In progress / Available / Completed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → Wallet → Wallet Activity</t>
   </si>
   <si>
     <t xml:space="preserve">Reward details (timeline: submitted → under review → available)</t>
   </si>
   <si>
-    <t xml:space="preserve">Not built on the website.</t>
+    <t xml:space="preserve">Reward Details pop-up with timeline, reward type, campaign, receipt date, reference.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → Wallet → tap an item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a pending rebate.</t>
   </si>
   <si>
     <t xml:space="preserve">Payout methods: one PayPal/Venmo identity per account; locked; change via request</t>
@@ -1583,7 +1586,7 @@
     <t xml:space="preserve">Amount → locked method → SMS code → confirm (checkbox) → requested status tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Amount, method, SMS code, submit.</t>
+    <t xml:space="preserve">All five steps incl. any amount, locked method + Request a change, SMS, confirm checkbox, Requested / Processing / Paid tracker.</t>
   </si>
   <si>
     <t xml:space="preserve">Website → Wallet → Withdraw</t>
@@ -1592,31 +1595,34 @@
     <t xml:space="preserve">Withdraw a small amount.</t>
   </si>
   <si>
-    <t xml:space="preserve">Twilio approved — retest SMS. Confirm-step checkbox and Requested/Processing/Paid tracker not built.</t>
+    <t xml:space="preserve">Twilio approved — retest the SMS step on production, then Completed.</t>
   </si>
   <si>
     <t xml:space="preserve">'Additional review needed' popup; status stays Processing</t>
   </si>
   <si>
-    <t xml:space="preserve">Review routing in Admin.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger a review rule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper popup not built.</t>
+    <t xml:space="preserve">Pop-up with Got it; request shows Processing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → Wallet → Withdraw over the review threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Withdraw above $25.</t>
   </si>
   <si>
     <t xml:space="preserve">Withdrawal failed / rejected balance handling</t>
   </si>
   <si>
-    <t xml:space="preserve">Rejected returns the amount (hold released).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reject a withdrawal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Failed (retryable vs permanent) handling waits on PayPal results import.</t>
+    <t xml:space="preserve">Rejected: full amount back to the balance with the reason. Failed (from PayPal results): retryable stays reserved (Retry), permanent returns the amount (Return to balance).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper Website + Admin Dashboard + Backend / API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → Wallet Activity; Admin → Withdrawals → Failed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Import a FAILED result, then Return to balance.</t>
   </si>
   <si>
     <t xml:space="preserve">#43</t>
@@ -1715,7 +1721,7 @@
     <t xml:space="preserve">Change date range.</t>
   </si>
   <si>
-    <t xml:space="preserve">Brand category filter (brands have no category); failed payouts wait on results import.</t>
+    <t xml:space="preserve">Brand category filter (brands have no category). Failed payouts count is now live.</t>
   </si>
   <si>
     <t xml:space="preserve">#42</t>
@@ -1727,37 +1733,55 @@
     <t xml:space="preserve">Tabs: Ready for Batch, Manual Review, Processing, Completed, Failed; batch summary (PayPal fees)</t>
   </si>
   <si>
-    <t xml:space="preserve">Batches, approve/reject, manual review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Withdraw Request / Payout Reviews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a batch.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab set and batch-cost summary per mockup; no Failed tab.</t>
+    <t xml:space="preserve">All five tabs with counts; safe requests enter Ready for Batch automatically; live batch summary (count, payouts, est. PayPal fees, total).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Withdrawals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select requests; watch the summary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PayPal fee estimate = $0.25 per payout (configurable on the server).</t>
   </si>
   <si>
     <t xml:space="preserve">Create batch, download PayPal file</t>
   </si>
   <si>
-    <t xml:space="preserve">Admin → Withdraw Request</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Download a batch file.</t>
+    <t xml:space="preserve">Create Batch from selected requests downloads the PayPal Payouts CSV (Reference ID = Withdrawal ID); past batches can be downloaded again; an exported request can't join a second batch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Withdrawals → Create Batch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a batch; upload the file to PayPal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the file against PayPal's current Payouts template on first use.</t>
   </si>
   <si>
     <t xml:space="preserve">Import PayPal results (Paid / Failed, partial success, idempotent, match by Withdrawal ID)</t>
   </si>
   <si>
+    <t xml:space="preserve">Import PayPal Results: matches Reference ID; SUCCESS → Paid, failures → Failed (retryable or permanent); partial success; re-import changes nothing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Withdrawals → Import PayPal Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Import a results CSV twice.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Manual review: flag reason + history; approve / reject with customer-facing reason; audit</t>
   </si>
   <si>
-    <t xml:space="preserve">Admin → Payout Reviews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approve a flagged request.</t>
+    <t xml:space="preserve">Manual Review panel: flag reason, shopper history, Approve (→ Ready for Batch) / Reject with required reason; every decision audit-logged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Withdrawals → Manual Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approve and reject a flagged request.</t>
   </si>
   <si>
     <t xml:space="preserve">#43, #51</t>
@@ -2973,11 +2997,11 @@
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Completed")</f>
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Progress")</f>
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Review")</f>
@@ -2985,11 +3009,11 @@
       </c>
       <c r="G5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Planned")</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H5" s="5" t="n">
         <f aca="false">IF(C5&gt;0,D5/C5,0)</f>
-        <v>0.613333333333333</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4733,7 +4757,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="9" t="n">
         <v>50</v>
       </c>
@@ -4747,23 +4771,21 @@
         <v>247</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>208</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="K58" s="10" t="s">
         <v>249</v>
       </c>
+      <c r="K58" s="10"/>
       <c r="L58" s="12"/>
       <c r="M58" s="13" t="s">
         <v>250</v>
@@ -7103,7 +7125,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B126" s="9" t="n">
         <v>118</v>
       </c>
@@ -7117,23 +7139,21 @@
         <v>508</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G126" s="10" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="H126" s="10" t="s">
         <v>208</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>509</v>
-      </c>
-      <c r="K126" s="10" t="s">
-        <v>510</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="K126" s="10"/>
       <c r="L126" s="12"/>
       <c r="M126" s="13" t="s">
         <v>506</v>
@@ -7147,29 +7167,27 @@
         <v>503</v>
       </c>
       <c r="D127" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="E127" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="E127" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="F127" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="H127" s="10" t="s">
         <v>208</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>31</v>
+        <v>512</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K127" s="10" t="s">
-        <v>512</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="K127" s="10"/>
       <c r="L127" s="12"/>
       <c r="M127" s="13" t="s">
         <v>506</v>
@@ -7183,7 +7201,7 @@
         <v>503</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>59</v>
@@ -7201,26 +7219,26 @@
         <v>505</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K128" s="10"/>
       <c r="L128" s="12"/>
       <c r="M128" s="13" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B129" s="9" t="n">
         <v>121</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F129" s="11" t="s">
         <v>72</v>
@@ -7232,13 +7250,13 @@
         <v>208</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K129" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L129" s="12"/>
       <c r="M129" s="13" t="s">
@@ -7250,16 +7268,16 @@
         <v>122</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G130" s="10" t="s">
         <v>236</v>
@@ -7268,53 +7286,49 @@
         <v>208</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>524</v>
-      </c>
-      <c r="K130" s="10" t="s">
-        <v>525</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="K130" s="10"/>
       <c r="L130" s="12"/>
       <c r="M130" s="13" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B131" s="9" t="n">
         <v>123</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>175</v>
+        <v>529</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>31</v>
+        <v>208</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>176</v>
+        <v>530</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>528</v>
-      </c>
-      <c r="K131" s="10" t="s">
-        <v>529</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="K131" s="10"/>
       <c r="L131" s="12"/>
       <c r="M131" s="13" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7322,13 +7336,13 @@
         <v>124</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F132" s="11" t="s">
         <v>72</v>
@@ -7343,14 +7357,14 @@
         <v>256</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K132" s="10" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L132" s="12"/>
       <c r="M132" s="13" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7358,13 +7372,13 @@
         <v>125</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F133" s="11" t="s">
         <v>72</v>
@@ -7382,11 +7396,11 @@
         <v>446</v>
       </c>
       <c r="K133" s="10" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="L133" s="12"/>
       <c r="M133" s="13" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7394,13 +7408,13 @@
         <v>126</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F134" s="11" t="s">
         <v>72</v>
@@ -7415,14 +7429,14 @@
         <v>256</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="K134" s="10" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="L134" s="12"/>
       <c r="M134" s="13" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7430,10 +7444,10 @@
         <v>127</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>59</v>
@@ -7451,12 +7465,12 @@
         <v>505</v>
       </c>
       <c r="J135" s="10" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="K135" s="10"/>
       <c r="L135" s="12"/>
       <c r="M135" s="13" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7464,13 +7478,13 @@
         <v>128</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F136" s="11" t="s">
         <v>86</v>
@@ -7488,7 +7502,7 @@
         <v>31</v>
       </c>
       <c r="K136" s="10" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L136" s="12"/>
       <c r="M136" s="13" t="s">
@@ -7500,13 +7514,13 @@
         <v>129</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F137" s="11" t="s">
         <v>72</v>
@@ -7518,13 +7532,13 @@
         <v>208</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K137" s="10" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L137" s="12"/>
       <c r="M137" s="13" t="s">
@@ -7536,122 +7550,124 @@
         <v>130</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F138" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G138" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H138" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I138" s="10" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="J138" s="10" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="K138" s="10" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L138" s="12"/>
       <c r="M138" s="13" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B139" s="9" t="n">
         <v>131</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F139" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>559</v>
+        <v>202</v>
       </c>
       <c r="H139" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="K139" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="L139" s="12"/>
       <c r="M139" s="13" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B140" s="9" t="n">
         <v>132</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>59</v>
+        <v>573</v>
       </c>
       <c r="F140" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G140" s="10" t="s">
-        <v>559</v>
+        <v>202</v>
       </c>
       <c r="H140" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I140" s="10" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="J140" s="10" t="s">
-        <v>572</v>
-      </c>
-      <c r="K140" s="10"/>
+        <v>575</v>
+      </c>
+      <c r="K140" s="10" t="s">
+        <v>576</v>
+      </c>
       <c r="L140" s="12"/>
       <c r="M140" s="13" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B141" s="9" t="n">
         <v>133</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>31</v>
+        <v>578</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G141" s="10" t="s">
         <v>202</v>
@@ -7660,51 +7676,49 @@
         <v>31</v>
       </c>
       <c r="I141" s="10" t="s">
-        <v>31</v>
+        <v>579</v>
       </c>
       <c r="J141" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K141" s="10" t="s">
-        <v>358</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="K141" s="10"/>
       <c r="L141" s="12"/>
       <c r="M141" s="13" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B142" s="9" t="n">
         <v>134</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>59</v>
+        <v>582</v>
       </c>
       <c r="F142" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G142" s="10" t="s">
-        <v>559</v>
+        <v>202</v>
       </c>
       <c r="H142" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I142" s="10" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="K142" s="10"/>
       <c r="L142" s="12"/>
       <c r="M142" s="13" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7712,35 +7726,35 @@
         <v>135</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="F143" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I143" s="10" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="K143" s="10" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="L143" s="12"/>
       <c r="M143" s="13" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7748,35 +7762,35 @@
         <v>136</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="F144" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G144" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H144" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I144" s="10" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="J144" s="10" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="K144" s="10" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="L144" s="12"/>
       <c r="M144" s="13" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7784,10 +7798,10 @@
         <v>137</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>59</v>
@@ -7796,21 +7810,21 @@
         <v>29</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I145" s="10" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="J145" s="10" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="K145" s="10"/>
       <c r="L145" s="12"/>
       <c r="M145" s="13" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7818,10 +7832,10 @@
         <v>138</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="E146" s="10" t="s">
         <v>59</v>
@@ -7830,21 +7844,21 @@
         <v>29</v>
       </c>
       <c r="G146" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H146" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="J146" s="10" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="K146" s="10"/>
       <c r="L146" s="12"/>
       <c r="M146" s="13" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7852,31 +7866,31 @@
         <v>139</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F147" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H147" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I147" s="10" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="J147" s="10" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="K147" s="10" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="L147" s="12"/>
       <c r="M147" s="13" t="s">
@@ -7888,35 +7902,35 @@
         <v>140</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="F148" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H148" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I148" s="10" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="J148" s="10" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="K148" s="10" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="L148" s="12"/>
       <c r="M148" s="13" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7924,19 +7938,19 @@
         <v>141</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="F149" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>31</v>
@@ -7948,7 +7962,7 @@
         <v>31</v>
       </c>
       <c r="K149" s="10" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="L149" s="12"/>
       <c r="M149" s="13" t="s">
@@ -7960,10 +7974,10 @@
         <v>142</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>59</v>
@@ -7972,21 +7986,21 @@
         <v>29</v>
       </c>
       <c r="G150" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H150" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I150" s="10" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="J150" s="10" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="K150" s="10"/>
       <c r="L150" s="12"/>
       <c r="M150" s="13" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7994,35 +8008,35 @@
         <v>143</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="F151" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H151" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I151" s="10" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="J151" s="10" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="K151" s="10" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="L151" s="12"/>
       <c r="M151" s="13" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8030,10 +8044,10 @@
         <v>144</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>59</v>
@@ -8042,23 +8056,23 @@
         <v>29</v>
       </c>
       <c r="G152" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H152" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I152" s="10" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="J152" s="10" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="K152" s="10" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="L152" s="12"/>
       <c r="M152" s="13" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8066,10 +8080,10 @@
         <v>145</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>59</v>
@@ -8078,7 +8092,7 @@
         <v>29</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H153" s="10" t="s">
         <v>31</v>
@@ -8087,12 +8101,12 @@
         <v>217</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="K153" s="10"/>
       <c r="L153" s="12"/>
       <c r="M153" s="13" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8100,13 +8114,13 @@
         <v>146</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="E154" s="10" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="F154" s="11" t="s">
         <v>72</v>
@@ -8121,14 +8135,14 @@
         <v>217</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="K154" s="10" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="L154" s="12"/>
       <c r="M154" s="13" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8136,10 +8150,10 @@
         <v>147</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>31</v>
@@ -8148,7 +8162,7 @@
         <v>86</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H155" s="10" t="s">
         <v>31</v>
@@ -8164,7 +8178,7 @@
       </c>
       <c r="L155" s="12"/>
       <c r="M155" s="13" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8172,10 +8186,10 @@
         <v>148</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="E156" s="10" t="s">
         <v>59</v>
@@ -8190,17 +8204,17 @@
         <v>208</v>
       </c>
       <c r="I156" s="10" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="J156" s="10" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="K156" s="10" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="L156" s="12"/>
       <c r="M156" s="13" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8208,10 +8222,10 @@
         <v>149</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>31</v>
@@ -8244,13 +8258,13 @@
         <v>150</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="E158" s="10" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="F158" s="11" t="s">
         <v>86</v>
@@ -8268,7 +8282,7 @@
         <v>31</v>
       </c>
       <c r="K158" s="10" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="L158" s="12"/>
       <c r="M158" s="13" t="s">
@@ -8325,7 +8339,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8333,7 +8347,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>29</v>
@@ -8348,7 +8362,7 @@
         <v>86</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8593,11 +8607,11 @@
       </c>
       <c r="D13" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B13,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B13,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B13,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -8609,7 +8623,7 @@
       </c>
       <c r="H13" s="19" t="n">
         <f aca="false">IF(C13&gt;0,D13/C13,0)</f>
-        <v>0.571428571428571</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9173,11 +9187,11 @@
       </c>
       <c r="D33" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B33,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B33,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B33,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9185,16 +9199,16 @@
       </c>
       <c r="G33" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B33,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="19" t="n">
         <f aca="false">IF(C33&gt;0,D33/C33,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="17" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C34" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B34)</f>
@@ -9202,11 +9216,11 @@
       </c>
       <c r="D34" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B34,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B34,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B34,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9218,12 +9232,12 @@
       </c>
       <c r="H34" s="19" t="n">
         <f aca="false">IF(C34&gt;0,D34/C34,0)</f>
-        <v>0</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="17" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C35" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B35)</f>
@@ -9252,7 +9266,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="17" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C36" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B36)</f>
@@ -9281,7 +9295,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="17" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C37" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B37)</f>
@@ -9310,7 +9324,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="17" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C38" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B38)</f>
@@ -9339,7 +9353,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="17" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C39" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B39)</f>
@@ -9347,11 +9361,11 @@
       </c>
       <c r="D39" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B39,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E39" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B39,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B39,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9359,16 +9373,16 @@
       </c>
       <c r="G39" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B39,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="19" t="n">
         <f aca="false">IF(C39&gt;0,D39/C39,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="17" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="C40" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B40)</f>
@@ -9397,7 +9411,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="17" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="C41" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B41)</f>
@@ -9426,7 +9440,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="17" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="C42" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B42)</f>
@@ -9455,7 +9469,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="17" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="C43" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B43)</f>
@@ -9484,7 +9498,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="17" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="C44" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B44)</f>
@@ -9513,7 +9527,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="17" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="C45" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B45)</f>
@@ -9542,7 +9556,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="17" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C46" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B46)</f>
@@ -9571,7 +9585,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="17" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="C47" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B47)</f>
@@ -9600,7 +9614,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="17" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="C48" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B48)</f>
@@ -9629,7 +9643,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="17" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="C49" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B49)</f>
@@ -9658,7 +9672,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="20" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="C50" s="21" t="n">
         <f aca="false">SUM(C5:C49)</f>
@@ -9666,11 +9680,11 @@
       </c>
       <c r="D50" s="21" t="n">
         <f aca="false">SUM(D5:D49)</f>
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">SUM(E5:E49)</f>
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F50" s="21" t="n">
         <f aca="false">SUM(F5:F49)</f>
@@ -9678,11 +9692,11 @@
       </c>
       <c r="G50" s="21" t="n">
         <f aca="false">SUM(G5:G49)</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H50" s="22" t="n">
         <f aca="false">IF(C50&gt;0,D50/C50,0)</f>
-        <v>0.613333333333333</v>
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>
@@ -9713,18 +9727,18 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="23" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>18</v>
@@ -9732,13 +9746,13 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>72</v>
@@ -9746,13 +9760,13 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="24" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>72</v>
@@ -9760,13 +9774,13 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="24" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>72</v>
@@ -9774,13 +9788,13 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>295</v>
@@ -9788,13 +9802,13 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="24" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>72</v>
@@ -9802,13 +9816,13 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>86</v>
@@ -9816,13 +9830,13 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>86</v>
@@ -9830,13 +9844,13 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>86</v>
@@ -9888,15 +9902,15 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="26" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9904,7 +9918,7 @@
         <v>29</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9912,7 +9926,7 @@
         <v>72</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9920,7 +9934,7 @@
         <v>295</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9928,7 +9942,7 @@
         <v>86</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9936,7 +9950,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9944,15 +9958,15 @@
         <v>22</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="26" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9960,15 +9974,15 @@
         <v>20</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="26" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>

--- a/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
+++ b/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="704">
   <si>
     <t xml:space="preserve">Nibbl AI — Master Requirements Tracker</t>
   </si>
@@ -1634,13 +1634,13 @@
     <t xml:space="preserve">Referral home, share link, share a product deal</t>
   </si>
   <si>
-    <t xml:space="preserve">Website invite card + Share this deal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copy the link.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master link format is joinnibbl.com/r/CODE (we use ?ref=).</t>
+    <t xml:space="preserve">Code + copy, share sheet with joinnibbl.com/r/CODE, Share a product list (deal links carry the code), How it works.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → My Rewards → Refer a Friend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share the link; open it signed out.</t>
   </si>
   <si>
     <t xml:space="preserve">#40</t>
@@ -1649,22 +1649,22 @@
     <t xml:space="preserve">Qualification: join, claim, approved redemption, payout method, withdrawal — within 90 days</t>
   </si>
   <si>
-    <t xml:space="preserve">5-step qualification + review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90-day completion window / expiry not built.</t>
+    <t xml:space="preserve">5-step qualification; only steps inside the 90-day window count; unfinished referrals expire (checked every 15 minutes).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend; Admin → Referrals → Expired</t>
   </si>
   <si>
     <t xml:space="preserve">Referral progress (earned, pending, invited; step X of 4; expires in N days; not eligible) + rules sheet</t>
   </si>
   <si>
-    <t xml:space="preserve">Per-friend 5-step progress.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check a referral.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Totals, expiry countdown, 'not eligible' and rules sheet per mockup.</t>
+    <t xml:space="preserve">Earned / Pending / Invited totals, per-friend Step X of 4 + next step, Expires in N days, Earned / Not eligible, Referral Rules sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → My Rewards → My referrals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check a friend's progress.</t>
   </si>
   <si>
     <t xml:space="preserve">Shopper Restriction Messages</t>
@@ -2997,11 +2997,11 @@
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Completed")</f>
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Progress")</f>
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Review")</f>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="H5" s="5" t="n">
         <f aca="false">IF(C5&gt;0,D5/C5,0)</f>
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7331,7 +7331,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B132" s="9" t="n">
         <v>124</v>
       </c>
@@ -7345,7 +7345,7 @@
         <v>535</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G132" s="10" t="s">
         <v>207</v>
@@ -7354,20 +7354,18 @@
         <v>208</v>
       </c>
       <c r="I132" s="10" t="s">
-        <v>256</v>
+        <v>536</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>536</v>
-      </c>
-      <c r="K132" s="10" t="s">
         <v>537</v>
       </c>
+      <c r="K132" s="10"/>
       <c r="L132" s="12"/>
       <c r="M132" s="13" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B133" s="9" t="n">
         <v>125</v>
       </c>
@@ -7381,29 +7379,27 @@
         <v>540</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="H133" s="10" t="s">
         <v>208</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>176</v>
+        <v>541</v>
       </c>
       <c r="J133" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="K133" s="10" t="s">
-        <v>541</v>
-      </c>
+      <c r="K133" s="10"/>
       <c r="L133" s="12"/>
       <c r="M133" s="13" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B134" s="9" t="n">
         <v>126</v>
       </c>
@@ -7417,23 +7413,21 @@
         <v>543</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G134" s="10" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="H134" s="10" t="s">
         <v>208</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>256</v>
+        <v>544</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>544</v>
-      </c>
-      <c r="K134" s="10" t="s">
         <v>545</v>
       </c>
+      <c r="K134" s="10"/>
       <c r="L134" s="12"/>
       <c r="M134" s="13" t="s">
         <v>538</v>
@@ -9245,11 +9239,11 @@
       </c>
       <c r="D35" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B35,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E35" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B35,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F35" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B35,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9261,7 +9255,7 @@
       </c>
       <c r="H35" s="19" t="n">
         <f aca="false">IF(C35&gt;0,D35/C35,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9680,11 +9674,11 @@
       </c>
       <c r="D50" s="21" t="n">
         <f aca="false">SUM(D5:D49)</f>
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">SUM(E5:E49)</f>
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F50" s="21" t="n">
         <f aca="false">SUM(F5:F49)</f>
@@ -9696,7 +9690,7 @@
       </c>
       <c r="H50" s="22" t="n">
         <f aca="false">IF(C50&gt;0,D50/C50,0)</f>
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
     </row>
   </sheetData>

--- a/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
+++ b/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="710">
   <si>
     <t xml:space="preserve">Nibbl AI — Master Requirements Tracker</t>
   </si>
@@ -830,16 +830,13 @@
     <t xml:space="preserve">Submit inside the active campaign: requirements list, take/choose photo, review before submit, submitted state</t>
   </si>
   <si>
-    <t xml:space="preserve">Upload from My Rewards.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → My Rewards → Upload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload a receipt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipt requirements screen, review-before-submit and 'Receipt submitted' state not built on the website.</t>
+    <t xml:space="preserve">Per-claim flow: Receipt Requirements (from the claim's locked terms), Take / Choose Photo, Review Your Receipt, Receipt submitted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → My Rewards → Upload receipt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload a receipt for a claim.</t>
   </si>
   <si>
     <t xml:space="preserve">#19</t>
@@ -872,19 +869,25 @@
     <t xml:space="preserve">One resubmission before the original deadline (deadline never restarts)</t>
   </si>
   <si>
-    <t xml:space="preserve">Resubmission after a first date/retailer rejection not built.</t>
+    <t xml:space="preserve">First clear date/retailer rejection keeps the claim open with one resubmission; the second is final (claim closed, slot released). Purchase must be on or after the claim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload a receipt dated before the claim, then another.</t>
   </si>
   <si>
     <t xml:space="preserve">Outcome messages: accepted, manual review, unreadable, date, retailer, final rejection</t>
   </si>
   <si>
-    <t xml:space="preserve">Status + reason shown in receipt history.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check each outcome.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dedicated outcome screens per the mockup not built.</t>
+    <t xml:space="preserve">Master outcome screens: Purchase verified, Manual review, We couldn't read it, Date / Retailer does not qualify (with one resubmission), Final rejection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → after submitting a receipt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger each outcome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-app + email decision notifications are tracked in Notifications &amp; Reminders.</t>
   </si>
   <si>
     <t xml:space="preserve">Notifications &amp; Reminders</t>
@@ -905,7 +908,13 @@
     <t xml:space="preserve">Reservation confirmation, receipt submitted, approval/rejection (in-app + email), claim expiration</t>
   </si>
   <si>
-    <t xml:space="preserve">These shopper notifications aren't sent yet.</t>
+    <t xml:space="preserve">All five sent immediately in-app; approval and rejection also emailed (SES).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → notifications; email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim, upload, get approved/rejected, let a claim expire.</t>
   </si>
   <si>
     <t xml:space="preserve">Push notification delivery (FCM / APNs)</t>
@@ -1400,16 +1409,16 @@
     <t xml:space="preserve">Notifications per member (Email + SMS): wallet below 25%, auto-refill failed, campaign paused, exhausted early, new negative review, weekly summary</t>
   </si>
   <si>
-    <t xml:space="preserve">Per-member toggles for campaign approvals, receipts to review, low-rating reviews, refill failed.</t>
+    <t xml:space="preserve">Master's six notifications (+ campaign approvals, receipts to review) all sent in-app + email per member preference.</t>
   </si>
   <si>
     <t xml:space="preserve">Settings → Notifications</t>
   </si>
   <si>
-    <t xml:space="preserve">Toggle and trigger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align the list with the Master (add wallet below 25%, campaign paused, exhausted early, weekly summary). SMS sending waits on Klaviyo.</t>
+    <t xml:space="preserve">Toggle and trigger each.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS toggles are stored; SMS sending waits on Klaviyo.</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking &amp; Attribution (Meta Pixel; Google/TikTok Coming Soon)</t>
@@ -1424,7 +1433,7 @@
     <t xml:space="preserve">Security: passwordless sign-in, active sessions, last sign-in, sign out others</t>
   </si>
   <si>
-    <t xml:space="preserve">Sessions + sign out others + last sign-in.</t>
+    <t xml:space="preserve">Passwordless (magic-link) sign-in active, sessions, last sign-in, sign out others.</t>
   </si>
   <si>
     <t xml:space="preserve">Settings → Security</t>
@@ -1433,9 +1442,6 @@
     <t xml:space="preserve">Sign out another device.</t>
   </si>
   <si>
-    <t xml:space="preserve">Passwordless (magic-link) sign-in not built — brands use a password.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Account &amp; Support (Contact Nibbl Support, Owner-only closure, Klaviyo Coming Soon — Scale)</t>
   </si>
   <si>
@@ -1460,22 +1466,28 @@
     <t xml:space="preserve">Role gate (I'm a Brand / I'm a Shopper)</t>
   </si>
   <si>
+    <t xml:space="preserve">What brings you to Nibbl? — Explore Nibbl for Brands / View Deals; choice remembered on the device.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brand.joinnibbl.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">#38</t>
   </si>
   <si>
     <t xml:space="preserve">Public brand homepage + How it works / Reviews / Controls / Plans</t>
   </si>
   <si>
-    <t xml:space="preserve">Brand landing page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open the landing page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align sections and plan cards with the Master mockups.</t>
+    <t xml:space="preserve">Master homepage: hero, Why Nibbl, How it works, Reviews, Controls, Plans ($39/$199/$999), promo note.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brand.joinnibbl.com/brand-landing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Browse the page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ entries are labels until FAQ pages exist.</t>
   </si>
   <si>
     <t xml:space="preserve">Plan → Create Account (contact, work email, phone, company, website, category, terms)</t>
@@ -1493,49 +1505,52 @@
     <t xml:space="preserve">Passwordless magic-link sign-in (link expires in 15 minutes)</t>
   </si>
   <si>
-    <t xml:space="preserve">Secure one-time verification link (24 h) + password.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Register → email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open the emailed link.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master uses magic-link sign-in without a password, 15-minute link.</t>
+    <t xml:space="preserve">Signup without a password (Send Magic Link); 15-minute one-time link signs you straight in; Sign In emails a sign-in link (password still available).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brand.joinnibbl.com → Register / Sign In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register, open the email link; sign in by link.</t>
   </si>
   <si>
     <t xml:space="preserve">Secure checkout: card required even when credits cover today; card saved for renewals; promo code</t>
   </si>
   <si>
-    <t xml:space="preserve">Card payment + promo code; activates on payment.</t>
+    <t xml:space="preserve">Card always required ($0 due saves it with a SetupIntent); card saved to the brand for renewals and auto-replenishment; promo code.</t>
   </si>
   <si>
     <t xml:space="preserve">After sign-up → Checkout</t>
   </si>
   <si>
-    <t xml:space="preserve">Pay with a test card.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card must be required even at $0 due and saved for renewals. Retest on Stripe live keys.</t>
+    <t xml:space="preserve">Check out with a promo covering the plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retest after the Stripe live switch.</t>
   </si>
   <si>
     <t xml:space="preserve">Account Activated page + First Dashboard (3 growth goals, 5 steps)</t>
   </si>
   <si>
-    <t xml:space="preserve">Get-ready checklist with 2 goals.</t>
+    <t xml:space="preserve">Welcome to Nibbl page (plan, slots, credits, card, growth toolkit, getting started) + 3 growth goals and the 5 launch steps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dashboard after checkout</t>
   </si>
   <si>
     <t xml:space="preserve">Finish checkout.</t>
   </si>
   <si>
-    <t xml:space="preserve">Add the activation page and the 3rd goal (Reconnect &amp; Build Loyalty).</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wallet funding required before launch (7-day need + auto-replenishment)</t>
   </si>
   <si>
-    <t xml:space="preserve">Launch gate not built.</t>
+    <t xml:space="preserve">Submit is blocked until the Wallet covers the 7-day requirement and auto-replenishment is on; 'Fund your campaign before launch' pop-up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebate campaign → Submit for review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit with an empty wallet.</t>
   </si>
   <si>
     <t xml:space="preserve">Shopper Wallet</t>
@@ -2000,10 +2015,13 @@
     <t xml:space="preserve">System email via AWS SES with bounce / complaint handling</t>
   </si>
   <si>
-    <t xml:space="preserve">Email sent via Gmail SMTP today.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switch to SES (client set it up).</t>
+    <t xml:space="preserve">All system email now goes through Amazon SES as Nibbl &lt;no-reply@joinnibbl.com&gt; (DKIM-signed domain, production access); bounces and complaints go to the SES suppression list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any emailed code or notification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request an email code; check the sender.</t>
   </si>
   <si>
     <t xml:space="preserve">Progress by Master Document Section</t>
@@ -2078,7 +2096,7 @@
     <t xml:space="preserve">System email from @joinnibbl.com + bounce/complaint handling</t>
   </si>
   <si>
-    <t xml:space="preserve">SES in sandbox until AWS approval</t>
+    <t xml:space="preserve">Done — production email switched to SES on 11 Oct 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Client — Firebase</t>
@@ -2997,11 +3015,11 @@
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Completed")</f>
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Progress")</f>
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Review")</f>
@@ -3009,11 +3027,11 @@
       </c>
       <c r="G5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Planned")</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H5" s="5" t="n">
         <f aca="false">IF(C5&gt;0,D5/C5,0)</f>
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4941,10 +4959,10 @@
         <v>267</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="H63" s="10" t="s">
         <v>208</v>
@@ -4955,12 +4973,10 @@
       <c r="J63" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="K63" s="10" t="s">
-        <v>270</v>
-      </c>
+      <c r="K63" s="10"/>
       <c r="L63" s="12"/>
       <c r="M63" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4968,10 +4984,10 @@
         <v>56</v>
       </c>
       <c r="C64" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="D64" s="10" t="s">
         <v>272</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>273</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>59</v>
@@ -4989,14 +5005,14 @@
         <v>176</v>
       </c>
       <c r="J64" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="K64" s="10" t="s">
         <v>274</v>
-      </c>
-      <c r="K64" s="10" t="s">
-        <v>275</v>
       </c>
       <c r="L64" s="12"/>
       <c r="M64" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5004,10 +5020,10 @@
         <v>57</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>59</v>
@@ -5025,29 +5041,29 @@
         <v>176</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K65" s="10"/>
       <c r="L65" s="12"/>
       <c r="M65" s="13" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="9" t="n">
         <v>58</v>
       </c>
       <c r="C66" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D66" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="E66" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="E66" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="F66" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>181</v>
@@ -5056,25 +5072,23 @@
         <v>208</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>31</v>
+        <v>268</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K66" s="10" t="s">
         <v>281</v>
       </c>
+      <c r="K66" s="10"/>
       <c r="L66" s="12"/>
       <c r="M66" s="13" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="9" t="n">
         <v>59</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>282</v>
@@ -5083,26 +5097,26 @@
         <v>283</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="H67" s="10" t="s">
         <v>208</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="J67" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K67" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L67" s="12"/>
       <c r="M67" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5110,10 +5124,10 @@
         <v>60</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>59</v>
@@ -5128,15 +5142,15 @@
         <v>208</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K68" s="10"/>
       <c r="L68" s="12"/>
       <c r="M68" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5144,35 +5158,33 @@
         <v>61</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>31</v>
+        <v>293</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H69" s="10" t="s">
         <v>208</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>31</v>
+        <v>294</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K69" s="10" t="s">
-        <v>292</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="K69" s="10"/>
       <c r="L69" s="12"/>
       <c r="M69" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5180,16 +5192,16 @@
         <v>62</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G70" s="10" t="s">
         <v>175</v>
@@ -5204,7 +5216,7 @@
         <v>31</v>
       </c>
       <c r="K70" s="10" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="L70" s="12"/>
       <c r="M70" s="13" t="s">
@@ -5216,10 +5228,10 @@
         <v>63</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>59</v>
@@ -5234,15 +5246,15 @@
         <v>31</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="J71" s="10" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="K71" s="10"/>
       <c r="L71" s="12"/>
       <c r="M71" s="13" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5250,10 +5262,10 @@
         <v>64</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>59</v>
@@ -5268,15 +5280,15 @@
         <v>31</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K72" s="10"/>
       <c r="L72" s="12"/>
       <c r="M72" s="13" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5284,10 +5296,10 @@
         <v>65</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>59</v>
@@ -5302,7 +5314,7 @@
         <v>31</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="J73" s="10" t="s">
         <v>115</v>
@@ -5310,7 +5322,7 @@
       <c r="K73" s="10"/>
       <c r="L73" s="12"/>
       <c r="M73" s="13" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5318,13 +5330,13 @@
         <v>66</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>29</v>
@@ -5336,15 +5348,15 @@
         <v>31</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K74" s="10"/>
       <c r="L74" s="12"/>
       <c r="M74" s="13" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5352,10 +5364,10 @@
         <v>67</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>59</v>
@@ -5370,15 +5382,15 @@
         <v>31</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J75" s="10" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="K75" s="10"/>
       <c r="L75" s="12"/>
       <c r="M75" s="13" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5386,10 +5398,10 @@
         <v>68</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>59</v>
@@ -5404,15 +5416,15 @@
         <v>31</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K76" s="10"/>
       <c r="L76" s="12"/>
       <c r="M76" s="13" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5420,13 +5432,13 @@
         <v>69</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F77" s="11" t="s">
         <v>29</v>
@@ -5438,15 +5450,15 @@
         <v>31</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K77" s="10"/>
       <c r="L77" s="12"/>
       <c r="M77" s="13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5454,13 +5466,13 @@
         <v>70</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>29</v>
@@ -5472,7 +5484,7 @@
         <v>31</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J78" s="10" t="s">
         <v>115</v>
@@ -5480,7 +5492,7 @@
       <c r="K78" s="10"/>
       <c r="L78" s="12"/>
       <c r="M78" s="13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5488,13 +5500,13 @@
         <v>71</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F79" s="11" t="s">
         <v>29</v>
@@ -5506,15 +5518,15 @@
         <v>31</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K79" s="10"/>
       <c r="L79" s="12"/>
       <c r="M79" s="13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5522,13 +5534,13 @@
         <v>72</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F80" s="11" t="s">
         <v>29</v>
@@ -5540,15 +5552,15 @@
         <v>31</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K80" s="10"/>
       <c r="L80" s="12"/>
       <c r="M80" s="13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5556,13 +5568,13 @@
         <v>73</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F81" s="11" t="s">
         <v>29</v>
@@ -5574,15 +5586,15 @@
         <v>31</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="K81" s="10"/>
       <c r="L81" s="12"/>
       <c r="M81" s="13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5590,13 +5602,13 @@
         <v>74</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F82" s="11" t="s">
         <v>29</v>
@@ -5608,15 +5620,15 @@
         <v>31</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K82" s="10"/>
       <c r="L82" s="12"/>
       <c r="M82" s="13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5624,13 +5636,13 @@
         <v>75</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F83" s="11" t="s">
         <v>29</v>
@@ -5642,15 +5654,15 @@
         <v>31</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K83" s="10"/>
       <c r="L83" s="12"/>
       <c r="M83" s="13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5658,10 +5670,10 @@
         <v>76</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>59</v>
@@ -5676,15 +5688,15 @@
         <v>31</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="K84" s="10"/>
       <c r="L84" s="12"/>
       <c r="M84" s="13" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5692,13 +5704,13 @@
         <v>77</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F85" s="11" t="s">
         <v>72</v>
@@ -5710,17 +5722,17 @@
         <v>31</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K85" s="10" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L85" s="12"/>
       <c r="M85" s="13" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5728,13 +5740,13 @@
         <v>78</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>86</v>
@@ -5752,11 +5764,11 @@
         <v>31</v>
       </c>
       <c r="K86" s="10" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L86" s="12"/>
       <c r="M86" s="13" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5764,10 +5776,10 @@
         <v>79</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>31</v>
@@ -5788,11 +5800,11 @@
         <v>31</v>
       </c>
       <c r="K87" s="10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L87" s="12"/>
       <c r="M87" s="13" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5800,13 +5812,13 @@
         <v>80</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F88" s="11" t="s">
         <v>29</v>
@@ -5821,12 +5833,12 @@
         <v>256</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K88" s="10"/>
       <c r="L88" s="12"/>
       <c r="M88" s="13" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5834,10 +5846,10 @@
         <v>81</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>31</v>
@@ -5858,11 +5870,11 @@
         <v>31</v>
       </c>
       <c r="K89" s="10" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L89" s="12"/>
       <c r="M89" s="13" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5870,10 +5882,10 @@
         <v>82</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>59</v>
@@ -5896,7 +5908,7 @@
       <c r="K90" s="10"/>
       <c r="L90" s="12"/>
       <c r="M90" s="13" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5904,10 +5916,10 @@
         <v>83</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>59</v>
@@ -5922,15 +5934,15 @@
         <v>208</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K91" s="10"/>
       <c r="L91" s="12"/>
       <c r="M91" s="13" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5938,16 +5950,16 @@
         <v>84</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G92" s="10" t="s">
         <v>175</v>
@@ -5962,11 +5974,11 @@
         <v>31</v>
       </c>
       <c r="K92" s="10" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="L92" s="12"/>
       <c r="M92" s="13" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5974,13 +5986,13 @@
         <v>85</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F93" s="11" t="s">
         <v>72</v>
@@ -5992,17 +6004,17 @@
         <v>208</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K93" s="10" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L93" s="12"/>
       <c r="M93" s="13" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6010,10 +6022,10 @@
         <v>86</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>59</v>
@@ -6028,15 +6040,15 @@
         <v>208</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K94" s="10"/>
       <c r="L94" s="12"/>
       <c r="M94" s="13" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6044,13 +6056,13 @@
         <v>87</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F95" s="11" t="s">
         <v>72</v>
@@ -6062,17 +6074,17 @@
         <v>208</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K95" s="10" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="L95" s="12"/>
       <c r="M95" s="13" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6080,10 +6092,10 @@
         <v>88</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>59</v>
@@ -6098,15 +6110,15 @@
         <v>31</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="K96" s="10"/>
       <c r="L96" s="12"/>
       <c r="M96" s="13" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6114,10 +6126,10 @@
         <v>89</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>59</v>
@@ -6132,15 +6144,15 @@
         <v>31</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K97" s="10"/>
       <c r="L97" s="12"/>
       <c r="M97" s="13" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6148,13 +6160,13 @@
         <v>90</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F98" s="11" t="s">
         <v>72</v>
@@ -6166,17 +6178,17 @@
         <v>31</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K98" s="10" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L98" s="12"/>
       <c r="M98" s="13" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6184,13 +6196,13 @@
         <v>91</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F99" s="11" t="s">
         <v>72</v>
@@ -6202,17 +6214,17 @@
         <v>31</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="K99" s="10" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="L99" s="12"/>
       <c r="M99" s="13" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6220,13 +6232,13 @@
         <v>92</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>72</v>
@@ -6238,17 +6250,17 @@
         <v>31</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="K100" s="10" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="L100" s="12"/>
       <c r="M100" s="13" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6256,10 +6268,10 @@
         <v>93</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>31</v>
@@ -6280,11 +6292,11 @@
         <v>31</v>
       </c>
       <c r="K101" s="10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L101" s="12"/>
       <c r="M101" s="13" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6292,10 +6304,10 @@
         <v>94</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E102" s="10" t="s">
         <v>31</v>
@@ -6316,11 +6328,11 @@
         <v>31</v>
       </c>
       <c r="K102" s="10" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L102" s="12"/>
       <c r="M102" s="13" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6328,10 +6340,10 @@
         <v>95</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>59</v>
@@ -6346,15 +6358,15 @@
         <v>31</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="K103" s="10"/>
       <c r="L103" s="12"/>
       <c r="M103" s="13" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6362,10 +6374,10 @@
         <v>96</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>59</v>
@@ -6380,15 +6392,15 @@
         <v>31</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="J104" s="10" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="K104" s="10"/>
       <c r="L104" s="12"/>
       <c r="M104" s="13" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6396,10 +6408,10 @@
         <v>97</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>59</v>
@@ -6414,17 +6426,17 @@
         <v>31</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="J105" s="10" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K105" s="10" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L105" s="12"/>
       <c r="M105" s="13" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6432,10 +6444,10 @@
         <v>98</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>59</v>
@@ -6450,15 +6462,15 @@
         <v>31</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K106" s="10"/>
       <c r="L106" s="12"/>
       <c r="M106" s="13" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6466,31 +6478,31 @@
         <v>99</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F107" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="H107" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L107" s="12"/>
       <c r="M107" s="13" t="s">
@@ -6502,10 +6514,10 @@
         <v>100</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>59</v>
@@ -6520,15 +6532,15 @@
         <v>31</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K108" s="10"/>
       <c r="L108" s="12"/>
       <c r="M108" s="13" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6536,13 +6548,13 @@
         <v>101</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F109" s="11" t="s">
         <v>29</v>
@@ -6554,10 +6566,10 @@
         <v>31</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K109" s="10"/>
       <c r="L109" s="12"/>
@@ -6570,13 +6582,13 @@
         <v>102</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F110" s="11" t="s">
         <v>29</v>
@@ -6591,12 +6603,12 @@
         <v>176</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="K110" s="10"/>
       <c r="L110" s="12"/>
       <c r="M110" s="13" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6604,10 +6616,10 @@
         <v>103</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>59</v>
@@ -6622,15 +6634,15 @@
         <v>31</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K111" s="10"/>
       <c r="L111" s="12"/>
       <c r="M111" s="13" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6638,10 +6650,10 @@
         <v>104</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>59</v>
@@ -6656,15 +6668,15 @@
         <v>31</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="J112" s="10" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K112" s="10"/>
       <c r="L112" s="12"/>
       <c r="M112" s="13" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6672,13 +6684,13 @@
         <v>105</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F113" s="11" t="s">
         <v>72</v>
@@ -6690,17 +6702,17 @@
         <v>31</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K113" s="10" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L113" s="12"/>
       <c r="M113" s="13" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6708,10 +6720,10 @@
         <v>106</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>59</v>
@@ -6726,10 +6738,10 @@
         <v>31</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K114" s="10"/>
       <c r="L114" s="12"/>
@@ -6742,16 +6754,16 @@
         <v>107</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G115" s="10" t="s">
         <v>51</v>
@@ -6760,17 +6772,15 @@
         <v>31</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="K115" s="10" t="s">
-        <v>468</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="K115" s="10"/>
       <c r="L115" s="12"/>
       <c r="M115" s="13" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6778,10 +6788,10 @@
         <v>108</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>59</v>
@@ -6796,15 +6806,15 @@
         <v>31</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K116" s="10"/>
       <c r="L116" s="12"/>
       <c r="M116" s="13" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6812,10 +6822,10 @@
         <v>109</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>59</v>
@@ -6830,32 +6840,32 @@
         <v>31</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K117" s="10"/>
       <c r="L117" s="12"/>
       <c r="M117" s="13" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B118" s="9" t="n">
         <v>110</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>31</v>
+        <v>479</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G118" s="10" t="s">
         <v>30</v>
@@ -6864,34 +6874,32 @@
         <v>31</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>31</v>
+        <v>480</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K118" s="10" t="s">
-        <v>358</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="K118" s="10"/>
       <c r="L118" s="12"/>
       <c r="M118" s="13" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B119" s="9" t="n">
         <v>111</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G119" s="10" t="s">
         <v>30</v>
@@ -6900,17 +6908,17 @@
         <v>31</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="K119" s="10" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="L119" s="12"/>
       <c r="M119" s="13" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6918,13 +6926,13 @@
         <v>112</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F120" s="11" t="s">
         <v>29</v>
@@ -6936,32 +6944,32 @@
         <v>31</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="K120" s="10"/>
       <c r="L120" s="12"/>
       <c r="M120" s="13" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B121" s="9" t="n">
         <v>113</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G121" s="10" t="s">
         <v>51</v>
@@ -6970,34 +6978,32 @@
         <v>31</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J121" s="10" t="s">
-        <v>490</v>
-      </c>
-      <c r="K121" s="10" t="s">
-        <v>491</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="K121" s="10"/>
       <c r="L121" s="12"/>
       <c r="M121" s="13" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B122" s="9" t="n">
         <v>114</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G122" s="10" t="s">
         <v>51</v>
@@ -7006,34 +7012,34 @@
         <v>31</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="J122" s="10" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K122" s="10" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L122" s="12"/>
       <c r="M122" s="13" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B123" s="9" t="n">
         <v>115</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G123" s="10" t="s">
         <v>30</v>
@@ -7042,34 +7048,32 @@
         <v>31</v>
       </c>
       <c r="I123" s="10" t="s">
-        <v>32</v>
+        <v>502</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="K123" s="10" t="s">
-        <v>500</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="K123" s="10"/>
       <c r="L123" s="12"/>
       <c r="M123" s="13" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B124" s="9" t="n">
         <v>116</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>31</v>
+        <v>505</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G124" s="10" t="s">
         <v>51</v>
@@ -7078,17 +7082,15 @@
         <v>31</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>31</v>
+        <v>506</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K124" s="10" t="s">
-        <v>502</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="K124" s="10"/>
       <c r="L124" s="12"/>
       <c r="M124" s="13" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7096,10 +7098,10 @@
         <v>117</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>59</v>
@@ -7114,15 +7116,15 @@
         <v>208</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="K125" s="10"/>
       <c r="L125" s="12"/>
       <c r="M125" s="13" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7130,13 +7132,13 @@
         <v>118</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="F126" s="11" t="s">
         <v>29</v>
@@ -7148,7 +7150,7 @@
         <v>208</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="J126" s="10" t="s">
         <v>115</v>
@@ -7156,7 +7158,7 @@
       <c r="K126" s="10"/>
       <c r="L126" s="12"/>
       <c r="M126" s="13" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7164,13 +7166,13 @@
         <v>119</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F127" s="11" t="s">
         <v>29</v>
@@ -7182,15 +7184,15 @@
         <v>208</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K127" s="10"/>
       <c r="L127" s="12"/>
       <c r="M127" s="13" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7198,10 +7200,10 @@
         <v>120</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>59</v>
@@ -7216,15 +7218,15 @@
         <v>208</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="K128" s="10"/>
       <c r="L128" s="12"/>
       <c r="M128" s="13" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7232,13 +7234,13 @@
         <v>121</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="F129" s="11" t="s">
         <v>72</v>
@@ -7250,17 +7252,17 @@
         <v>208</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="K129" s="10" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="L129" s="12"/>
       <c r="M129" s="13" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7268,13 +7270,13 @@
         <v>122</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="F130" s="11" t="s">
         <v>29</v>
@@ -7286,15 +7288,15 @@
         <v>208</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="K130" s="10"/>
       <c r="L130" s="12"/>
       <c r="M130" s="13" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7302,33 +7304,33 @@
         <v>123</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="F131" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="H131" s="10" t="s">
         <v>208</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="K131" s="10"/>
       <c r="L131" s="12"/>
       <c r="M131" s="13" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7336,13 +7338,13 @@
         <v>124</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="F132" s="11" t="s">
         <v>29</v>
@@ -7354,15 +7356,15 @@
         <v>208</v>
       </c>
       <c r="I132" s="10" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="K132" s="10"/>
       <c r="L132" s="12"/>
       <c r="M132" s="13" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7370,13 +7372,13 @@
         <v>125</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="F133" s="11" t="s">
         <v>29</v>
@@ -7388,15 +7390,15 @@
         <v>208</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="J133" s="10" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="K133" s="10"/>
       <c r="L133" s="12"/>
       <c r="M133" s="13" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7404,13 +7406,13 @@
         <v>126</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="F134" s="11" t="s">
         <v>29</v>
@@ -7422,15 +7424,15 @@
         <v>208</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="K134" s="10"/>
       <c r="L134" s="12"/>
       <c r="M134" s="13" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7438,10 +7440,10 @@
         <v>127</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>59</v>
@@ -7456,15 +7458,15 @@
         <v>208</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="J135" s="10" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="K135" s="10"/>
       <c r="L135" s="12"/>
       <c r="M135" s="13" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7472,13 +7474,13 @@
         <v>128</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="F136" s="11" t="s">
         <v>86</v>
@@ -7496,7 +7498,7 @@
         <v>31</v>
       </c>
       <c r="K136" s="10" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="L136" s="12"/>
       <c r="M136" s="13" t="s">
@@ -7508,13 +7510,13 @@
         <v>129</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="F137" s="11" t="s">
         <v>72</v>
@@ -7526,17 +7528,17 @@
         <v>208</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K137" s="10" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="L137" s="12"/>
       <c r="M137" s="13" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7544,35 +7546,35 @@
         <v>130</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="F138" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G138" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H138" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I138" s="10" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="J138" s="10" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="K138" s="10" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="L138" s="12"/>
       <c r="M138" s="13" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7580,13 +7582,13 @@
         <v>131</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="F139" s="11" t="s">
         <v>29</v>
@@ -7598,17 +7600,17 @@
         <v>31</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="K139" s="10" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="L139" s="12"/>
       <c r="M139" s="13" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7616,13 +7618,13 @@
         <v>132</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F140" s="11" t="s">
         <v>29</v>
@@ -7634,17 +7636,17 @@
         <v>31</v>
       </c>
       <c r="I140" s="10" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="J140" s="10" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="K140" s="10" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="L140" s="12"/>
       <c r="M140" s="13" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7652,13 +7654,13 @@
         <v>133</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="F141" s="11" t="s">
         <v>29</v>
@@ -7670,15 +7672,15 @@
         <v>31</v>
       </c>
       <c r="I141" s="10" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="J141" s="10" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="K141" s="10"/>
       <c r="L141" s="12"/>
       <c r="M141" s="13" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7686,13 +7688,13 @@
         <v>134</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="F142" s="11" t="s">
         <v>29</v>
@@ -7704,15 +7706,15 @@
         <v>31</v>
       </c>
       <c r="I142" s="10" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="K142" s="10"/>
       <c r="L142" s="12"/>
       <c r="M142" s="13" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7720,35 +7722,35 @@
         <v>135</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="F143" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I143" s="10" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="K143" s="10" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="L143" s="12"/>
       <c r="M143" s="13" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7756,35 +7758,35 @@
         <v>136</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F144" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G144" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H144" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I144" s="10" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="J144" s="10" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="K144" s="10" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="L144" s="12"/>
       <c r="M144" s="13" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7792,10 +7794,10 @@
         <v>137</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>59</v>
@@ -7804,21 +7806,21 @@
         <v>29</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I145" s="10" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="J145" s="10" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="K145" s="10"/>
       <c r="L145" s="12"/>
       <c r="M145" s="13" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7826,10 +7828,10 @@
         <v>138</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="E146" s="10" t="s">
         <v>59</v>
@@ -7838,21 +7840,21 @@
         <v>29</v>
       </c>
       <c r="G146" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H146" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="J146" s="10" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="K146" s="10"/>
       <c r="L146" s="12"/>
       <c r="M146" s="13" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7860,35 +7862,35 @@
         <v>139</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="F147" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H147" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I147" s="10" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="J147" s="10" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="K147" s="10" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="L147" s="12"/>
       <c r="M147" s="13" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7896,35 +7898,35 @@
         <v>140</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="F148" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H148" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I148" s="10" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="J148" s="10" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="K148" s="10" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="L148" s="12"/>
       <c r="M148" s="13" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7932,19 +7934,19 @@
         <v>141</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="F149" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>31</v>
@@ -7956,11 +7958,11 @@
         <v>31</v>
       </c>
       <c r="K149" s="10" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="L149" s="12"/>
       <c r="M149" s="13" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7968,10 +7970,10 @@
         <v>142</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>59</v>
@@ -7980,21 +7982,21 @@
         <v>29</v>
       </c>
       <c r="G150" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H150" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I150" s="10" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="J150" s="10" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="K150" s="10"/>
       <c r="L150" s="12"/>
       <c r="M150" s="13" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8002,35 +8004,35 @@
         <v>143</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="F151" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H151" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I151" s="10" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="J151" s="10" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="K151" s="10" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="L151" s="12"/>
       <c r="M151" s="13" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8038,10 +8040,10 @@
         <v>144</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>59</v>
@@ -8050,23 +8052,23 @@
         <v>29</v>
       </c>
       <c r="G152" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H152" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I152" s="10" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="J152" s="10" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="K152" s="10" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="L152" s="12"/>
       <c r="M152" s="13" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8074,10 +8076,10 @@
         <v>145</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>59</v>
@@ -8086,7 +8088,7 @@
         <v>29</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H153" s="10" t="s">
         <v>31</v>
@@ -8095,12 +8097,12 @@
         <v>217</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="K153" s="10"/>
       <c r="L153" s="12"/>
       <c r="M153" s="13" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8108,13 +8110,13 @@
         <v>146</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="E154" s="10" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="F154" s="11" t="s">
         <v>72</v>
@@ -8129,14 +8131,14 @@
         <v>217</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="K154" s="10" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="L154" s="12"/>
       <c r="M154" s="13" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8144,10 +8146,10 @@
         <v>147</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>31</v>
@@ -8156,7 +8158,7 @@
         <v>86</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="H155" s="10" t="s">
         <v>31</v>
@@ -8168,11 +8170,11 @@
         <v>31</v>
       </c>
       <c r="K155" s="10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L155" s="12"/>
       <c r="M155" s="13" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8180,10 +8182,10 @@
         <v>148</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="E156" s="10" t="s">
         <v>59</v>
@@ -8198,17 +8200,17 @@
         <v>208</v>
       </c>
       <c r="I156" s="10" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="J156" s="10" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="K156" s="10" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="L156" s="12"/>
       <c r="M156" s="13" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8216,10 +8218,10 @@
         <v>149</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>31</v>
@@ -8240,28 +8242,28 @@
         <v>31</v>
       </c>
       <c r="K157" s="10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L157" s="12"/>
       <c r="M157" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B158" s="9" t="n">
         <v>150</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="E158" s="10" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="F158" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G158" s="10" t="s">
         <v>175</v>
@@ -8270,14 +8272,12 @@
         <v>31</v>
       </c>
       <c r="I158" s="10" t="s">
-        <v>31</v>
+        <v>663</v>
       </c>
       <c r="J158" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K158" s="10" t="s">
-        <v>658</v>
-      </c>
+        <v>664</v>
+      </c>
+      <c r="K158" s="10"/>
       <c r="L158" s="12"/>
       <c r="M158" s="13" t="s">
         <v>31</v>
@@ -8333,7 +8333,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8341,7 +8341,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>29</v>
@@ -8350,13 +8350,13 @@
         <v>72</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>86</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8630,11 +8630,11 @@
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B14,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B14,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B14,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -8646,12 +8646,12 @@
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false">IF(C14&gt;0,D14/C14,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C15" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B15)</f>
@@ -8680,7 +8680,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C16" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B16)</f>
@@ -8688,11 +8688,11 @@
       </c>
       <c r="D16" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B16,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B16,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B16,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -8700,16 +8700,16 @@
       </c>
       <c r="G16" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B16,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="19" t="n">
         <f aca="false">IF(C16&gt;0,D16/C16,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B17)</f>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="D17" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B17,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B17,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
@@ -8729,16 +8729,16 @@
       </c>
       <c r="G17" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B17,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="19" t="n">
         <f aca="false">IF(C17&gt;0,D17/C17,0)</f>
-        <v>0.333333333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="17" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B18)</f>
@@ -8767,7 +8767,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="17" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C19" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B19)</f>
@@ -8796,7 +8796,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="17" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C20" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B20)</f>
@@ -8825,7 +8825,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="17" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B21)</f>
@@ -8854,7 +8854,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="17" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B22)</f>
@@ -8883,7 +8883,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B23)</f>
@@ -8912,7 +8912,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="17" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B24)</f>
@@ -8941,7 +8941,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="17" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C25" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B25)</f>
@@ -8970,7 +8970,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="17" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B26)</f>
@@ -8999,7 +8999,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="17" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C27" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B27)</f>
@@ -9028,7 +9028,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="17" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C28" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B28)</f>
@@ -9057,7 +9057,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="17" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C29" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B29)</f>
@@ -9086,7 +9086,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="17" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C30" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B30)</f>
@@ -9094,11 +9094,11 @@
       </c>
       <c r="D30" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B30,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B30,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B30,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9110,12 +9110,12 @@
       </c>
       <c r="H30" s="19" t="n">
         <f aca="false">IF(C30&gt;0,D30/C30,0)</f>
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="17" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C31" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B31)</f>
@@ -9144,7 +9144,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="17" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C32" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B32)</f>
@@ -9152,11 +9152,11 @@
       </c>
       <c r="D32" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B32,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E32" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B32,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F32" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B32,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9164,16 +9164,16 @@
       </c>
       <c r="G32" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B32,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" s="19" t="n">
         <f aca="false">IF(C32&gt;0,D32/C32,0)</f>
-        <v>0.142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="17" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="C33" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B33)</f>
@@ -9202,7 +9202,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="17" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C34" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B34)</f>
@@ -9231,7 +9231,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="17" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C35" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B35)</f>
@@ -9260,7 +9260,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="17" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C36" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B36)</f>
@@ -9289,7 +9289,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="17" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C37" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B37)</f>
@@ -9318,7 +9318,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="17" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C38" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B38)</f>
@@ -9347,7 +9347,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="17" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C39" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B39)</f>
@@ -9376,7 +9376,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="17" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C40" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B40)</f>
@@ -9405,7 +9405,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="17" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C41" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B41)</f>
@@ -9434,7 +9434,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="17" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="C42" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B42)</f>
@@ -9463,7 +9463,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="17" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="C43" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B43)</f>
@@ -9492,7 +9492,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="17" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="C44" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B44)</f>
@@ -9521,7 +9521,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="17" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="C45" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B45)</f>
@@ -9550,7 +9550,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="17" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="C46" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B46)</f>
@@ -9579,7 +9579,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="17" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="C47" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B47)</f>
@@ -9608,7 +9608,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="17" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="C48" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B48)</f>
@@ -9637,7 +9637,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="17" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="C49" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B49)</f>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="D49" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B49,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B49,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
@@ -9657,16 +9657,16 @@
       </c>
       <c r="G49" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B49,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" s="19" t="n">
         <f aca="false">IF(C49&gt;0,D49/C49,0)</f>
-        <v>0.333333333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="20" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C50" s="21" t="n">
         <f aca="false">SUM(C5:C49)</f>
@@ -9674,11 +9674,11 @@
       </c>
       <c r="D50" s="21" t="n">
         <f aca="false">SUM(D5:D49)</f>
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">SUM(E5:E49)</f>
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F50" s="21" t="n">
         <f aca="false">SUM(F5:F49)</f>
@@ -9686,11 +9686,11 @@
       </c>
       <c r="G50" s="21" t="n">
         <f aca="false">SUM(G5:G49)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H50" s="22" t="n">
         <f aca="false">IF(C50&gt;0,D50/C50,0)</f>
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>
@@ -9721,18 +9721,18 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="23" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>18</v>
@@ -9740,13 +9740,13 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>72</v>
@@ -9754,13 +9754,13 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="24" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>72</v>
@@ -9768,13 +9768,13 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="24" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>72</v>
@@ -9782,27 +9782,27 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="24" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>72</v>
@@ -9810,27 +9810,27 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>86</v>
@@ -9838,13 +9838,13 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>86</v>
@@ -9896,15 +9896,15 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="26" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9912,7 +9912,7 @@
         <v>29</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9920,15 +9920,15 @@
         <v>72</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="26" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9936,7 +9936,7 @@
         <v>86</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9944,7 +9944,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9952,15 +9952,15 @@
         <v>22</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="26" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9968,15 +9968,15 @@
         <v>20</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="26" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
     </row>
   </sheetData>

--- a/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
+++ b/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="720">
   <si>
     <t xml:space="preserve">Nibbl AI — Master Requirements Tracker</t>
   </si>
@@ -1229,13 +1229,10 @@
     <t xml:space="preserve">Table: brand activity, site activity, open claims, cooldowns, last active, status</t>
   </si>
   <si>
-    <t xml:space="preserve">Customer table.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Customers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site-activity and cooldown columns to match the mockup.</t>
+    <t xml:space="preserve">Columns per Master: Customer, Contact, Brand Activity (claims / rebates / reviews), Site Activity (total claims / % completion / reviews), Open Claims, Cooldowns (days left), Last Active, Status (Active / Banned), View. Tabs: All, Open Claim, Active Cooldown, Completed Rebate, Banned, Inactive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Customers; check each column and tab against a shopper with an open claim and a cooldown.</t>
   </si>
   <si>
     <t xml:space="preserve">Customer Profile</t>
@@ -1244,16 +1241,13 @@
     <t xml:space="preserve">Header (opt-in badges, status) + Ban Customer with reason</t>
   </si>
   <si>
-    <t xml:space="preserve">Suspend from brand exists.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customers → profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suspend a customer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profile header/ban dialog per mockup.</t>
+    <t xml:space="preserve">Header: name, contact, customer since, last active, Nibbl Opt-In + brand Opt-In badges, Active/Banned. Ban modal with reason (suspicious activity, altered receipts, abuse, other); banned shoppers can't claim or get review opportunities from the brand; existing claims stay valid. Lift Ban.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers → View → Ban Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ban with a reason; status shows Banned with the reason; Lift Ban restores it.</t>
   </si>
   <si>
     <t xml:space="preserve">#46</t>
@@ -1262,22 +1256,37 @@
     <t xml:space="preserve">Relationship with brand · Nibbl activity totals · Recent activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Older profile layout.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a profile.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebuild to the Master layout.</t>
+    <t xml:space="preserve">Relationship tiles (claims, completed rebates, conversion, rewards, reviews, open claims); Nibbl totals only (claims, completion, reviews, rewards) — other brands' data never shown; recent activity timeline for this brand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers → View</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a profile; totals match the shopper's history.</t>
   </si>
   <si>
     <t xml:space="preserve">Open claims · Cooldowns with Remove (confirmation + audit)</t>
   </si>
   <si>
+    <t xml:space="preserve">Open claims with days left. Rebate and review cooldowns with Remove → confirmation → cooldown cleared and an audit-log entry (who, when, which). Managers only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers → View → Cooldowns → Remove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove a cooldown; the shopper can claim/review again; the audit log shows the removal.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Redemption history: full receipt 30 days, then matching line only</t>
   </si>
   <si>
-    <t xml:space="preserve">Receipt retention / cleanup rule not built.</t>
+    <t xml:space="preserve">Redemption history with View receipt + days left for 30 days; afterwards only the matching line item(s) are shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers → View → Redemption History</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recent receipt shows View receipt; one older than 30 days shows Matching line only.</t>
   </si>
   <si>
     <t xml:space="preserve">Brand Wallet</t>
@@ -1610,7 +1619,7 @@
     <t xml:space="preserve">Withdraw a small amount.</t>
   </si>
   <si>
-    <t xml:space="preserve">Twilio approved — retest the SMS step on production, then Completed.</t>
+    <t xml:space="preserve">SMS verification works on production (12 Oct). Do one real website withdrawal with the SMS step, then Completed.</t>
   </si>
   <si>
     <t xml:space="preserve">'Additional review needed' popup; status stays Processing</t>
@@ -2012,6 +2021,18 @@
     <t xml:space="preserve">Receipt retention / cleanup (full receipt 30 days, then matching line only)</t>
   </si>
   <si>
+    <t xml:space="preserve">Scheduled job (every 15 min) deletes receipt images 30 days after submission (pending receipts are skipped) and records when; matching line items and receipt details stay.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend job</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated test: a 31-day-old receipt loses its image and keeps the matching line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ships switched off in production (RECEIPT_IMAGE_PURGE_ENABLED) until the owner approves deleting existing receipt photos.</t>
+  </si>
+  <si>
     <t xml:space="preserve">System email via AWS SES with bounce / complaint handling</t>
   </si>
   <si>
@@ -2060,7 +2081,7 @@
     <t xml:space="preserve">Retest SMS-verified withdrawals; lock verified phones (change via admin + history)</t>
   </si>
   <si>
-    <t xml:space="preserve">Client: Twilio approved and ready for retesting</t>
+    <t xml:space="preserve">Twilio SMS verified on production 12 Oct 2026 (code sent to a Bangladesh number, delivered, approved). Remaining: one real website withdrawal with the SMS step</t>
   </si>
   <si>
     <t xml:space="preserve">Client — DNS</t>
@@ -2069,7 +2090,7 @@
     <t xml:space="preserve">Cloudflare access for www / brand / admin so the web apps can go live</t>
   </si>
   <si>
-    <t xml:space="preserve">Invite requested for syedriajul9624@gmail.com</t>
+    <t xml:space="preserve">Done — www / brand / admin.joinnibbl.com live with SSL on 11 Oct 2026</t>
   </si>
   <si>
     <t xml:space="preserve">AI service (Sakibur)</t>
@@ -2096,7 +2117,7 @@
     <t xml:space="preserve">System email from @joinnibbl.com + bounce/complaint handling</t>
   </si>
   <si>
-    <t xml:space="preserve">Done — production email switched to SES on 11 Oct 2026</t>
+    <t xml:space="preserve">Done — production email switched to SES on 11 Oct 2026 (per the client's 10 Oct credentials doc). Note: the Master says Klaviyo sends system emails — confirm SES is the long-term choice</t>
   </si>
   <si>
     <t xml:space="preserve">Client — Firebase</t>
@@ -2108,13 +2129,22 @@
     <t xml:space="preserve">Waiting on client setup</t>
   </si>
   <si>
-    <t xml:space="preserve">Client — Klaviyo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand + system SMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not integrated yet</t>
+    <t xml:space="preserve">Client — Klaviyo / SMS decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Settings §3: 'Klaviyo will send Nibbl system emails and SMS messages' (Nibbl's internal Klaviyo account). Brand SMS toggles are stored but no SMS is sent yet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision needed: Klaviyo access (private API key + SMS sender) as the Master says, or use the existing Twilio account for brand SMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client — FAQ content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand homepage 'Questions?' strip (Master mockup ④ only): Pricing / Review campaigns / Account &amp; billing / General FAQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No FAQ content in the Master — need questions/answers or a help-centre link; shown as labels until then</t>
   </si>
   <si>
     <t xml:space="preserve">How to Use This Tracker</t>
@@ -3015,11 +3045,11 @@
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Completed")</f>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Progress")</f>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Review")</f>
@@ -3027,11 +3057,11 @@
       </c>
       <c r="G5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Planned")</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H5" s="5" t="n">
         <f aca="false">IF(C5&gt;0,D5/C5,0)</f>
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6155,7 +6185,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="9" t="n">
         <v>90</v>
       </c>
@@ -6169,10 +6199,10 @@
         <v>400</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="H98" s="10" t="s">
         <v>31</v>
@@ -6183,101 +6213,95 @@
       <c r="J98" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="K98" s="10" t="s">
-        <v>402</v>
-      </c>
+      <c r="K98" s="10"/>
       <c r="L98" s="12"/>
       <c r="M98" s="13" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="9" t="n">
         <v>91</v>
       </c>
       <c r="C99" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D99" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="D99" s="10" t="s">
+      <c r="E99" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="E99" s="10" t="s">
+      <c r="F99" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I99" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="F99" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I99" s="10" t="s">
+      <c r="J99" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="J99" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="K99" s="10" t="s">
-        <v>408</v>
-      </c>
+      <c r="K99" s="10"/>
       <c r="L99" s="12"/>
       <c r="M99" s="13" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="9" t="n">
         <v>92</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D100" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="F100" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I100" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="E100" s="10" t="s">
+      <c r="J100" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="F100" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G100" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H100" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I100" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="J100" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="K100" s="10" t="s">
-        <v>413</v>
-      </c>
+      <c r="K100" s="10"/>
       <c r="L100" s="12"/>
       <c r="M100" s="13" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="9" t="n">
         <v>93</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G101" s="10" t="s">
         <v>51</v>
@@ -6286,34 +6310,32 @@
         <v>31</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>31</v>
+        <v>414</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K101" s="10" t="s">
-        <v>361</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="K101" s="10"/>
       <c r="L101" s="12"/>
       <c r="M101" s="13" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="9" t="n">
         <v>94</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>31</v>
+        <v>417</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G102" s="10" t="s">
         <v>51</v>
@@ -6322,14 +6344,12 @@
         <v>31</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>31</v>
+        <v>418</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K102" s="10" t="s">
-        <v>416</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="K102" s="10"/>
       <c r="L102" s="12"/>
       <c r="M102" s="13" t="s">
         <v>398</v>
@@ -6340,10 +6360,10 @@
         <v>95</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>59</v>
@@ -6358,15 +6378,15 @@
         <v>31</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="K103" s="10"/>
       <c r="L103" s="12"/>
       <c r="M103" s="13" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6374,10 +6394,10 @@
         <v>96</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>59</v>
@@ -6392,15 +6412,15 @@
         <v>31</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="J104" s="10" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K104" s="10"/>
       <c r="L104" s="12"/>
       <c r="M104" s="13" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6408,10 +6428,10 @@
         <v>97</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>59</v>
@@ -6426,17 +6446,17 @@
         <v>31</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="J105" s="10" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K105" s="10" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L105" s="12"/>
       <c r="M105" s="13" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6444,10 +6464,10 @@
         <v>98</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>59</v>
@@ -6462,15 +6482,15 @@
         <v>31</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="K106" s="10"/>
       <c r="L106" s="12"/>
       <c r="M106" s="13" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6478,31 +6498,31 @@
         <v>99</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F107" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="H107" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L107" s="12"/>
       <c r="M107" s="13" t="s">
@@ -6514,10 +6534,10 @@
         <v>100</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>59</v>
@@ -6532,15 +6552,15 @@
         <v>31</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K108" s="10"/>
       <c r="L108" s="12"/>
       <c r="M108" s="13" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6548,13 +6568,13 @@
         <v>101</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F109" s="11" t="s">
         <v>29</v>
@@ -6566,10 +6586,10 @@
         <v>31</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="K109" s="10"/>
       <c r="L109" s="12"/>
@@ -6582,13 +6602,13 @@
         <v>102</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F110" s="11" t="s">
         <v>29</v>
@@ -6603,12 +6623,12 @@
         <v>176</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="K110" s="10"/>
       <c r="L110" s="12"/>
       <c r="M110" s="13" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6616,10 +6636,10 @@
         <v>103</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>59</v>
@@ -6634,15 +6654,15 @@
         <v>31</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="K111" s="10"/>
       <c r="L111" s="12"/>
       <c r="M111" s="13" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6650,10 +6670,10 @@
         <v>104</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>59</v>
@@ -6668,15 +6688,15 @@
         <v>31</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="J112" s="10" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="K112" s="10"/>
       <c r="L112" s="12"/>
       <c r="M112" s="13" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6684,13 +6704,13 @@
         <v>105</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F113" s="11" t="s">
         <v>72</v>
@@ -6702,17 +6722,17 @@
         <v>31</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="K113" s="10" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L113" s="12"/>
       <c r="M113" s="13" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6720,10 +6740,10 @@
         <v>106</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>59</v>
@@ -6738,10 +6758,10 @@
         <v>31</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K114" s="10"/>
       <c r="L114" s="12"/>
@@ -6754,13 +6774,13 @@
         <v>107</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F115" s="11" t="s">
         <v>29</v>
@@ -6772,15 +6792,15 @@
         <v>31</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K115" s="10"/>
       <c r="L115" s="12"/>
       <c r="M115" s="13" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6788,10 +6808,10 @@
         <v>108</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>59</v>
@@ -6806,15 +6826,15 @@
         <v>31</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="K116" s="10"/>
       <c r="L116" s="12"/>
       <c r="M116" s="13" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6822,10 +6842,10 @@
         <v>109</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>59</v>
@@ -6840,15 +6860,15 @@
         <v>31</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="K117" s="10"/>
       <c r="L117" s="12"/>
       <c r="M117" s="13" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6856,13 +6876,13 @@
         <v>110</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F118" s="11" t="s">
         <v>29</v>
@@ -6874,7 +6894,7 @@
         <v>31</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J118" s="10" t="s">
         <v>229</v>
@@ -6882,7 +6902,7 @@
       <c r="K118" s="10"/>
       <c r="L118" s="12"/>
       <c r="M118" s="13" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6890,13 +6910,13 @@
         <v>111</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F119" s="11" t="s">
         <v>29</v>
@@ -6908,17 +6928,17 @@
         <v>31</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K119" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L119" s="12"/>
       <c r="M119" s="13" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6926,13 +6946,13 @@
         <v>112</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F120" s="11" t="s">
         <v>29</v>
@@ -6944,15 +6964,15 @@
         <v>31</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K120" s="10"/>
       <c r="L120" s="12"/>
       <c r="M120" s="13" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6960,13 +6980,13 @@
         <v>113</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F121" s="11" t="s">
         <v>29</v>
@@ -6978,15 +6998,15 @@
         <v>31</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="J121" s="10" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="K121" s="10"/>
       <c r="L121" s="12"/>
       <c r="M121" s="13" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6994,13 +7014,13 @@
         <v>114</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F122" s="11" t="s">
         <v>29</v>
@@ -7012,17 +7032,17 @@
         <v>31</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="J122" s="10" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="K122" s="10" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L122" s="12"/>
       <c r="M122" s="13" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7030,13 +7050,13 @@
         <v>115</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F123" s="11" t="s">
         <v>29</v>
@@ -7048,15 +7068,15 @@
         <v>31</v>
       </c>
       <c r="I123" s="10" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K123" s="10"/>
       <c r="L123" s="12"/>
       <c r="M123" s="13" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7064,13 +7084,13 @@
         <v>116</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F124" s="11" t="s">
         <v>29</v>
@@ -7082,15 +7102,15 @@
         <v>31</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K124" s="10"/>
       <c r="L124" s="12"/>
       <c r="M124" s="13" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7098,10 +7118,10 @@
         <v>117</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>59</v>
@@ -7116,15 +7136,15 @@
         <v>208</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="K125" s="10"/>
       <c r="L125" s="12"/>
       <c r="M125" s="13" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7132,13 +7152,13 @@
         <v>118</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F126" s="11" t="s">
         <v>29</v>
@@ -7150,7 +7170,7 @@
         <v>208</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="J126" s="10" t="s">
         <v>115</v>
@@ -7158,7 +7178,7 @@
       <c r="K126" s="10"/>
       <c r="L126" s="12"/>
       <c r="M126" s="13" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7166,13 +7186,13 @@
         <v>119</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F127" s="11" t="s">
         <v>29</v>
@@ -7184,15 +7204,15 @@
         <v>208</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K127" s="10"/>
       <c r="L127" s="12"/>
       <c r="M127" s="13" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7200,10 +7220,10 @@
         <v>120</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>59</v>
@@ -7218,15 +7238,15 @@
         <v>208</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K128" s="10"/>
       <c r="L128" s="12"/>
       <c r="M128" s="13" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7234,13 +7254,13 @@
         <v>121</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F129" s="11" t="s">
         <v>72</v>
@@ -7252,17 +7272,17 @@
         <v>208</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="K129" s="10" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="L129" s="12"/>
       <c r="M129" s="13" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7270,13 +7290,13 @@
         <v>122</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F130" s="11" t="s">
         <v>29</v>
@@ -7288,15 +7308,15 @@
         <v>208</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="K130" s="10"/>
       <c r="L130" s="12"/>
       <c r="M130" s="13" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7304,33 +7324,33 @@
         <v>123</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F131" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="H131" s="10" t="s">
         <v>208</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K131" s="10"/>
       <c r="L131" s="12"/>
       <c r="M131" s="13" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7338,13 +7358,13 @@
         <v>124</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="F132" s="11" t="s">
         <v>29</v>
@@ -7356,15 +7376,15 @@
         <v>208</v>
       </c>
       <c r="I132" s="10" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="K132" s="10"/>
       <c r="L132" s="12"/>
       <c r="M132" s="13" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7372,13 +7392,13 @@
         <v>125</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F133" s="11" t="s">
         <v>29</v>
@@ -7390,15 +7410,15 @@
         <v>208</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="J133" s="10" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="K133" s="10"/>
       <c r="L133" s="12"/>
       <c r="M133" s="13" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7406,13 +7426,13 @@
         <v>126</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F134" s="11" t="s">
         <v>29</v>
@@ -7424,15 +7444,15 @@
         <v>208</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K134" s="10"/>
       <c r="L134" s="12"/>
       <c r="M134" s="13" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7440,10 +7460,10 @@
         <v>127</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>59</v>
@@ -7458,15 +7478,15 @@
         <v>208</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="J135" s="10" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K135" s="10"/>
       <c r="L135" s="12"/>
       <c r="M135" s="13" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7474,13 +7494,13 @@
         <v>128</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="F136" s="11" t="s">
         <v>86</v>
@@ -7498,7 +7518,7 @@
         <v>31</v>
       </c>
       <c r="K136" s="10" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L136" s="12"/>
       <c r="M136" s="13" t="s">
@@ -7510,13 +7530,13 @@
         <v>129</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F137" s="11" t="s">
         <v>72</v>
@@ -7528,17 +7548,17 @@
         <v>208</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K137" s="10" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="L137" s="12"/>
       <c r="M137" s="13" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7546,35 +7566,35 @@
         <v>130</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="F138" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G138" s="10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H138" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I138" s="10" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="J138" s="10" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K138" s="10" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L138" s="12"/>
       <c r="M138" s="13" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7582,13 +7602,13 @@
         <v>131</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="F139" s="11" t="s">
         <v>29</v>
@@ -7600,17 +7620,17 @@
         <v>31</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="K139" s="10" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="L139" s="12"/>
       <c r="M139" s="13" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7618,13 +7638,13 @@
         <v>132</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="F140" s="11" t="s">
         <v>29</v>
@@ -7636,17 +7656,17 @@
         <v>31</v>
       </c>
       <c r="I140" s="10" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="J140" s="10" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="K140" s="10" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="L140" s="12"/>
       <c r="M140" s="13" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7654,13 +7674,13 @@
         <v>133</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="F141" s="11" t="s">
         <v>29</v>
@@ -7672,15 +7692,15 @@
         <v>31</v>
       </c>
       <c r="I141" s="10" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="J141" s="10" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="K141" s="10"/>
       <c r="L141" s="12"/>
       <c r="M141" s="13" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7688,13 +7708,13 @@
         <v>134</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F142" s="11" t="s">
         <v>29</v>
@@ -7706,15 +7726,15 @@
         <v>31</v>
       </c>
       <c r="I142" s="10" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="K142" s="10"/>
       <c r="L142" s="12"/>
       <c r="M142" s="13" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7722,35 +7742,35 @@
         <v>135</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="F143" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I143" s="10" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="K143" s="10" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="L143" s="12"/>
       <c r="M143" s="13" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7758,35 +7778,35 @@
         <v>136</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="F144" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G144" s="10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H144" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I144" s="10" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="J144" s="10" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="K144" s="10" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L144" s="12"/>
       <c r="M144" s="13" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7794,10 +7814,10 @@
         <v>137</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>59</v>
@@ -7806,21 +7826,21 @@
         <v>29</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I145" s="10" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="J145" s="10" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="K145" s="10"/>
       <c r="L145" s="12"/>
       <c r="M145" s="13" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7828,10 +7848,10 @@
         <v>138</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E146" s="10" t="s">
         <v>59</v>
@@ -7840,21 +7860,21 @@
         <v>29</v>
       </c>
       <c r="G146" s="10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H146" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="J146" s="10" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K146" s="10"/>
       <c r="L146" s="12"/>
       <c r="M146" s="13" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7862,35 +7882,35 @@
         <v>139</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="F147" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H147" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I147" s="10" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="J147" s="10" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K147" s="10" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="L147" s="12"/>
       <c r="M147" s="13" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7898,35 +7918,35 @@
         <v>140</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F148" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H148" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I148" s="10" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="J148" s="10" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="K148" s="10" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="L148" s="12"/>
       <c r="M148" s="13" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7934,19 +7954,19 @@
         <v>141</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F149" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>31</v>
@@ -7958,11 +7978,11 @@
         <v>31</v>
       </c>
       <c r="K149" s="10" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="L149" s="12"/>
       <c r="M149" s="13" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7970,10 +7990,10 @@
         <v>142</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>59</v>
@@ -7982,21 +8002,21 @@
         <v>29</v>
       </c>
       <c r="G150" s="10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H150" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I150" s="10" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="J150" s="10" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="K150" s="10"/>
       <c r="L150" s="12"/>
       <c r="M150" s="13" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8004,35 +8024,35 @@
         <v>143</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="F151" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H151" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I151" s="10" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="J151" s="10" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K151" s="10" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="L151" s="12"/>
       <c r="M151" s="13" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8040,10 +8060,10 @@
         <v>144</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>59</v>
@@ -8052,23 +8072,23 @@
         <v>29</v>
       </c>
       <c r="G152" s="10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H152" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I152" s="10" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="J152" s="10" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="K152" s="10" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L152" s="12"/>
       <c r="M152" s="13" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8076,10 +8096,10 @@
         <v>145</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>59</v>
@@ -8088,7 +8108,7 @@
         <v>29</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H153" s="10" t="s">
         <v>31</v>
@@ -8097,12 +8117,12 @@
         <v>217</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="K153" s="10"/>
       <c r="L153" s="12"/>
       <c r="M153" s="13" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8110,13 +8130,13 @@
         <v>146</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="E154" s="10" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="F154" s="11" t="s">
         <v>72</v>
@@ -8131,14 +8151,14 @@
         <v>217</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="K154" s="10" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="L154" s="12"/>
       <c r="M154" s="13" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8146,10 +8166,10 @@
         <v>147</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>31</v>
@@ -8158,7 +8178,7 @@
         <v>86</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H155" s="10" t="s">
         <v>31</v>
@@ -8174,7 +8194,7 @@
       </c>
       <c r="L155" s="12"/>
       <c r="M155" s="13" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8182,10 +8202,10 @@
         <v>148</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E156" s="10" t="s">
         <v>59</v>
@@ -8200,34 +8220,34 @@
         <v>208</v>
       </c>
       <c r="I156" s="10" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="J156" s="10" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="K156" s="10" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="L156" s="12"/>
       <c r="M156" s="13" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B157" s="9" t="n">
         <v>149</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>31</v>
+        <v>664</v>
       </c>
       <c r="F157" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G157" s="10" t="s">
         <v>175</v>
@@ -8236,13 +8256,13 @@
         <v>31</v>
       </c>
       <c r="I157" s="10" t="s">
-        <v>31</v>
+        <v>665</v>
       </c>
       <c r="J157" s="10" t="s">
-        <v>31</v>
+        <v>666</v>
       </c>
       <c r="K157" s="10" t="s">
-        <v>361</v>
+        <v>667</v>
       </c>
       <c r="L157" s="12"/>
       <c r="M157" s="13" t="s">
@@ -8254,13 +8274,13 @@
         <v>150</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="E158" s="10" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="F158" s="11" t="s">
         <v>29</v>
@@ -8272,10 +8292,10 @@
         <v>31</v>
       </c>
       <c r="I158" s="10" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="J158" s="10" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="K158" s="10"/>
       <c r="L158" s="12"/>
@@ -8333,7 +8353,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8341,7 +8361,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>29</v>
@@ -8356,7 +8376,7 @@
         <v>86</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8978,11 +8998,11 @@
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B26,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B26,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B26,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -8994,12 +9014,12 @@
       </c>
       <c r="H26" s="19" t="n">
         <f aca="false">IF(C26&gt;0,D26/C26,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="17" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C27" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B27)</f>
@@ -9007,11 +9027,11 @@
       </c>
       <c r="D27" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B27,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E27" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B27,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B27,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9019,16 +9039,16 @@
       </c>
       <c r="G27" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B27,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" s="19" t="n">
         <f aca="false">IF(C27&gt;0,D27/C27,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="17" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C28" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B28)</f>
@@ -9057,7 +9077,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="17" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C29" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B29)</f>
@@ -9086,7 +9106,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="17" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C30" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B30)</f>
@@ -9115,7 +9135,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="17" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C31" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B31)</f>
@@ -9144,7 +9164,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="17" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C32" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B32)</f>
@@ -9173,7 +9193,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="17" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C33" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B33)</f>
@@ -9202,7 +9222,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="17" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C34" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B34)</f>
@@ -9231,7 +9251,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="17" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C35" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B35)</f>
@@ -9260,7 +9280,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="17" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C36" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B36)</f>
@@ -9289,7 +9309,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="17" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C37" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B37)</f>
@@ -9318,7 +9338,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="17" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C38" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B38)</f>
@@ -9347,7 +9367,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="17" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C39" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B39)</f>
@@ -9376,7 +9396,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="17" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C40" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B40)</f>
@@ -9405,7 +9425,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="17" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C41" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B41)</f>
@@ -9434,7 +9454,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="17" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C42" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B42)</f>
@@ -9463,7 +9483,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="17" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C43" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B43)</f>
@@ -9492,7 +9512,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="17" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C44" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B44)</f>
@@ -9521,7 +9541,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="17" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C45" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B45)</f>
@@ -9550,7 +9570,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="17" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C46" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B46)</f>
@@ -9579,7 +9599,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="17" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C47" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B47)</f>
@@ -9608,7 +9628,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="17" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C48" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B48)</f>
@@ -9637,7 +9657,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="17" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C49" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B49)</f>
@@ -9645,7 +9665,7 @@
       </c>
       <c r="D49" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B49,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B49,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
@@ -9657,16 +9677,16 @@
       </c>
       <c r="G49" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B49,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" s="19" t="n">
         <f aca="false">IF(C49&gt;0,D49/C49,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="20" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="C50" s="21" t="n">
         <f aca="false">SUM(C5:C49)</f>
@@ -9674,11 +9694,11 @@
       </c>
       <c r="D50" s="21" t="n">
         <f aca="false">SUM(D5:D49)</f>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">SUM(E5:E49)</f>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F50" s="21" t="n">
         <f aca="false">SUM(F5:F49)</f>
@@ -9686,11 +9706,11 @@
       </c>
       <c r="G50" s="21" t="n">
         <f aca="false">SUM(G5:G49)</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H50" s="22" t="n">
         <f aca="false">IF(C50&gt;0,D50/C50,0)</f>
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -9709,7 +9729,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:E12"/>
+  <dimension ref="B2:E13"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.75"/>
@@ -9721,18 +9741,18 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="23" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>18</v>
@@ -9740,13 +9760,13 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>72</v>
@@ -9754,13 +9774,13 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="24" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>72</v>
@@ -9768,27 +9788,27 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="24" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>298</v>
@@ -9796,13 +9816,13 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="24" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>72</v>
@@ -9810,13 +9830,13 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>29</v>
@@ -9824,13 +9844,13 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>86</v>
@@ -9838,20 +9858,34 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>86</v>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="24" t="s">
+        <v>703</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>704</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>705</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E12">
+  <conditionalFormatting sqref="E5:E13">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>"Completed"</formula>
     </cfRule>
@@ -9866,7 +9900,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E12" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E13" type="list">
       <formula1>"Completed,In Progress,In Review,Planned"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9896,15 +9930,15 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="26" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9912,7 +9946,7 @@
         <v>29</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9920,7 +9954,7 @@
         <v>72</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9928,7 +9962,7 @@
         <v>298</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9936,7 +9970,7 @@
         <v>86</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9944,7 +9978,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9952,15 +9986,15 @@
         <v>22</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="26" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9968,15 +10002,15 @@
         <v>20</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="26" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
     </row>
   </sheetData>

--- a/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
+++ b/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="724">
   <si>
     <t xml:space="preserve">Nibbl AI — Master Requirements Tracker</t>
   </si>
@@ -635,10 +635,16 @@
     <t xml:space="preserve">Only Nibbl admin may cancel an existing reservation, with a reason</t>
   </si>
   <si>
+    <t xml:space="preserve">Admin → Shoppers → Claims &amp; Reviews → Cancel claim: reason required; the claim closes, the brand's reserved funds return, and the cancel is audit-logged. Brands can't cancel claims.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Admin Dashboard + Backend / API</t>
   </si>
   <si>
-    <t xml:space="preserve">Admin reservation cancel with reason + audit not built.</t>
+    <t xml:space="preserve">Admin → Shoppers → shopper → Claims &amp; Reviews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel an open claim with a reason; the brand's Reserved Funds drop by that claim.</t>
   </si>
   <si>
     <t xml:space="preserve">Discovery</t>
@@ -1733,7 +1739,7 @@
     <t xml:space="preserve">Revenue cards, Needs Attention, Brand Revenue (category/status filter, lowest first), brand-funded rewards</t>
   </si>
   <si>
-    <t xml:space="preserve">As specified except category.</t>
+    <t xml:space="preserve">Revenue cards, Needs Attention links, Brand Revenue with category / status / plan filters, lowest first, Total Nibbl Revenue + Last Activity, brand-funded rewards shown separately.</t>
   </si>
   <si>
     <t xml:space="preserve">Admin Dashboard</t>
@@ -1742,10 +1748,10 @@
     <t xml:space="preserve">Admin → Dashboard</t>
   </si>
   <si>
-    <t xml:space="preserve">Change date range.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand category filter (brands have no category). Failed payouts count is now live.</t>
+    <t xml:space="preserve">Change the date range and the category filter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A brand's category = its most common product category (the sign-up category isn't stored).</t>
   </si>
   <si>
     <t xml:space="preserve">#42</t>
@@ -1817,16 +1823,13 @@
     <t xml:space="preserve">KPIs, brand table (category, Nibbl revenue, funds, payment status, activity), filters, sort</t>
   </si>
   <si>
-    <t xml:space="preserve">Brand list.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Brand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Brands.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue / payment-status columns and KPIs per mockup.</t>
+    <t xml:space="preserve">KPIs (active, pending verification, failed payments, suspended); table with category, plan, Nibbl revenue, wallet funds, payment status, last activity, status; search, filters, sort (lowest revenue first).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Brands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter by category and plan; sort by lowest revenue.</t>
   </si>
   <si>
     <t xml:space="preserve">#45</t>
@@ -1835,13 +1838,13 @@
     <t xml:space="preserve">Admin brand access mode ('viewing as Nibbl', every action logged) + brand summary + actions</t>
   </si>
   <si>
-    <t xml:space="preserve">Promo credit, suspend.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a brand.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open-brand-dashboard superuser mode not built.</t>
+    <t xml:space="preserve">Selected-brand summary (verified, payment connected, wallet funds, promotional credits, Nibbl revenue, active campaigns); Open Brand Dashboard opens the brand app in Nibbl Admin Mode (banner: Viewing &lt;brand&gt;. Every action is logged.), every change made there is audit-logged; Add Promotional Credit; Suspend / Reactivate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Brands → brand → Open Brand Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a brand's dashboard, change a setting, then find it in Settings → View Audit Log.</t>
   </si>
   <si>
     <t xml:space="preserve">#45, #46</t>
@@ -1880,133 +1883,142 @@
     <t xml:space="preserve">List (status, wallet, redemptions, referrals, brand suspensions, last activity)</t>
   </si>
   <si>
-    <t xml:space="preserve">Users list.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Users.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columns per mockup.</t>
+    <t xml:space="preserve">Searchable list (name, email, phone, Shopper ID) with account status, wallet, redemptions, referrals, brand suspensions, last activity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Shoppers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search a shopper by email.</t>
   </si>
   <si>
     <t xml:space="preserve">Detail tabs (overview, wallet ledger, claims &amp; reviews, referrals, suspensions), purchase activity, cooldowns, adjust wallet, internal note, global suspend</t>
   </si>
   <si>
-    <t xml:space="preserve">Details, wallet credit with reason, suspend, linked accounts.</t>
+    <t xml:space="preserve">Selected shopper: identity + status; tabs Overview (account &amp; payout, wallet: available / pending / lifetime paid, purchase activity: brands + retailers, active cooldowns, internal notes), Wallet Ledger, Claims &amp; Reviews (cancel claim), Referrals, Suspensions; Adjust Wallet (credit/debit, reason required, before/after audit), Add Internal Note, Global Suspend / Reactivate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Shoppers → shopper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjust a wallet with a reason; add a note; check the ledger tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#46, #51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Suspensions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary, list, review (remove brand suspension, global suspend), repeated-suspension alert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Suspensions page: summary (active brand suspensions, repeat suspensions, global suspensions), searchable list (brand, reason, date, prior count, status) with date/status filters; detail with View Shopper, Remove Brand Suspension, Globally Suspend; repeated suspensions alert only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Suspensions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove a brand suspension; globally suspend a shopper.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Referrals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary, filters, details, flag review (approve / reject / suspend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Referrals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the Flagged tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Revenue Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources, promo credits used, refunds, processing costs, net revenue, trend chart, brand contribution + export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Analytics page: revenue sources, promotional credits used, refunds, processing costs, net revenue, brand-funded rewards; daily Revenue Trend chart; Brand Revenue Contribution (credits + processing per brand) with category / plan filters and Export CSV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch the date range; export the CSV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processing costs are estimates (Stripe 2.9% + $0.30 per wallet top-up; $0.25 per payout). Refunds = brand wallet cash returned, shown but not deducted from revenue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Receipt Brand Discovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary, filters, leads, brand insight, export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Brand Discovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a lead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand detected from receipt text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Withdrawal review rules · Discovery ranking · device/network limits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change a threshold.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#50, #51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referral flag rules: duplicate payout identity, same device, self-referral, unusual referral volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toggles for the Master rules: duplicate payout identity, same device, self-referral (same name / email / phone, Gmail dots and +tags ignored), unusual referral volume (limit per 7 days); same-network and fraud-signal checks kept as additional toggles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turn a rule off; a matching referral no longer gets flagged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin Users (staff roles) + View Audit Log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin Users: list, + Add User (Administrator / Operations / Analytics; new admins set their password through the emailed code), change role, remove access; Analytics is read-only and only Administrators change Settings or Admin Users; View Audit Log (latest 200 sensitive actions).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Settings → Admin Users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add an Analytics user; they can view pages but can't save changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-cutting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud &amp; abuse: duplicates, velocity, device / IP / browser checks</t>
   </si>
   <si>
     <t xml:space="preserve">Admin → Users → user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a shopper.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabs, purchase activity, cooldowns and internal notes not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#46, #51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Suspensions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary, list, review (remove brand suspension, global suspend), repeated-suspension alert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand suspensions + alert exist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dedicated Suspensions page not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Referrals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary, filters, details, flag review (approve / reject / suspend)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Referrals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open the Flagged tab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Revenue Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sources, promo credits used, refunds, processing costs, net revenue, trend chart, brand contribution + export</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sources, credits, trend table, brand revenue.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check revenue.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refunds / processing costs not recorded; chart and export per mockup.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Receipt Brand Discovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary, filters, leads, brand insight, export</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Brand Discovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a lead.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand detected from receipt text.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Settings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Withdrawal review rules · Discovery ranking · device/network limits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change a threshold.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#50, #51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referral flag rules: duplicate payout identity, same device, self-referral, unusual referral volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same device, same network, fraud signals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toggle rules.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align rule set with the Master list.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin Users (staff roles) + View Audit Log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross-cutting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud &amp; abuse: duplicates, velocity, device / IP / browser checks</t>
   </si>
   <si>
     <t xml:space="preserve">Create 3 accounts on one browser.</t>
@@ -3045,11 +3057,11 @@
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Completed")</f>
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Progress")</f>
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Review")</f>
@@ -3057,11 +3069,11 @@
       </c>
       <c r="G5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Planned")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H5" s="5" t="n">
         <f aca="false">IF(C5&gt;0,D5/C5,0)</f>
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4459,7 +4471,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="9" t="n">
         <v>40</v>
       </c>
@@ -4470,26 +4482,24 @@
         <v>201</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>31</v>
+        <v>202</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H48" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>31</v>
+        <v>204</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K48" s="10" t="s">
-        <v>203</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="K48" s="10"/>
       <c r="L48" s="12"/>
       <c r="M48" s="13" t="s">
         <v>31</v>
@@ -4500,28 +4510,28 @@
         <v>41</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K49" s="10"/>
       <c r="L49" s="12"/>
@@ -4534,13 +4544,13 @@
         <v>42</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>29</v>
@@ -4549,13 +4559,13 @@
         <v>175</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K50" s="10"/>
       <c r="L50" s="12"/>
@@ -4568,10 +4578,10 @@
         <v>43</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>59</v>
@@ -4580,21 +4590,21 @@
         <v>29</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K51" s="10"/>
       <c r="L51" s="12"/>
       <c r="M51" s="13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4602,31 +4612,31 @@
         <v>44</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L52" s="12"/>
       <c r="M52" s="13" t="s">
@@ -4638,10 +4648,10 @@
         <v>45</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>59</v>
@@ -4659,12 +4669,12 @@
         <v>176</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K53" s="10"/>
       <c r="L53" s="12"/>
       <c r="M53" s="13" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4672,10 +4682,10 @@
         <v>46</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>59</v>
@@ -4684,16 +4694,16 @@
         <v>29</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K54" s="10"/>
       <c r="L54" s="12"/>
@@ -4706,10 +4716,10 @@
         <v>47</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>59</v>
@@ -4721,18 +4731,18 @@
         <v>175</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K55" s="10"/>
       <c r="L55" s="12"/>
       <c r="M55" s="13" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4740,33 +4750,33 @@
         <v>48</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K56" s="10"/>
       <c r="L56" s="12"/>
       <c r="M56" s="13" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4774,35 +4784,35 @@
         <v>49</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F57" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K57" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L57" s="12"/>
       <c r="M57" s="13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4810,33 +4820,33 @@
         <v>50</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K58" s="10"/>
       <c r="L58" s="12"/>
       <c r="M58" s="13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4844,13 +4854,13 @@
         <v>51</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>29</v>
@@ -4865,12 +4875,12 @@
         <v>176</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K59" s="10"/>
       <c r="L59" s="12"/>
       <c r="M59" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4878,10 +4888,10 @@
         <v>52</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>59</v>
@@ -4893,18 +4903,18 @@
         <v>175</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K60" s="10"/>
       <c r="L60" s="12"/>
       <c r="M60" s="13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4912,10 +4922,10 @@
         <v>53</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>59</v>
@@ -4924,16 +4934,16 @@
         <v>29</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K61" s="10"/>
       <c r="L61" s="12"/>
@@ -4944,35 +4954,35 @@
         <v>54</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L62" s="12"/>
       <c r="M62" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4980,33 +4990,33 @@
         <v>55</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K63" s="10"/>
       <c r="L63" s="12"/>
       <c r="M63" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5014,10 +5024,10 @@
         <v>56</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>59</v>
@@ -5035,14 +5045,14 @@
         <v>176</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L64" s="12"/>
       <c r="M64" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5050,10 +5060,10 @@
         <v>57</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>59</v>
@@ -5071,12 +5081,12 @@
         <v>176</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K65" s="10"/>
       <c r="L65" s="12"/>
       <c r="M65" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5084,13 +5094,13 @@
         <v>58</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>29</v>
@@ -5099,18 +5109,18 @@
         <v>181</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K66" s="10"/>
       <c r="L66" s="12"/>
       <c r="M66" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5118,35 +5128,35 @@
         <v>59</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J67" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K67" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L67" s="12"/>
       <c r="M67" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5154,10 +5164,10 @@
         <v>60</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>59</v>
@@ -5169,18 +5179,18 @@
         <v>175</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K68" s="10"/>
       <c r="L68" s="12"/>
       <c r="M68" s="13" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5188,13 +5198,13 @@
         <v>61</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>29</v>
@@ -5203,18 +5213,18 @@
         <v>181</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K69" s="10"/>
       <c r="L69" s="12"/>
       <c r="M69" s="13" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5222,22 +5232,22 @@
         <v>62</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G70" s="10" t="s">
         <v>175</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I70" s="10" t="s">
         <v>31</v>
@@ -5246,7 +5256,7 @@
         <v>31</v>
       </c>
       <c r="K70" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L70" s="12"/>
       <c r="M70" s="13" t="s">
@@ -5258,10 +5268,10 @@
         <v>63</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>59</v>
@@ -5276,15 +5286,15 @@
         <v>31</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J71" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K71" s="10"/>
       <c r="L71" s="12"/>
       <c r="M71" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5292,10 +5302,10 @@
         <v>64</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>59</v>
@@ -5310,15 +5320,15 @@
         <v>31</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K72" s="10"/>
       <c r="L72" s="12"/>
       <c r="M72" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5326,10 +5336,10 @@
         <v>65</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>59</v>
@@ -5344,7 +5354,7 @@
         <v>31</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J73" s="10" t="s">
         <v>115</v>
@@ -5352,7 +5362,7 @@
       <c r="K73" s="10"/>
       <c r="L73" s="12"/>
       <c r="M73" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5360,13 +5370,13 @@
         <v>66</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>29</v>
@@ -5378,15 +5388,15 @@
         <v>31</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K74" s="10"/>
       <c r="L74" s="12"/>
       <c r="M74" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5394,10 +5404,10 @@
         <v>67</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>59</v>
@@ -5412,15 +5422,15 @@
         <v>31</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J75" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K75" s="10"/>
       <c r="L75" s="12"/>
       <c r="M75" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5428,10 +5438,10 @@
         <v>68</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>59</v>
@@ -5446,15 +5456,15 @@
         <v>31</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K76" s="10"/>
       <c r="L76" s="12"/>
       <c r="M76" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5462,13 +5472,13 @@
         <v>69</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F77" s="11" t="s">
         <v>29</v>
@@ -5480,15 +5490,15 @@
         <v>31</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K77" s="10"/>
       <c r="L77" s="12"/>
       <c r="M77" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5496,13 +5506,13 @@
         <v>70</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>29</v>
@@ -5514,7 +5524,7 @@
         <v>31</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J78" s="10" t="s">
         <v>115</v>
@@ -5522,7 +5532,7 @@
       <c r="K78" s="10"/>
       <c r="L78" s="12"/>
       <c r="M78" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5530,13 +5540,13 @@
         <v>71</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F79" s="11" t="s">
         <v>29</v>
@@ -5548,15 +5558,15 @@
         <v>31</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K79" s="10"/>
       <c r="L79" s="12"/>
       <c r="M79" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5564,13 +5574,13 @@
         <v>72</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F80" s="11" t="s">
         <v>29</v>
@@ -5582,15 +5592,15 @@
         <v>31</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K80" s="10"/>
       <c r="L80" s="12"/>
       <c r="M80" s="13" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5598,13 +5608,13 @@
         <v>73</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F81" s="11" t="s">
         <v>29</v>
@@ -5616,15 +5626,15 @@
         <v>31</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K81" s="10"/>
       <c r="L81" s="12"/>
       <c r="M81" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5632,13 +5642,13 @@
         <v>74</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F82" s="11" t="s">
         <v>29</v>
@@ -5650,15 +5660,15 @@
         <v>31</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K82" s="10"/>
       <c r="L82" s="12"/>
       <c r="M82" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5666,13 +5676,13 @@
         <v>75</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F83" s="11" t="s">
         <v>29</v>
@@ -5684,15 +5694,15 @@
         <v>31</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K83" s="10"/>
       <c r="L83" s="12"/>
       <c r="M83" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5700,10 +5710,10 @@
         <v>76</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>59</v>
@@ -5718,15 +5728,15 @@
         <v>31</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K84" s="10"/>
       <c r="L84" s="12"/>
       <c r="M84" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5734,13 +5744,13 @@
         <v>77</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F85" s="11" t="s">
         <v>72</v>
@@ -5752,17 +5762,17 @@
         <v>31</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K85" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L85" s="12"/>
       <c r="M85" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5770,13 +5780,13 @@
         <v>78</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>86</v>
@@ -5794,11 +5804,11 @@
         <v>31</v>
       </c>
       <c r="K86" s="10" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L86" s="12"/>
       <c r="M86" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5806,10 +5816,10 @@
         <v>79</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>31</v>
@@ -5830,11 +5840,11 @@
         <v>31</v>
       </c>
       <c r="K87" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L87" s="12"/>
       <c r="M87" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5842,33 +5852,33 @@
         <v>80</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F88" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K88" s="10"/>
       <c r="L88" s="12"/>
       <c r="M88" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5876,10 +5886,10 @@
         <v>81</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>31</v>
@@ -5888,10 +5898,10 @@
         <v>86</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I89" s="10" t="s">
         <v>31</v>
@@ -5900,11 +5910,11 @@
         <v>31</v>
       </c>
       <c r="K89" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L89" s="12"/>
       <c r="M89" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5912,10 +5922,10 @@
         <v>82</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>59</v>
@@ -5933,12 +5943,12 @@
         <v>176</v>
       </c>
       <c r="J90" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K90" s="10"/>
       <c r="L90" s="12"/>
       <c r="M90" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5946,10 +5956,10 @@
         <v>83</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>59</v>
@@ -5958,21 +5968,21 @@
         <v>29</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K91" s="10"/>
       <c r="L91" s="12"/>
       <c r="M91" s="13" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5980,22 +5990,22 @@
         <v>84</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G92" s="10" t="s">
         <v>175</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I92" s="10" t="s">
         <v>31</v>
@@ -6004,11 +6014,11 @@
         <v>31</v>
       </c>
       <c r="K92" s="10" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L92" s="12"/>
       <c r="M92" s="13" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6016,35 +6026,35 @@
         <v>85</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F93" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K93" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L93" s="12"/>
       <c r="M93" s="13" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6052,10 +6062,10 @@
         <v>86</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>59</v>
@@ -6064,21 +6074,21 @@
         <v>29</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K94" s="10"/>
       <c r="L94" s="12"/>
       <c r="M94" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6086,35 +6096,35 @@
         <v>87</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F95" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K95" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L95" s="12"/>
       <c r="M95" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6122,10 +6132,10 @@
         <v>88</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>59</v>
@@ -6140,15 +6150,15 @@
         <v>31</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K96" s="10"/>
       <c r="L96" s="12"/>
       <c r="M96" s="13" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6156,10 +6166,10 @@
         <v>89</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>59</v>
@@ -6174,15 +6184,15 @@
         <v>31</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K97" s="10"/>
       <c r="L97" s="12"/>
       <c r="M97" s="13" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6190,13 +6200,13 @@
         <v>90</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F98" s="11" t="s">
         <v>29</v>
@@ -6208,15 +6218,15 @@
         <v>31</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K98" s="10"/>
       <c r="L98" s="12"/>
       <c r="M98" s="13" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6224,13 +6234,13 @@
         <v>91</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F99" s="11" t="s">
         <v>29</v>
@@ -6242,15 +6252,15 @@
         <v>31</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K99" s="10"/>
       <c r="L99" s="12"/>
       <c r="M99" s="13" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6258,13 +6268,13 @@
         <v>92</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>29</v>
@@ -6276,15 +6286,15 @@
         <v>31</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K100" s="10"/>
       <c r="L100" s="12"/>
       <c r="M100" s="13" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6292,13 +6302,13 @@
         <v>93</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F101" s="11" t="s">
         <v>29</v>
@@ -6310,15 +6320,15 @@
         <v>31</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K101" s="10"/>
       <c r="L101" s="12"/>
       <c r="M101" s="13" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6326,13 +6336,13 @@
         <v>94</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>29</v>
@@ -6344,15 +6354,15 @@
         <v>31</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K102" s="10"/>
       <c r="L102" s="12"/>
       <c r="M102" s="13" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6360,10 +6370,10 @@
         <v>95</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>59</v>
@@ -6378,15 +6388,15 @@
         <v>31</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K103" s="10"/>
       <c r="L103" s="12"/>
       <c r="M103" s="13" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6394,10 +6404,10 @@
         <v>96</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>59</v>
@@ -6412,15 +6422,15 @@
         <v>31</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J104" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K104" s="10"/>
       <c r="L104" s="12"/>
       <c r="M104" s="13" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6428,10 +6438,10 @@
         <v>97</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>59</v>
@@ -6446,17 +6456,17 @@
         <v>31</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J105" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K105" s="10" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L105" s="12"/>
       <c r="M105" s="13" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6464,10 +6474,10 @@
         <v>98</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>59</v>
@@ -6482,15 +6492,15 @@
         <v>31</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K106" s="10"/>
       <c r="L106" s="12"/>
       <c r="M106" s="13" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6498,31 +6508,31 @@
         <v>99</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F107" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H107" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L107" s="12"/>
       <c r="M107" s="13" t="s">
@@ -6534,10 +6544,10 @@
         <v>100</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>59</v>
@@ -6552,15 +6562,15 @@
         <v>31</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="K108" s="10"/>
       <c r="L108" s="12"/>
       <c r="M108" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6568,13 +6578,13 @@
         <v>101</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F109" s="11" t="s">
         <v>29</v>
@@ -6586,10 +6596,10 @@
         <v>31</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K109" s="10"/>
       <c r="L109" s="12"/>
@@ -6602,13 +6612,13 @@
         <v>102</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F110" s="11" t="s">
         <v>29</v>
@@ -6623,12 +6633,12 @@
         <v>176</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K110" s="10"/>
       <c r="L110" s="12"/>
       <c r="M110" s="13" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6636,10 +6646,10 @@
         <v>103</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>59</v>
@@ -6654,15 +6664,15 @@
         <v>31</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K111" s="10"/>
       <c r="L111" s="12"/>
       <c r="M111" s="13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6670,10 +6680,10 @@
         <v>104</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>59</v>
@@ -6688,15 +6698,15 @@
         <v>31</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J112" s="10" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K112" s="10"/>
       <c r="L112" s="12"/>
       <c r="M112" s="13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6704,13 +6714,13 @@
         <v>105</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F113" s="11" t="s">
         <v>72</v>
@@ -6722,17 +6732,17 @@
         <v>31</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K113" s="10" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="L113" s="12"/>
       <c r="M113" s="13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6740,10 +6750,10 @@
         <v>106</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>59</v>
@@ -6758,10 +6768,10 @@
         <v>31</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K114" s="10"/>
       <c r="L114" s="12"/>
@@ -6774,13 +6784,13 @@
         <v>107</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F115" s="11" t="s">
         <v>29</v>
@@ -6792,15 +6802,15 @@
         <v>31</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K115" s="10"/>
       <c r="L115" s="12"/>
       <c r="M115" s="13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6808,10 +6818,10 @@
         <v>108</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>59</v>
@@ -6826,15 +6836,15 @@
         <v>31</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K116" s="10"/>
       <c r="L116" s="12"/>
       <c r="M116" s="13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6842,10 +6852,10 @@
         <v>109</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>59</v>
@@ -6860,15 +6870,15 @@
         <v>31</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K117" s="10"/>
       <c r="L117" s="12"/>
       <c r="M117" s="13" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6876,13 +6886,13 @@
         <v>110</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F118" s="11" t="s">
         <v>29</v>
@@ -6894,15 +6904,15 @@
         <v>31</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K118" s="10"/>
       <c r="L118" s="12"/>
       <c r="M118" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6910,13 +6920,13 @@
         <v>111</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F119" s="11" t="s">
         <v>29</v>
@@ -6928,17 +6938,17 @@
         <v>31</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K119" s="10" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L119" s="12"/>
       <c r="M119" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6946,13 +6956,13 @@
         <v>112</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F120" s="11" t="s">
         <v>29</v>
@@ -6964,15 +6974,15 @@
         <v>31</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="K120" s="10"/>
       <c r="L120" s="12"/>
       <c r="M120" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6980,13 +6990,13 @@
         <v>113</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F121" s="11" t="s">
         <v>29</v>
@@ -6998,15 +7008,15 @@
         <v>31</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J121" s="10" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K121" s="10"/>
       <c r="L121" s="12"/>
       <c r="M121" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7014,13 +7024,13 @@
         <v>114</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F122" s="11" t="s">
         <v>29</v>
@@ -7032,17 +7042,17 @@
         <v>31</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="J122" s="10" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K122" s="10" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L122" s="12"/>
       <c r="M122" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7050,13 +7060,13 @@
         <v>115</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F123" s="11" t="s">
         <v>29</v>
@@ -7068,15 +7078,15 @@
         <v>31</v>
       </c>
       <c r="I123" s="10" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K123" s="10"/>
       <c r="L123" s="12"/>
       <c r="M123" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7084,13 +7094,13 @@
         <v>116</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F124" s="11" t="s">
         <v>29</v>
@@ -7102,15 +7112,15 @@
         <v>31</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K124" s="10"/>
       <c r="L124" s="12"/>
       <c r="M124" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7118,10 +7128,10 @@
         <v>117</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>59</v>
@@ -7130,21 +7140,21 @@
         <v>29</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K125" s="10"/>
       <c r="L125" s="12"/>
       <c r="M125" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7152,25 +7162,25 @@
         <v>118</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F126" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G126" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J126" s="10" t="s">
         <v>115</v>
@@ -7178,7 +7188,7 @@
       <c r="K126" s="10"/>
       <c r="L126" s="12"/>
       <c r="M126" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7186,33 +7196,33 @@
         <v>119</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F127" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="K127" s="10"/>
       <c r="L127" s="12"/>
       <c r="M127" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7220,10 +7230,10 @@
         <v>120</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>59</v>
@@ -7232,21 +7242,21 @@
         <v>29</v>
       </c>
       <c r="G128" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H128" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K128" s="10"/>
       <c r="L128" s="12"/>
       <c r="M128" s="13" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7254,35 +7264,35 @@
         <v>121</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F129" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K129" s="10" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L129" s="12"/>
       <c r="M129" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7290,33 +7300,33 @@
         <v>122</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F130" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G130" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K130" s="10"/>
       <c r="L130" s="12"/>
       <c r="M130" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7324,33 +7334,33 @@
         <v>123</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F131" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="K131" s="10"/>
       <c r="L131" s="12"/>
       <c r="M131" s="13" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7358,33 +7368,33 @@
         <v>124</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="F132" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G132" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I132" s="10" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="K132" s="10"/>
       <c r="L132" s="12"/>
       <c r="M132" s="13" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7392,33 +7402,33 @@
         <v>125</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F133" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="J133" s="10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K133" s="10"/>
       <c r="L133" s="12"/>
       <c r="M133" s="13" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7426,33 +7436,33 @@
         <v>126</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F134" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G134" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K134" s="10"/>
       <c r="L134" s="12"/>
       <c r="M134" s="13" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7460,10 +7470,10 @@
         <v>127</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>59</v>
@@ -7472,21 +7482,21 @@
         <v>29</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J135" s="10" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K135" s="10"/>
       <c r="L135" s="12"/>
       <c r="M135" s="13" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7494,22 +7504,22 @@
         <v>128</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="F136" s="11" t="s">
         <v>86</v>
       </c>
       <c r="G136" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H136" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I136" s="10" t="s">
         <v>31</v>
@@ -7518,7 +7528,7 @@
         <v>31</v>
       </c>
       <c r="K136" s="10" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L136" s="12"/>
       <c r="M136" s="13" t="s">
@@ -7530,71 +7540,71 @@
         <v>129</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="F137" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K137" s="10" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L137" s="12"/>
       <c r="M137" s="13" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B138" s="9" t="n">
         <v>130</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="F138" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G138" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H138" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I138" s="10" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="J138" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K138" s="10" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L138" s="12"/>
       <c r="M138" s="13" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7602,35 +7612,35 @@
         <v>131</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F139" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H139" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="K139" s="10" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L139" s="12"/>
       <c r="M139" s="13" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7638,35 +7648,35 @@
         <v>132</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F140" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G140" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H140" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I140" s="10" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="J140" s="10" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K140" s="10" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L140" s="12"/>
       <c r="M140" s="13" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7674,33 +7684,33 @@
         <v>133</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F141" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H141" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I141" s="10" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="J141" s="10" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K141" s="10"/>
       <c r="L141" s="12"/>
       <c r="M141" s="13" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7708,105 +7718,101 @@
         <v>134</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F142" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G142" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H142" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I142" s="10" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="K142" s="10"/>
       <c r="L142" s="12"/>
       <c r="M142" s="13" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B143" s="9" t="n">
         <v>135</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I143" s="10" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>598</v>
-      </c>
-      <c r="K143" s="10" t="s">
-        <v>599</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="K143" s="10"/>
       <c r="L143" s="12"/>
       <c r="M143" s="13" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B144" s="9" t="n">
         <v>136</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G144" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H144" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I144" s="10" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="J144" s="10" t="s">
-        <v>603</v>
-      </c>
-      <c r="K144" s="10" t="s">
-        <v>604</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="K144" s="10"/>
       <c r="L144" s="12"/>
       <c r="M144" s="13" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7814,10 +7820,10 @@
         <v>137</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>59</v>
@@ -7826,21 +7832,21 @@
         <v>29</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I145" s="10" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="J145" s="10" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K145" s="10"/>
       <c r="L145" s="12"/>
       <c r="M145" s="13" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7848,10 +7854,10 @@
         <v>138</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E146" s="10" t="s">
         <v>59</v>
@@ -7860,65 +7866,63 @@
         <v>29</v>
       </c>
       <c r="G146" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H146" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J146" s="10" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K146" s="10"/>
       <c r="L146" s="12"/>
       <c r="M146" s="13" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B147" s="9" t="n">
         <v>139</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F147" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H147" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I147" s="10" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="J147" s="10" t="s">
-        <v>619</v>
-      </c>
-      <c r="K147" s="10" t="s">
         <v>620</v>
       </c>
+      <c r="K147" s="10"/>
       <c r="L147" s="12"/>
       <c r="M147" s="13" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B148" s="9" t="n">
         <v>140</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D148" s="10" t="s">
         <v>621</v>
@@ -7927,10 +7931,10 @@
         <v>622</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H148" s="10" t="s">
         <v>31</v>
@@ -7941,48 +7945,44 @@
       <c r="J148" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="K148" s="10" t="s">
-        <v>625</v>
-      </c>
+      <c r="K148" s="10"/>
       <c r="L148" s="12"/>
       <c r="M148" s="13" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B149" s="9" t="n">
         <v>141</v>
       </c>
       <c r="C149" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="D149" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="D149" s="10" t="s">
+      <c r="E149" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="E149" s="10" t="s">
+      <c r="F149" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G149" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="H149" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I149" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="F149" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G149" s="10" t="s">
-        <v>569</v>
-      </c>
-      <c r="H149" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I149" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="J149" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K149" s="10" t="s">
         <v>630</v>
       </c>
+      <c r="K149" s="10"/>
       <c r="L149" s="12"/>
       <c r="M149" s="13" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8002,7 +8002,7 @@
         <v>29</v>
       </c>
       <c r="G150" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H150" s="10" t="s">
         <v>31</v>
@@ -8019,7 +8019,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B151" s="9" t="n">
         <v>143</v>
       </c>
@@ -8033,26 +8033,26 @@
         <v>638</v>
       </c>
       <c r="F151" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H151" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I151" s="10" t="s">
-        <v>570</v>
+        <v>639</v>
       </c>
       <c r="J151" s="10" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K151" s="10" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L151" s="12"/>
       <c r="M151" s="13" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8060,10 +8060,10 @@
         <v>144</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>59</v>
@@ -8072,23 +8072,23 @@
         <v>29</v>
       </c>
       <c r="G152" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H152" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I152" s="10" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J152" s="10" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K152" s="10" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L152" s="12"/>
       <c r="M152" s="13" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8096,10 +8096,10 @@
         <v>145</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>59</v>
@@ -8108,93 +8108,89 @@
         <v>29</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H153" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I153" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="K153" s="10"/>
       <c r="L153" s="12"/>
       <c r="M153" s="13" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B154" s="9" t="n">
         <v>146</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E154" s="10" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G154" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H154" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I154" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>654</v>
-      </c>
-      <c r="K154" s="10" t="s">
         <v>655</v>
       </c>
+      <c r="K154" s="10"/>
       <c r="L154" s="12"/>
       <c r="M154" s="13" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B155" s="9" t="n">
         <v>147</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D155" s="10" t="s">
         <v>656</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>31</v>
+        <v>657</v>
       </c>
       <c r="F155" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H155" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I155" s="10" t="s">
-        <v>31</v>
+        <v>658</v>
       </c>
       <c r="J155" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K155" s="10" t="s">
-        <v>361</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="K155" s="10"/>
       <c r="L155" s="12"/>
       <c r="M155" s="13" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8202,10 +8198,10 @@
         <v>148</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="E156" s="10" t="s">
         <v>59</v>
@@ -8214,23 +8210,23 @@
         <v>29</v>
       </c>
       <c r="G156" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H156" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I156" s="10" t="s">
-        <v>623</v>
+        <v>663</v>
       </c>
       <c r="J156" s="10" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K156" s="10" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="L156" s="12"/>
       <c r="M156" s="13" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8238,13 +8234,13 @@
         <v>149</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="F157" s="11" t="s">
         <v>29</v>
@@ -8256,13 +8252,13 @@
         <v>31</v>
       </c>
       <c r="I157" s="10" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="J157" s="10" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K157" s="10" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="L157" s="12"/>
       <c r="M157" s="13" t="s">
@@ -8274,13 +8270,13 @@
         <v>150</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="E158" s="10" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="F158" s="11" t="s">
         <v>29</v>
@@ -8292,10 +8288,10 @@
         <v>31</v>
       </c>
       <c r="I158" s="10" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="J158" s="10" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="K158" s="10"/>
       <c r="L158" s="12"/>
@@ -8353,7 +8349,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8361,7 +8357,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>29</v>
@@ -8370,13 +8366,13 @@
         <v>72</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>86</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8563,7 +8559,7 @@
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B11,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B11,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
@@ -8575,16 +8571,16 @@
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B11,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="19" t="n">
         <f aca="false">IF(C11&gt;0,D11/C11,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="17" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C12" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B12)</f>
@@ -8613,7 +8609,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="17" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C13" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B13)</f>
@@ -8642,7 +8638,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="17" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C14" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B14)</f>
@@ -8671,7 +8667,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C15" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B15)</f>
@@ -8700,7 +8696,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C16" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B16)</f>
@@ -8729,7 +8725,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B17)</f>
@@ -8758,7 +8754,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="17" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B18)</f>
@@ -8787,7 +8783,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="17" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C19" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B19)</f>
@@ -8816,7 +8812,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="17" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C20" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B20)</f>
@@ -8845,7 +8841,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="17" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B21)</f>
@@ -8874,7 +8870,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="17" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B22)</f>
@@ -8903,7 +8899,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="17" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B23)</f>
@@ -8932,7 +8928,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="17" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B24)</f>
@@ -8961,7 +8957,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="17" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C25" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B25)</f>
@@ -8990,7 +8986,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="17" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B26)</f>
@@ -9019,7 +9015,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="17" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C27" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B27)</f>
@@ -9048,7 +9044,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="17" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C28" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B28)</f>
@@ -9077,7 +9073,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="17" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C29" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B29)</f>
@@ -9106,7 +9102,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="17" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C30" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B30)</f>
@@ -9135,7 +9131,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="17" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C31" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B31)</f>
@@ -9164,7 +9160,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="17" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C32" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B32)</f>
@@ -9193,7 +9189,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="17" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C33" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B33)</f>
@@ -9222,7 +9218,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="17" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C34" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B34)</f>
@@ -9251,7 +9247,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="17" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C35" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B35)</f>
@@ -9280,7 +9276,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="17" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C36" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B36)</f>
@@ -9309,7 +9305,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="17" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C37" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B37)</f>
@@ -9338,7 +9334,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="17" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C38" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B38)</f>
@@ -9346,11 +9342,11 @@
       </c>
       <c r="D38" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B38,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B38,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B38,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9362,12 +9358,12 @@
       </c>
       <c r="H38" s="19" t="n">
         <f aca="false">IF(C38&gt;0,D38/C38,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="17" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C39" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B39)</f>
@@ -9396,7 +9392,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="17" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C40" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B40)</f>
@@ -9404,11 +9400,11 @@
       </c>
       <c r="D40" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B40,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B40,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B40,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9420,12 +9416,12 @@
       </c>
       <c r="H40" s="19" t="n">
         <f aca="false">IF(C40&gt;0,D40/C40,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="17" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C41" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B41)</f>
@@ -9454,7 +9450,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="17" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C42" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B42)</f>
@@ -9483,7 +9479,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="17" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C43" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B43)</f>
@@ -9491,11 +9487,11 @@
       </c>
       <c r="D43" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B43,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E43" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B43,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F43" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B43,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9507,12 +9503,12 @@
       </c>
       <c r="H43" s="19" t="n">
         <f aca="false">IF(C43&gt;0,D43/C43,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="17" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C44" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B44)</f>
@@ -9520,11 +9516,11 @@
       </c>
       <c r="D44" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B44,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B44,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B44,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9536,7 +9532,7 @@
       </c>
       <c r="H44" s="19" t="n">
         <f aca="false">IF(C44&gt;0,D44/C44,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9578,11 +9574,11 @@
       </c>
       <c r="D46" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B46,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B46,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B46,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9594,12 +9590,12 @@
       </c>
       <c r="H46" s="19" t="n">
         <f aca="false">IF(C46&gt;0,D46/C46,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="17" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C47" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B47)</f>
@@ -9628,7 +9624,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="17" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C48" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B48)</f>
@@ -9636,11 +9632,11 @@
       </c>
       <c r="D48" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B48,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B48,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B48,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9648,16 +9644,16 @@
       </c>
       <c r="G48" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B48,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="19" t="n">
         <f aca="false">IF(C48&gt;0,D48/C48,0)</f>
-        <v>0.333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="17" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C49" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B49)</f>
@@ -9686,7 +9682,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="20" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C50" s="21" t="n">
         <f aca="false">SUM(C5:C49)</f>
@@ -9694,11 +9690,11 @@
       </c>
       <c r="D50" s="21" t="n">
         <f aca="false">SUM(D5:D49)</f>
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">SUM(E5:E49)</f>
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F50" s="21" t="n">
         <f aca="false">SUM(F5:F49)</f>
@@ -9706,11 +9702,11 @@
       </c>
       <c r="G50" s="21" t="n">
         <f aca="false">SUM(G5:G49)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H50" s="22" t="n">
         <f aca="false">IF(C50&gt;0,D50/C50,0)</f>
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -9741,18 +9737,18 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="23" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>18</v>
@@ -9760,13 +9756,13 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>72</v>
@@ -9774,13 +9770,13 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="24" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>72</v>
@@ -9788,13 +9784,13 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="24" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>29</v>
@@ -9802,27 +9798,27 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="24" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>72</v>
@@ -9830,13 +9826,13 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>29</v>
@@ -9844,13 +9840,13 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>86</v>
@@ -9858,30 +9854,30 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -9930,15 +9926,15 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="26" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9946,7 +9942,7 @@
         <v>29</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9954,15 +9950,15 @@
         <v>72</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="26" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9970,7 +9966,7 @@
         <v>86</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9978,7 +9974,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9986,15 +9982,15 @@
         <v>22</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="26" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10002,15 +9998,15 @@
         <v>20</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="26" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
   </sheetData>

--- a/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
+++ b/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="726">
   <si>
     <t xml:space="preserve">Nibbl AI — Master Requirements Tracker</t>
   </si>
@@ -242,1477 +242,1483 @@
     <t xml:space="preserve">Product cards: image, name/flavor/size, rating, category, Product ID, receipt alias count, Edit</t>
   </si>
   <si>
-    <t xml:space="preserve">Cards with image, details, rating, Edit.</t>
+    <t xml:space="preserve">Cards per mockup: image, name, flavor · size, clickable ★ rating + review count (opens Review Management filtered to that product), category, Product ID, receipt alias count, Edit Product; product count + Add Product at the top.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click a card's rating; Review Management opens filtered to it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product identity: separate record per flavor/size with permanent Product ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One record per flavor / size (name may repeat across variants); Size + Unit + Pack Count; permanent per-brand Product ID (PRD-001…) assigned on save, backfilled for existing products in creation order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add / Edit Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create Vanilla 12 oz and Chocolate 12 oz under one name; each gets its own Product ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product description kept for AI review questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description sent to the AI for review questions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill the description.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2, #24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standardized, admin-managed categories; brands can request a category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category dropdown from Nibbl's admin-managed list (seeded with 10 standard categories) + Request category; Admin → Settings → Product Categories: add / hide categories and approve / reject brand requests (reason required to reject).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Dashboard + Admin Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add Product → Category; Admin → Settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request a category; approve it in Admin; it appears in the dropdown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional UPC / SKU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKU field stored.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter a SKU and save.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt matching aliases: retailer + receipt text + optional item code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt Matching table on Add / Edit: Retailer + Receipt Product Text + optional Item Code. A retailer limits the alias to that store's receipts; the item code matches when printed on the receipt. Aliases still save from manual review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add / Edit Product → Receipt Matching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add an alias with a retailer; a receipt from another store doesn't match it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2, #21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clickable rating opens Review Management filtered to the product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rating links to filtered Review Management.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product details → rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click a product rating.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add Product: same single-page fields as Edit; ID assigned on save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same form for add and edit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a product.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete Product: type DELETE; history preserved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmation + archive keeps reviews/redemptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit Product → Delete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete with and without typing DELETE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebate Campaigns List</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status tabs with counts (Draft, Pending Review, Scheduled, Active, Paused, Changes Requested, Ended)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status tabs on the rebate list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebate Campaigns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch tabs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'X of Y active campaigns used — Upgrade' banner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usage bar with plan name and Upgrade button to Plans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activate campaigns up to the limit; click Upgrade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign cards: image, claims, active claims, pending review, redemptions, rate, total spend, current cycle claims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cards with metrics and 'X of Y' current cycle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare a card with its detail page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#4, #7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create Rebate Campaign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① Basics: internal name, start/end, campaign image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebate → Create</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a draft.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">② Eligible products (search, select, same-category check)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product search and selection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select 3 products.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">③ Offer setup: Free / BOGO Free / Buy 1 Get 1 50% / Buy X Get $Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All four with locked reward math.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create one of each.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">④ Offer details &amp; shopper wording (suggested, editable, 100/250 limits) + locked system rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested wording + locked rules summary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit the headline.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑤ Retailer availability, Request/Add Retailer, up to 3 Featured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directory, add retailer, featured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a retailer; pick featured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑥ Receipt eligibility: Any Retailer / Retailer Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enforced on receipts; saved on claim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set Retailer Required; upload another store's receipt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑦ 25-Hour Claim Capacity (desired ÷ rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live calculation; cycles from activation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the calculated capacity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑧ Customer cooldown (none / 30 / 60 / 90 / one time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign-specific cooldown from approved redemption.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redeem, then try to claim again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#8, #12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery geography (Nationwide / States / ZIP + radius)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All three, multiple areas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set ZIP radius; test from outside it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta Pixel tracking on/off (validated Pixel ID only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-campaign switch; Pixel from Settings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Dashboard + Shopper Website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turn tracking on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel validation is a format check.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live shopper preview (same data as published offer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live preview in builder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit and watch the preview.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save Draft / Submit for Nibbl Review; revisions keep approved version live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full approval workflow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign page; Admin → Approvals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit, request changes, approve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#7, #44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing reservation rule snapshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each claim keeps its terms.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend / API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edit a live campaign; old claim unchanged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offer Type Inputs &amp; Shopper Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reward math per offer type, net eligible price, rounding; shopper output sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend / API + Shopper Website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → offer page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare offer page with campaign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign Detail Page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① Status · ② Summary + Preview Offer · ④ Performance · ⑤ Current cycle · ⑥ Review activity · ⑦ Actions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All sections.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebate → View Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a campaign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">③ Assets: URL, QR, Open Preview, Download QR (PNG + high-res), 'don't distribute until approved'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL, QR and download.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign page → Assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Download the QR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect on Existing Reservations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign goes live; limit reached → Temporarily Unavailable; expired claims never restore capacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill capacity; claim shows unavailable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserved reward funding (reserve max, pay actual, return difference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet → Reserved Funds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim and redeem; check the ledger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only Nibbl admin may cancel an existing reservation, with a reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Shoppers → Claims &amp; Reviews → Cancel claim: reason required; the claim closes, the brand's reserved funds return, and the cancel is audit-logged. Brands can't cancel claims.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin Dashboard + Backend / API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Shoppers → shopper → Claims &amp; Reviews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel an open claim with a reason; the brand's Reserved Funds drop by that claim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location before discovery (allow location or ZIP; never unfiltered; don't re-ask)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location gate, saved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper Website + Backend / API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API ready — app developer to build/confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open signed out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geographic eligibility gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only eligible campaigns shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → For You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change ZIP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranking: Base CVR × Store Match × Brand Interest (admin values)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend / API + Admin Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change a multiplier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign cards on For You (not product cards), category tabs, up to 24 per category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign cards with category tabs.</t>
   </si>
   <si>
     <t xml:space="preserve">In Progress</t>
   </si>
   <si>
-    <t xml:space="preserve">Compare a card with the Master mockup.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alias count on the card to confirm against the mockup.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product identity: separate record per flavor/size with permanent Product ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flavor, format, size fields; ID assigned on save.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add / Edit Product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create two sizes of one product.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Separate Unit and Pack Count fields from the mockup aren't built (size is one field).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product description kept for AI review questions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description sent to the AI for review questions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fill the description.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#2, #24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standardized, admin-managed categories; brands can request a category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category is free text today.</t>
+    <t xml:space="preserve">Browse a category.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-per-category cap and 'N eligible products' line to confirm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retailer match = ranking boost; Any Retailer / Retailer Required verification (eligible / unclear → manual / ineligible)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload receipts from different stores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#10, #19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct entry: QR / Meta ad / URL bypasses geography only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open in a private window.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign-level suppression (never brand-wide)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim one campaign of a brand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper Rebate Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign details: products + ratings, Where to Buy, receipt eligibility, max rebate, offer eligibility, Going fast, share, save, Claim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offer page with all items.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper Website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → offer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open an offer; share and save.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#5, #10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserve Offer: prefill email/phone (collect if logged out), two required consents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both consents required.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → offer → Claim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim without consents → pop-up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logged-out shoppers must sign in first (Master allows collecting email/phone on this step).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm Reservation screen: slot X of 5, exact deadline, Confirm &amp; Reserve (slot consumed only here)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot use shown on Reserve Offer; separate Confirm screen with product, retailer, reward, exact deadline and resulting slot use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → offer → Continue → Confirm &amp; Reserve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim an offer; check the deadline is 7 days out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reservation eligibility checked before a claim slot is consumed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All checks (consent, slots, already claimed, cooldown, dates, capacity, funds) run before the slot is used.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered by automated tests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#17, #18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active claim slots (5) — occupied until approval, final rejection or expiry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → My Rewards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim to the limit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Action Prompt: carousel, Submit Receipt + time left, Save for Later, My Offers badge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → home; header badge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim, then return home.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebate restriction pop-ups (10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All with own code; consent, slots, claimed, cooldown, one-time, not started, paused, capacity, funds; retailer shown on offer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger each case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align titles/buttons exactly with the Master pop-up mockup (e.g. 'Review &amp; Accept', 'N days remaining', 'View Eligible Retailers').</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt Submission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit inside the active campaign: requirements list, take/choose photo, review before submit, submitted state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-claim flow: Receipt Requirements (from the claim's locked terms), Take / Choose Photo, Review Your Receipt, Receipt submitted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → My Rewards → Upload receipt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload a receipt for a claim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt Validation &amp; Routing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture date/time, retailer, transaction no., item, qty, net price, tax, total; clear date/retailer fail → reject; uncertain → manual; unreadable → new photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload clear / unclear / wrong-date receipts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCR = AI service.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#19, #21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplicate receipt + quantity allocation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload the same receipt twice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt Outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One resubmission before the original deadline (deadline never restarts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First clear date/retailer rejection keeps the claim open with one resubmission; the second is final (claim closed, slot released). Purchase must be on or after the claim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload a receipt dated before the claim, then another.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outcome messages: accepted, manual review, unreadable, date, retailer, final rejection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master outcome screens: Purchase verified, Manual review, We couldn't read it, Date / Retailer does not qualify (with one resubmission), Final rejection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → after submitting a receipt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger each outcome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-app + email decision notifications are tracked in Notifications &amp; Reminders.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notifications &amp; Reminders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt reminders 48h and 12h before the exact deadline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled job sends both reminders.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reservation confirmation, receipt submitted, approval/rejection (in-app + email), claim expiration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All five sent immediately in-app; approval and rejection also emailed (SES).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → notifications; email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim, upload, get approved/rejected, let a claim expire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push notification delivery (FCM / APNs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push is a placeholder today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting on client Firebase Workload Identity setup (EC2 role sent).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Manual Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① Claim &amp; customer (email visible on every plan) · ② Full receipt viewer (zoom/rotate/download) · ③ Locked requirements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redemptions → Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a pending receipt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">④ Select line · ⑤ Confirm mapping + corrections (audit) · ⑥ Optional alias · ⑦ Calculated reward, rejection reasons, internal note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approve with alias; reject with reason.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Redemptions Page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① Summary (pending, approved, rejected, total paid) · ② Status tabs · ⑤ Priority queue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redemptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#21, #22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">③ Search &amp; filters (campaign, product, status, submitted date)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search, campaign, product (via campaign products), status tabs, date range.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter by campaign and product.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑥ Pagination &amp; Export CSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redemptions → Export CSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Export.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven-day automatic approval (max reward, labelled, no alias, slot released)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check countdown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPIs: total, pending 1–3★ response, average rating, review spend, cost per review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All five KPIs; spend from the wallet ledger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviews → Review Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare spend with the Wallet ledger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabs (All, Published, 7-Day Hold, Flagged, Removed) + date range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabs with counts + date range + keyword search.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filters: rating, retailer, product, region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All four (retailer from the receipt, region from the shopper's state).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter by retailer and region.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review details: answers, final text, receipt evidence + gating summary, customer contact for service recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side panel with answers, receipt, gating summary, masked email + copy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Management → review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#26, #33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low-rating response: countdown, Contact Customer, Add Brand Response, Flag for Removal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live countdown, Contact Customer (email), response, flag.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a 2★ held review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flag reasons per Master (wrong product, unrelated, spam/fraud, PII, profanity, prohibited claim, other) + audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master's 7 reasons, 500-char details, audit log.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Management → Flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flag a review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Export: Download CSV + Download Reviews; API integration Coming Soon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSV + readable reviews file, both with disclosure; API Coming Soon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Management → Export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Download both.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create Review Campaign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basics (required image), eligible products, controls, locked rules &amp; cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviews → Create</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a review campaign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand question pool: add, suggest, Test Review Chat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Question pool: add, remove, ✨ Suggest Questions, and Test Review Chat (the same planned questions with answer chips and the AI draft; nothing saved or paid).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Campaigns → Create / campaign page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run Test Review Chat to the draft.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save Draft / Submit for Nibbl Review (published after review)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save Draft / Submit for Nibbl Review; Admin → Campaign Approvals → Review campaigns tab: Approve / Request changes / Reject (comment required); brand sees status + Nibbl's comment and resubmits. Approved campaigns can be paused and resumed. Campaigns live before this release were grandfathered as approved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Campaigns; Admin → Campaign Approvals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit a campaign, request changes in Admin, resubmit, approve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live shopper preview (mobile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live mobile preview of the shopper's review card (campaign image, Share your voice, $1 reward, 30 days left, Purchase verified, Claim $1) updates as the brand edits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change the image / products; the preview updates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper Review Opportunity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Offers: Review Rewards card (Claim $1, Save for Later)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review cards in the carousel and My Rewards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get a receipt verified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Confirmed · Multiple Matches · Missing Consent · Share Your Voice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website: review card (Share your voice · $1 · days left · Claim $1) → Product Confirmed (or This isn't my product) → Multiple Matches when receipt wording fits several variants → Missing Consent only when missing → Share Your Voice → chat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → My Offers → review card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy a product sold in two flavors under one name; pick the right one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile app screens are the app developer's.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer rules: scan all lines, 0/1/many opportunities, cooldown per shopper+product, $1 reserve, no second verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Chat Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product context loaded; rotating brand question; generated title &amp; review; edit; regenerate; final approval; $1 at any rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → review chat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete a review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five adaptive product questions with suggested answer chips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed AI questions today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adaptive questions wait on the AI service endpoint; suggested-answer chips not built.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separate 'recommend' and 'purchase again' questions; title 100 / body 500 limits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separate recommend and buy-again questions with Yes, definitely / Maybe / No chips (answers saved as would-recommend / would-buy-again); title ≤ 100 and body ≤ 500 with counters, AI drafts trimmed to fit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete a review; check the counters and chips.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratings &amp; Reviews Display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratings per product in campaign details; all reviews with sorting; review details + brand response; helpful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → offer → reviews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort and mark helpful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviews overview: rating, breakdown, % recommend, % would buy again, AI summary (positives + improvement)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rating, star breakdown, % recommend and % would buy again on the product reviews overview.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open an offer with reviews.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI summary (positives + improvement) waits on the AI service's summary endpoint; the backend hook is ready.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost &amp; Results · Customer &amp; Conversion · Campaign Performance (25-hour cycles)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare cost with the ledger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary, search &amp; filters, download opted-in, integrations Coming Soon, consent withdrawal rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter and download.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table: brand activity, site activity, open claims, cooldowns, last active, status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columns per Master: Customer, Contact, Brand Activity (claims / rebates / reviews), Site Activity (total claims / % completion / reviews), Open Claims, Cooldowns (days left), Last Active, Status (Active / Banned), View. Tabs: All, Open Claim, Active Cooldown, Completed Rebate, Banned, Inactive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Customers; check each column and tab against a shopper with an open claim and a cooldown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header (opt-in badges, status) + Ban Customer with reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header: name, contact, customer since, last active, Nibbl Opt-In + brand Opt-In badges, Active/Banned. Ban modal with reason (suspicious activity, altered receipts, abuse, other); banned shoppers can't claim or get review opportunities from the brand; existing claims stay valid. Lift Ban.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers → View → Ban Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ban with a reason; status shows Banned with the reason; Lift Ban restores it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relationship with brand · Nibbl activity totals · Recent activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relationship tiles (claims, completed rebates, conversion, rewards, reviews, open claims); Nibbl totals only (claims, completion, reviews, rewards) — other brands' data never shown; recent activity timeline for this brand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers → View</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a profile; totals match the shopper's history.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open claims · Cooldowns with Remove (confirmation + audit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open claims with days left. Rebate and review cooldowns with Remove → confirmation → cooldown cleared and an audit-log entry (who, when, which). Managers only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers → View → Cooldowns → Remove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove a cooldown; the shopper can claim/review again; the audit log shows the removal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redemption history: full receipt 30 days, then matching line only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redemption history with View receipt + days left for 30 days; afterwards only the matching line item(s) are shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers → View → Redemption History</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recent receipt shows View receipt; one older than 30 days shows Matching line only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Wallet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balances: Available, Reserved, Promotional (definitions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check balances.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign Funding: 7-day need vs Available, funded status, reservations split</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet → Campaign Funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activate a campaign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatic refill (Stripe): trigger 25%, fixed amount, recommendation, failure alert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet → Auto-refill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable auto-refill.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production still on Stripe test keys — switch to the live keys received from the client, then retest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending Overview + Weekly Statements + detailed ledger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Download a statement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request Refund (Available Cash refundable; reserved/promo not)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Owner requests up to Available Cash; Nibbl reviews in Admin → Refunds, refunds in Stripe, marks refunded (ledger refund entry) or rejects with a note.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Dashboard + Admin Dashboard + Backend / API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet → Request Refund; Admin → Refunds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request, then mark refunded in Admin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money is returned manually in Stripe, then recorded here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current plan, recommendation, plan options, scheduled changes, downgrade campaign choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedule and cancel a change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#33, #35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feature comparison table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side-by-side table (capacity, fees, review cost, identity, CSV, integrations, account manager, early access).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plans → Feature Comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Plans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan entitlement enforcement (campaign limits, customer identity, CSV, review cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limits, fees, CSV and identity enforced; Starter reviews show first name + last initial and email only on 1–3★.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered by tests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#33, #34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Profile (name, website, support email, time zone)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings → Brand Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change time zone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team &amp; Permissions (Owner / Admin / Viewer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings → Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invite a Viewer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notifications per member (Email + SMS): wallet below 25%, auto-refill failed, campaign paused, exhausted early, new negative review, weekly summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master's six notifications (+ campaign approvals, receipts to review) all sent in-app + email per member preference.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings → Notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toggle and trigger each.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS toggles are stored; SMS sending waits on Klaviyo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking &amp; Attribution (Meta Pixel; Google/TikTok Coming Soon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings → Tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save a Pixel ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security: passwordless sign-in, active sessions, last sign-in, sign out others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passwordless (magic-link) sign-in active, sessions, last sign-in, sign out others.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings → Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign out another device.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account &amp; Support (Contact Nibbl Support, Owner-only closure, Klaviyo Coming Soon — Scale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log in as Owner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tag Generator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Static Coming Soon page (example artwork)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Onboarding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role gate (I'm a Brand / I'm a Shopper)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What brings you to Nibbl? — Explore Nibbl for Brands / View Deals; choice remembered on the device.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brand.joinnibbl.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public brand homepage + How it works / Reviews / Controls / Plans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master homepage: hero, Why Nibbl, How it works, Reviews, Controls, Plans ($39/$199/$999), promo note.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brand.joinnibbl.com/brand-landing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Browse the page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ entries are labels until FAQ pages exist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan → Create Account (contact, work email, phone, company, website, category, terms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan picker + registration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand site → Register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passwordless magic-link sign-in (link expires in 15 minutes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signup without a password (Send Magic Link); 15-minute one-time link signs you straight in; Sign In emails a sign-in link (password still available).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brand.joinnibbl.com → Register / Sign In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register, open the email link; sign in by link.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secure checkout: card required even when credits cover today; card saved for renewals; promo code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Card always required ($0 due saves it with a SetupIntent); card saved to the brand for renewals and auto-replenishment; promo code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After sign-up → Checkout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check out with a promo covering the plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retest after the Stripe live switch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account Activated page + First Dashboard (3 growth goals, 5 steps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welcome to Nibbl page (plan, slots, credits, card, growth toolkit, getting started) + 3 growth goals and the 5 launch steps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dashboard after checkout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finish checkout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet funding required before launch (7-day need + auto-replenishment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit is blocked until the Wallet covers the 7-day requirement and auto-replenishment is on; 'Fund your campaign before launch' pop-up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebate campaign → Submit for review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit with an empty wallet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper Wallet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet overview: available, pending approval, payout method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → Wallet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet activity with filters (rebates, reviews, referrals, withdrawals) + statuses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New /wallet/activity/: All / Rebates / Reviews / Referrals / Withdrawals tabs, grouped Pending / In progress / Available / Completed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → Wallet → Wallet Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reward details (timeline: submitted → under review → available)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reward Details pop-up with timeline, reward type, campaign, receipt date, reference.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → Wallet → tap an item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a pending rebate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payout methods: one PayPal/Venmo identity per account; locked; change via request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a payout method.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secure Withdrawal Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount → locked method → SMS code → confirm (checkbox) → requested status tracker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All five steps incl. any amount, locked method + Request a change, SMS, confirm checkbox, Requested / Processing / Paid tracker.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → Wallet → Withdraw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Withdraw a small amount.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS verification works on production (12 Oct). Do one real website withdrawal with the SMS step, then Completed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Additional review needed' popup; status stays Processing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pop-up with Got it; request shows Processing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → Wallet → Withdraw over the review threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Withdraw above $25.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Withdrawal failed / rejected balance handling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejected: full amount back to the balance with the reason. Failed (from PayPal results): retryable stays reserved (Retry), permanent returns the amount (Return to balance).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper Website + Admin Dashboard + Backend / API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → Wallet Activity; Admin → Withdrawals → Failed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Import a FAILED result, then Return to balance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refer a Friend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referral home, share link, share a product deal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code + copy, share sheet with joinnibbl.com/r/CODE, Share a product list (deal links carry the code), How it works.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → My Rewards → Refer a Friend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share the link; open it signed out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualification: join, claim, approved redemption, payout method, withdrawal — within 90 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-step qualification; only steps inside the 90-day window count; unfinished referrals expire (checked every 15 minutes).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend; Admin → Referrals → Expired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referral progress (earned, pending, invited; step X of 4; expires in N days; not eligible) + rules sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earned / Pending / Invited totals, per-friend Step X of 4 + next step, Expires in N days, Earned / Not eligible, Referral Rules sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → My Rewards → My referrals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check a friend's progress.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper Restriction Messages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplicate payout account (Request Review) · payout-method change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a duplicate PayPal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passwordless access to My Offers, Wallet and Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoppers sign in with a password.</t>
   </si>
   <si>
     <t xml:space="preserve">Planned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Dashboard + Admin Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin category list + 'Request category' not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional UPC / SKU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SKU field stored.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter a SKU and save.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipt matching aliases: retailer + receipt text + optional item code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aliases (receipt text) added on the product or saved in manual review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product → Aliases; Redemptions → review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add an alias and upload a matching receipt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alias retailer and item code fields not built (text only).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#2, #21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clickable rating opens Review Management filtered to the product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rating links to filtered Review Management.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product details → rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click a product rating.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add Product: same single-page fields as Edit; ID assigned on save</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same form for add and edit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add Product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add a product.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delete Product: type DELETE; history preserved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmation + archive keeps reviews/redemptions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edit Product → Delete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delete with and without typing DELETE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebate Campaigns List</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status tabs with counts (Draft, Pending Review, Scheduled, Active, Paused, Changes Requested, Ended)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status tabs on the rebate list.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebate Campaigns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switch tabs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'X of Y active campaigns used — Upgrade' banner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usage bar with plan name and Upgrade button to Plans.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activate campaigns up to the limit; click Upgrade.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign cards: image, claims, active claims, pending review, redemptions, rate, total spend, current cycle claims</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cards with metrics and 'X of Y' current cycle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare a card with its detail page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#4, #7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create Rebate Campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① Basics: internal name, start/end, campaign image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebate → Create</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a draft.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">② Eligible products (search, select, same-category check)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product search and selection.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select 3 products.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">③ Offer setup: Free / BOGO Free / Buy 1 Get 1 50% / Buy X Get $Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All four with locked reward math.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create one of each.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">④ Offer details &amp; shopper wording (suggested, editable, 100/250 limits) + locked system rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suggested wording + locked rules summary.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edit the headline.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⑤ Retailer availability, Request/Add Retailer, up to 3 Featured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directory, add retailer, featured.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add a retailer; pick featured.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⑥ Receipt eligibility: Any Retailer / Retailer Required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enforced on receipts; saved on claim.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set Retailer Required; upload another store's receipt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⑦ 25-Hour Claim Capacity (desired ÷ rate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live calculation; cycles from activation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check the calculated capacity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⑧ Customer cooldown (none / 30 / 60 / 90 / one time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign-specific cooldown from approved redemption.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redeem, then try to claim again.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#8, #12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discovery geography (Nationwide / States / ZIP + radius)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All three, multiple areas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set ZIP radius; test from outside it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meta Pixel tracking on/off (validated Pixel ID only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-campaign switch; Pixel from Settings.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Dashboard + Shopper Website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turn tracking on.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pixel validation is a format check.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live shopper preview (same data as published offer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live preview in builder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edit and watch the preview.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save Draft / Submit for Nibbl Review; revisions keep approved version live</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full approval workflow.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign page; Admin → Approvals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit, request changes, approve.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#7, #44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Existing reservation rule snapshot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each claim keeps its terms.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend / API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edit a live campaign; old claim unchanged.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Offer Type Inputs &amp; Shopper Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reward math per offer type, net eligible price, rounding; shopper output sources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend / API + Shopper Website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → offer page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare offer page with campaign.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign Detail Page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① Status · ② Summary + Preview Offer · ④ Performance · ⑤ Current cycle · ⑥ Review activity · ⑦ Actions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All sections.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebate → View Details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a campaign.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">③ Assets: URL, QR, Open Preview, Download QR (PNG + high-res), 'don't distribute until approved'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL, QR and download.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign page → Assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Download the QR.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effect on Existing Reservations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign goes live; limit reached → Temporarily Unavailable; expired claims never restore capacity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fill capacity; claim shows unavailable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserved reward funding (reserve max, pay actual, return difference)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet → Reserved Funds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim and redeem; check the ledger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only Nibbl admin may cancel an existing reservation, with a reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Shoppers → Claims &amp; Reviews → Cancel claim: reason required; the claim closes, the brand's reserved funds return, and the cancel is audit-logged. Brands can't cancel claims.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin Dashboard + Backend / API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Shoppers → shopper → Claims &amp; Reviews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cancel an open claim with a reason; the brand's Reserved Funds drop by that claim.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location before discovery (allow location or ZIP; never unfiltered; don't re-ask)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location gate, saved.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper Website + Backend / API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API ready — app developer to build/confirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open signed out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geographic eligibility gate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only eligible campaigns shown.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → For You</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change ZIP.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranking: Base CVR × Store Match × Brand Interest (admin values)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend / API + Admin Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Settings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change a multiplier.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign cards on For You (not product cards), category tabs, up to 24 per category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign cards with category tabs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Browse a category.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-per-category cap and 'N eligible products' line to confirm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retailer match = ranking boost; Any Retailer / Retailer Required verification (eligible / unclear → manual / ineligible)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload receipts from different stores.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#10, #19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct entry: QR / Meta ad / URL bypasses geography only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open in a private window.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign-level suppression (never brand-wide)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim one campaign of a brand.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper Rebate Flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign details: products + ratings, Where to Buy, receipt eligibility, max rebate, offer eligibility, Going fast, share, save, Claim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Offer page with all items.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper Website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → offer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open an offer; share and save.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#5, #10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserve Offer: prefill email/phone (collect if logged out), two required consents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both consents required.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → offer → Claim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim without consents → pop-up.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logged-out shoppers must sign in first (Master allows collecting email/phone on this step).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm Reservation screen: slot X of 5, exact deadline, Confirm &amp; Reserve (slot consumed only here)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slot use shown on Reserve Offer; separate Confirm screen with product, retailer, reward, exact deadline and resulting slot use.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → offer → Continue → Confirm &amp; Reserve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim an offer; check the deadline is 7 days out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reservation eligibility checked before a claim slot is consumed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All checks (consent, slots, already claimed, cooldown, dates, capacity, funds) run before the slot is used.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered by automated tests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#17, #18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active claim slots (5) — occupied until approval, final rejection or expiry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → My Rewards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim to the limit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return Action Prompt: carousel, Submit Receipt + time left, Save for Later, My Offers badge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → home; header badge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim, then return home.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebate restriction pop-ups (10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All with own code; consent, slots, claimed, cooldown, one-time, not started, paused, capacity, funds; retailer shown on offer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger each case.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align titles/buttons exactly with the Master pop-up mockup (e.g. 'Review &amp; Accept', 'N days remaining', 'View Eligible Retailers').</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipt Submission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit inside the active campaign: requirements list, take/choose photo, review before submit, submitted state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-claim flow: Receipt Requirements (from the claim's locked terms), Take / Choose Photo, Review Your Receipt, Receipt submitted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → My Rewards → Upload receipt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload a receipt for a claim.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipt Validation &amp; Routing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capture date/time, retailer, transaction no., item, qty, net price, tax, total; clear date/retailer fail → reject; uncertain → manual; unreadable → new photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload clear / unclear / wrong-date receipts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OCR = AI service.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#19, #21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duplicate receipt + quantity allocation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload the same receipt twice.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipt Outcomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One resubmission before the original deadline (deadline never restarts)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First clear date/retailer rejection keeps the claim open with one resubmission; the second is final (claim closed, slot released). Purchase must be on or after the claim.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload a receipt dated before the claim, then another.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outcome messages: accepted, manual review, unreadable, date, retailer, final rejection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master outcome screens: Purchase verified, Manual review, We couldn't read it, Date / Retailer does not qualify (with one resubmission), Final rejection.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → after submitting a receipt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger each outcome.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-app + email decision notifications are tracked in Notifications &amp; Reminders.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications &amp; Reminders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipt reminders 48h and 12h before the exact deadline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scheduled job sends both reminders.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reservation confirmation, receipt submitted, approval/rejection (in-app + email), claim expiration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All five sent immediately in-app; approval and rejection also emailed (SES).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → notifications; email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim, upload, get approved/rejected, let a claim expire.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Push notification delivery (FCM / APNs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Push is a placeholder today.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting on client Firebase Workload Identity setup (EC2 role sent).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Manual Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① Claim &amp; customer (email visible on every plan) · ② Full receipt viewer (zoom/rotate/download) · ③ Locked requirements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redemptions → Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a pending receipt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">④ Select line · ⑤ Confirm mapping + corrections (audit) · ⑥ Optional alias · ⑦ Calculated reward, rejection reasons, internal note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approve with alias; reject with reason.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Redemptions Page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① Summary (pending, approved, rejected, total paid) · ② Status tabs · ⑤ Priority queue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redemptions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#21, #22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">③ Search &amp; filters (campaign, product, status, submitted date)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search, campaign, product (via campaign products), status tabs, date range.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter by campaign and product.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⑥ Pagination &amp; Export CSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redemptions → Export CSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Export.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven-day automatic approval (max reward, labelled, no alias, slot released)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check countdown.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPIs: total, pending 1–3★ response, average rating, review spend, cost per review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All five KPIs; spend from the wallet ledger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviews → Review Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare spend with the Wallet ledger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabs (All, Published, 7-Day Hold, Flagged, Removed) + date range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabs with counts + date range + keyword search.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filters: rating, retailer, product, region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All four (retailer from the receipt, region from the shopper's state).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter by retailer and region.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review details: answers, final text, receipt evidence + gating summary, customer contact for service recovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Side panel with answers, receipt, gating summary, masked email + copy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Management → review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#26, #33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low-rating response: countdown, Contact Customer, Add Brand Response, Flag for Removal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live countdown, Contact Customer (email), response, flag.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a 2★ held review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flag reasons per Master (wrong product, unrelated, spam/fraud, PII, profanity, prohibited claim, other) + audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master's 7 reasons, 500-char details, audit log.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Management → Flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flag a review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Export: Download CSV + Download Reviews; API integration Coming Soon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSV + readable reviews file, both with disclosure; API Coming Soon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Management → Export</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Download both.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create Review Campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basics (required image), eligible products, controls, locked rules &amp; cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviews → Create</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a review campaign.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand question pool: add, suggest, Test Review Chat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add + suggest.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review campaign page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add and suggest questions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Test Review Chat' not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save Draft / Submit for Nibbl Review (published after review)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brands activate review campaigns directly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nibbl approval for review campaigns not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live shopper preview (mobile)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper Review Opportunity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Offers: Review Rewards card (Claim $1, Save for Later)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review cards in the carousel and My Rewards.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Get a receipt verified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Confirmed · Multiple Matches · Missing Consent · Share Your Voice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">These screens aren't built on the website (chat opens directly).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer rules: scan all lines, 0/1/many opportunities, cooldown per shopper+product, $1 reserve, no second verification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Chat Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product context loaded; rotating brand question; generated title &amp; review; edit; regenerate; final approval; $1 at any rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → review chat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete a review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Five adaptive product questions with suggested answer chips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed AI questions today.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adaptive questions wait on the AI service endpoint; suggested-answer chips not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Separate 'recommend' and 'purchase again' questions; title 100 / body 500 limits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One combined recommend question.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Split recommend vs repurchase; enforce 100/500 character limits.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratings &amp; Reviews Display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratings per product in campaign details; all reviews with sorting; review details + brand response; helpful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → offer → reviews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sort and mark helpful.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviews overview: rating, breakdown, % recommend, % would buy again, AI summary (positives + improvement)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rating, breakdown, % recommend.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open an offer with reviews.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'% would buy again' not built; AI summary waits on the AI service.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost &amp; Results · Customer &amp; Conversion · Campaign Performance (25-hour cycles)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare cost with the ledger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary, search &amp; filters, download opted-in, integrations Coming Soon, consent withdrawal rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter and download.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table: brand activity, site activity, open claims, cooldowns, last active, status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columns per Master: Customer, Contact, Brand Activity (claims / rebates / reviews), Site Activity (total claims / % completion / reviews), Open Claims, Cooldowns (days left), Last Active, Status (Active / Banned), View. Tabs: All, Open Claim, Active Cooldown, Completed Rebate, Banned, Inactive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Customers; check each column and tab against a shopper with an open claim and a cooldown.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header (opt-in badges, status) + Ban Customer with reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header: name, contact, customer since, last active, Nibbl Opt-In + brand Opt-In badges, Active/Banned. Ban modal with reason (suspicious activity, altered receipts, abuse, other); banned shoppers can't claim or get review opportunities from the brand; existing claims stay valid. Lift Ban.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customers → View → Ban Customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ban with a reason; status shows Banned with the reason; Lift Ban restores it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relationship with brand · Nibbl activity totals · Recent activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relationship tiles (claims, completed rebates, conversion, rewards, reviews, open claims); Nibbl totals only (claims, completion, reviews, rewards) — other brands' data never shown; recent activity timeline for this brand.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customers → View</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a profile; totals match the shopper's history.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open claims · Cooldowns with Remove (confirmation + audit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open claims with days left. Rebate and review cooldowns with Remove → confirmation → cooldown cleared and an audit-log entry (who, when, which). Managers only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customers → View → Cooldowns → Remove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remove a cooldown; the shopper can claim/review again; the audit log shows the removal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redemption history: full receipt 30 days, then matching line only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redemption history with View receipt + days left for 30 days; afterwards only the matching line item(s) are shown.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customers → View → Redemption History</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recent receipt shows View receipt; one older than 30 days shows Matching line only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Wallet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balances: Available, Reserved, Promotional (definitions)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check balances.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign Funding: 7-day need vs Available, funded status, reservations split</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet → Campaign Funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activate a campaign.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatic refill (Stripe): trigger 25%, fixed amount, recommendation, failure alert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet → Auto-refill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable auto-refill.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production still on Stripe test keys — switch to the live keys received from the client, then retest.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending Overview + Weekly Statements + detailed ledger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Download a statement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request Refund (Available Cash refundable; reserved/promo not)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Owner requests up to Available Cash; Nibbl reviews in Admin → Refunds, refunds in Stripe, marks refunded (ledger refund entry) or rejects with a note.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Dashboard + Admin Dashboard + Backend / API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet → Request Refund; Admin → Refunds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request, then mark refunded in Admin.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Money is returned manually in Stripe, then recorded here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current plan, recommendation, plan options, scheduled changes, downgrade campaign choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schedule and cancel a change.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#33, #35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feature comparison table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Side-by-side table (capacity, fees, review cost, identity, CSV, integrations, account manager, early access).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plans → Feature Comparison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Plans.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan entitlement enforcement (campaign limits, customer identity, CSV, review cost)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limits, fees, CSV and identity enforced; Starter reviews show first name + last initial and email only on 1–3★.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered by tests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#33, #34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Profile (name, website, support email, time zone)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings → Brand Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change time zone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team &amp; Permissions (Owner / Admin / Viewer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings → Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invite a Viewer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications per member (Email + SMS): wallet below 25%, auto-refill failed, campaign paused, exhausted early, new negative review, weekly summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master's six notifications (+ campaign approvals, receipts to review) all sent in-app + email per member preference.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings → Notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toggle and trigger each.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS toggles are stored; SMS sending waits on Klaviyo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking &amp; Attribution (Meta Pixel; Google/TikTok Coming Soon)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings → Tracking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save a Pixel ID.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security: passwordless sign-in, active sessions, last sign-in, sign out others</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passwordless (magic-link) sign-in active, sessions, last sign-in, sign out others.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings → Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sign out another device.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account &amp; Support (Contact Nibbl Support, Owner-only closure, Klaviyo Coming Soon — Scale)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log in as Owner.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tag Generator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Static Coming Soon page (example artwork)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open the page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Onboarding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role gate (I'm a Brand / I'm a Shopper)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What brings you to Nibbl? — Explore Nibbl for Brands / View Deals; choice remembered on the device.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brand.joinnibbl.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public brand homepage + How it works / Reviews / Controls / Plans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master homepage: hero, Why Nibbl, How it works, Reviews, Controls, Plans ($39/$199/$999), promo note.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brand.joinnibbl.com/brand-landing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Browse the page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAQ entries are labels until FAQ pages exist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan → Create Account (contact, work email, phone, company, website, category, terms)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan picker + registration.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand site → Register</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Register.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passwordless magic-link sign-in (link expires in 15 minutes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signup without a password (Send Magic Link); 15-minute one-time link signs you straight in; Sign In emails a sign-in link (password still available).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brand.joinnibbl.com → Register / Sign In</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Register, open the email link; sign in by link.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secure checkout: card required even when credits cover today; card saved for renewals; promo code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card always required ($0 due saves it with a SetupIntent); card saved to the brand for renewals and auto-replenishment; promo code.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After sign-up → Checkout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check out with a promo covering the plan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retest after the Stripe live switch.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account Activated page + First Dashboard (3 growth goals, 5 steps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Welcome to Nibbl page (plan, slots, credits, card, growth toolkit, getting started) + 3 growth goals and the 5 launch steps.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dashboard after checkout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finish checkout.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet funding required before launch (7-day need + auto-replenishment)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit is blocked until the Wallet covers the 7-day requirement and auto-replenishment is on; 'Fund your campaign before launch' pop-up.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebate campaign → Submit for review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit with an empty wallet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper Wallet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet overview: available, pending approval, payout method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → Wallet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet activity with filters (rebates, reviews, referrals, withdrawals) + statuses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New /wallet/activity/: All / Rebates / Reviews / Referrals / Withdrawals tabs, grouped Pending / In progress / Available / Completed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → Wallet → Wallet Activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reward details (timeline: submitted → under review → available)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reward Details pop-up with timeline, reward type, campaign, receipt date, reference.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → Wallet → tap an item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a pending rebate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payout methods: one PayPal/Venmo identity per account; locked; change via request</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add a payout method.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secure Withdrawal Flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amount → locked method → SMS code → confirm (checkbox) → requested status tracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All five steps incl. any amount, locked method + Request a change, SMS, confirm checkbox, Requested / Processing / Paid tracker.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → Wallet → Withdraw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Withdraw a small amount.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS verification works on production (12 Oct). Do one real website withdrawal with the SMS step, then Completed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Additional review needed' popup; status stays Processing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pop-up with Got it; request shows Processing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → Wallet → Withdraw over the review threshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Withdraw above $25.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Withdrawal failed / rejected balance handling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejected: full amount back to the balance with the reason. Failed (from PayPal results): retryable stays reserved (Retry), permanent returns the amount (Return to balance).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper Website + Admin Dashboard + Backend / API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → Wallet Activity; Admin → Withdrawals → Failed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Import a FAILED result, then Return to balance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refer a Friend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referral home, share link, share a product deal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Code + copy, share sheet with joinnibbl.com/r/CODE, Share a product list (deal links carry the code), How it works.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → My Rewards → Refer a Friend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share the link; open it signed out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualification: join, claim, approved redemption, payout method, withdrawal — within 90 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-step qualification; only steps inside the 90-day window count; unfinished referrals expire (checked every 15 minutes).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend; Admin → Referrals → Expired</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referral progress (earned, pending, invited; step X of 4; expires in N days; not eligible) + rules sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earned / Pending / Invited totals, per-friend Step X of 4 + next step, Expires in N days, Earned / Not eligible, Referral Rules sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → My Rewards → My referrals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check a friend's progress.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper Restriction Messages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duplicate payout account (Request Review) · payout-method change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add a duplicate PayPal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passwordless access to My Offers, Wallet and Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoppers sign in with a password.</t>
   </si>
   <si>
     <t xml:space="preserve">Passwordless shopper sign-in not built.</t>
@@ -3057,23 +3063,23 @@
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Completed")</f>
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Progress")</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Review")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Planned")</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5" s="5" t="n">
         <f aca="false">IF(C5&gt;0,D5/C5,0)</f>
-        <v>0.866666666666667</v>
+        <v>0.926666666666667</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3441,7 +3447,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="n">
         <v>10</v>
       </c>
@@ -3455,7 +3461,7 @@
         <v>71</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>30</v>
@@ -3467,17 +3473,15 @@
         <v>65</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="K18" s="10"/>
       <c r="L18" s="12"/>
       <c r="M18" s="13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="n">
         <v>11</v>
       </c>
@@ -3485,13 +3489,13 @@
         <v>65</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>51</v>
@@ -3500,14 +3504,12 @@
         <v>31</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>79</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="K19" s="10"/>
       <c r="L19" s="12"/>
       <c r="M19" s="13" t="s">
         <v>69</v>
@@ -3521,10 +3523,10 @@
         <v>65</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>29</v>
@@ -3536,18 +3538,18 @@
         <v>31</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K20" s="10"/>
       <c r="L20" s="12"/>
       <c r="M20" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="9" t="n">
         <v>13</v>
       </c>
@@ -3555,29 +3557,27 @@
         <v>65</v>
       </c>
       <c r="D21" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="J21" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>88</v>
-      </c>
+      <c r="K21" s="10"/>
       <c r="L21" s="12"/>
       <c r="M21" s="13" t="s">
         <v>31</v>
@@ -3591,10 +3591,10 @@
         <v>65</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>29</v>
@@ -3606,10 +3606,10 @@
         <v>31</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K22" s="10"/>
       <c r="L22" s="12"/>
@@ -3617,7 +3617,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="9" t="n">
         <v>15</v>
       </c>
@@ -3625,13 +3625,13 @@
         <v>65</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>51</v>
@@ -3640,17 +3640,15 @@
         <v>31</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>96</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="K23" s="10"/>
       <c r="L23" s="12"/>
       <c r="M23" s="13" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3661,10 +3659,10 @@
         <v>65</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>29</v>
@@ -3676,15 +3674,15 @@
         <v>31</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="K24" s="10"/>
       <c r="L24" s="12"/>
       <c r="M24" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3695,10 +3693,10 @@
         <v>65</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>29</v>
@@ -3710,10 +3708,10 @@
         <v>31</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K25" s="10"/>
       <c r="L25" s="12"/>
@@ -3729,10 +3727,10 @@
         <v>65</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>29</v>
@@ -3744,15 +3742,15 @@
         <v>31</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K26" s="10"/>
       <c r="L26" s="12"/>
       <c r="M26" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3760,13 +3758,13 @@
         <v>19</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>29</v>
@@ -3778,15 +3776,15 @@
         <v>31</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="K27" s="10"/>
       <c r="L27" s="12"/>
       <c r="M27" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3794,13 +3792,13 @@
         <v>20</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>29</v>
@@ -3812,15 +3810,15 @@
         <v>31</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K28" s="10"/>
       <c r="L28" s="12"/>
       <c r="M28" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3828,13 +3826,13 @@
         <v>21</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>29</v>
@@ -3846,15 +3844,15 @@
         <v>31</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K29" s="10"/>
       <c r="L29" s="12"/>
       <c r="M29" s="13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3862,10 +3860,10 @@
         <v>22</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>59</v>
@@ -3880,15 +3878,15 @@
         <v>31</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K30" s="10"/>
       <c r="L30" s="12"/>
       <c r="M30" s="13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3896,13 +3894,13 @@
         <v>23</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>29</v>
@@ -3914,15 +3912,15 @@
         <v>31</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K31" s="10"/>
       <c r="L31" s="12"/>
       <c r="M31" s="13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3930,13 +3928,13 @@
         <v>24</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>29</v>
@@ -3948,15 +3946,15 @@
         <v>31</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K32" s="10"/>
       <c r="L32" s="12"/>
       <c r="M32" s="13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3964,13 +3962,13 @@
         <v>25</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>29</v>
@@ -3982,15 +3980,15 @@
         <v>31</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K33" s="10"/>
       <c r="L33" s="12"/>
       <c r="M33" s="13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3998,13 +3996,13 @@
         <v>26</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>29</v>
@@ -4016,15 +4014,15 @@
         <v>31</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="K34" s="10"/>
       <c r="L34" s="12"/>
       <c r="M34" s="13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4032,13 +4030,13 @@
         <v>27</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>29</v>
@@ -4050,15 +4048,15 @@
         <v>31</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K35" s="10"/>
       <c r="L35" s="12"/>
       <c r="M35" s="13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4066,13 +4064,13 @@
         <v>28</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>29</v>
@@ -4084,15 +4082,15 @@
         <v>31</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="K36" s="10"/>
       <c r="L36" s="12"/>
       <c r="M36" s="13" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4100,13 +4098,13 @@
         <v>29</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>29</v>
@@ -4118,15 +4116,15 @@
         <v>31</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K37" s="10"/>
       <c r="L37" s="12"/>
       <c r="M37" s="13" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4134,13 +4132,13 @@
         <v>30</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>29</v>
@@ -4152,15 +4150,15 @@
         <v>31</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="K38" s="10"/>
       <c r="L38" s="12"/>
       <c r="M38" s="13" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4168,35 +4166,35 @@
         <v>31</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D39" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="J39" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="K39" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="J39" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="K39" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="L39" s="12"/>
       <c r="M39" s="13" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4204,13 +4202,13 @@
         <v>32</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>29</v>
@@ -4222,15 +4220,15 @@
         <v>31</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="K40" s="10"/>
       <c r="L40" s="12"/>
       <c r="M40" s="13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4238,33 +4236,33 @@
         <v>33</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K41" s="10"/>
       <c r="L41" s="12"/>
       <c r="M41" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4272,33 +4270,33 @@
         <v>34</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D42" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="J42" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="J42" s="10" t="s">
-        <v>177</v>
       </c>
       <c r="K42" s="10"/>
       <c r="L42" s="12"/>
       <c r="M42" s="13" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4306,10 +4304,10 @@
         <v>35</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>59</v>
@@ -4318,21 +4316,21 @@
         <v>29</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="K43" s="10"/>
       <c r="L43" s="12"/>
       <c r="M43" s="13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4340,13 +4338,13 @@
         <v>36</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>29</v>
@@ -4358,15 +4356,15 @@
         <v>31</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K44" s="10"/>
       <c r="L44" s="12"/>
       <c r="M44" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4374,13 +4372,13 @@
         <v>37</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>29</v>
@@ -4392,15 +4390,15 @@
         <v>31</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K45" s="10"/>
       <c r="L45" s="12"/>
       <c r="M45" s="13" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4408,10 +4406,10 @@
         <v>38</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>59</v>
@@ -4420,21 +4418,21 @@
         <v>29</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H46" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="K46" s="10"/>
       <c r="L46" s="12"/>
       <c r="M46" s="13" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4442,10 +4440,10 @@
         <v>39</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>59</v>
@@ -4454,21 +4452,21 @@
         <v>29</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="K47" s="10"/>
       <c r="L47" s="12"/>
       <c r="M47" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4476,28 +4474,28 @@
         <v>40</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D48" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="J48" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>205</v>
       </c>
       <c r="K48" s="10"/>
       <c r="L48" s="12"/>
@@ -4510,33 +4508,33 @@
         <v>41</v>
       </c>
       <c r="C49" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="I49" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="J49" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="F49" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="J49" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="K49" s="10"/>
       <c r="L49" s="12"/>
       <c r="M49" s="13" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4544,33 +4542,33 @@
         <v>42</v>
       </c>
       <c r="C50" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H50" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="D50" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>210</v>
-      </c>
       <c r="I50" s="10" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K50" s="10"/>
       <c r="L50" s="12"/>
       <c r="M50" s="13" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4578,10 +4576,10 @@
         <v>43</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>59</v>
@@ -4590,21 +4588,21 @@
         <v>29</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K51" s="10"/>
       <c r="L51" s="12"/>
       <c r="M51" s="13" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4612,35 +4610,35 @@
         <v>44</v>
       </c>
       <c r="C52" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="H52" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="I52" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="J52" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="K52" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="F52" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="J52" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="K52" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="L52" s="12"/>
       <c r="M52" s="13" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4648,10 +4646,10 @@
         <v>45</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>59</v>
@@ -4660,21 +4658,21 @@
         <v>29</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H53" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K53" s="10"/>
       <c r="L53" s="12"/>
       <c r="M53" s="13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4682,10 +4680,10 @@
         <v>46</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>59</v>
@@ -4694,21 +4692,21 @@
         <v>29</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K54" s="10"/>
       <c r="L54" s="12"/>
       <c r="M54" s="13" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4716,10 +4714,10 @@
         <v>47</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>59</v>
@@ -4728,21 +4726,21 @@
         <v>29</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K55" s="10"/>
       <c r="L55" s="12"/>
       <c r="M55" s="13" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4750,33 +4748,33 @@
         <v>48</v>
       </c>
       <c r="C56" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G56" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="H56" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I56" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="J56" s="10" t="s">
         <v>237</v>
-      </c>
-      <c r="F56" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H56" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="I56" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>240</v>
       </c>
       <c r="K56" s="10"/>
       <c r="L56" s="12"/>
       <c r="M56" s="13" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4784,35 +4782,35 @@
         <v>49</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D57" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="J57" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="K57" s="10" t="s">
         <v>243</v>
-      </c>
-      <c r="F57" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="I57" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="J57" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="K57" s="10" t="s">
-        <v>246</v>
       </c>
       <c r="L57" s="12"/>
       <c r="M57" s="13" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4820,33 +4818,33 @@
         <v>50</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D58" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="J58" s="10" t="s">
         <v>248</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="F58" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="J58" s="10" t="s">
-        <v>251</v>
       </c>
       <c r="K58" s="10"/>
       <c r="L58" s="12"/>
       <c r="M58" s="13" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4854,33 +4852,33 @@
         <v>51</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H59" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="K59" s="10"/>
       <c r="L59" s="12"/>
       <c r="M59" s="13" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4888,10 +4886,10 @@
         <v>52</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>59</v>
@@ -4900,21 +4898,21 @@
         <v>29</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="K60" s="10"/>
       <c r="L60" s="12"/>
       <c r="M60" s="13" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4922,10 +4920,10 @@
         <v>53</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>59</v>
@@ -4934,16 +4932,16 @@
         <v>29</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="K61" s="10"/>
       <c r="L61" s="12"/>
@@ -4954,35 +4952,35 @@
         <v>54</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D62" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="H62" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="J62" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="K62" s="10" t="s">
         <v>263</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G62" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="I62" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="J62" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="K62" s="10" t="s">
-        <v>266</v>
       </c>
       <c r="L62" s="12"/>
       <c r="M62" s="13" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4990,33 +4988,33 @@
         <v>55</v>
       </c>
       <c r="C63" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I63" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="J63" s="10" t="s">
         <v>268</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="F63" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G63" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="I63" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="J63" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="K63" s="10"/>
       <c r="L63" s="12"/>
       <c r="M63" s="13" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5024,10 +5022,10 @@
         <v>56</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>59</v>
@@ -5036,23 +5034,23 @@
         <v>29</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H64" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="L64" s="12"/>
       <c r="M64" s="13" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5060,10 +5058,10 @@
         <v>57</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>59</v>
@@ -5072,21 +5070,21 @@
         <v>29</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H65" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K65" s="10"/>
       <c r="L65" s="12"/>
       <c r="M65" s="13" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5094,33 +5092,33 @@
         <v>58</v>
       </c>
       <c r="C66" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="J66" s="10" t="s">
         <v>280</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="F66" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G66" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="I66" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="J66" s="10" t="s">
-        <v>283</v>
       </c>
       <c r="K66" s="10"/>
       <c r="L66" s="12"/>
       <c r="M66" s="13" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5128,35 +5126,35 @@
         <v>59</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D67" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="J67" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="K67" s="10" t="s">
         <v>285</v>
-      </c>
-      <c r="F67" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G67" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="I67" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="J67" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="K67" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="L67" s="12"/>
       <c r="M67" s="13" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5164,10 +5162,10 @@
         <v>60</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>59</v>
@@ -5176,21 +5174,21 @@
         <v>29</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="K68" s="10"/>
       <c r="L68" s="12"/>
       <c r="M68" s="13" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5198,33 +5196,33 @@
         <v>61</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D69" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="J69" s="10" t="s">
         <v>294</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="F69" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G69" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="I69" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="J69" s="10" t="s">
-        <v>297</v>
       </c>
       <c r="K69" s="10"/>
       <c r="L69" s="12"/>
       <c r="M69" s="13" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5232,31 +5230,31 @@
         <v>62</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D70" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J70" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K70" s="10" t="s">
         <v>298</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="F70" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="H70" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="I70" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J70" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K70" s="10" t="s">
-        <v>301</v>
       </c>
       <c r="L70" s="12"/>
       <c r="M70" s="13" t="s">
@@ -5268,10 +5266,10 @@
         <v>63</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>59</v>
@@ -5286,15 +5284,15 @@
         <v>31</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J71" s="10" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K71" s="10"/>
       <c r="L71" s="12"/>
       <c r="M71" s="13" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5302,10 +5300,10 @@
         <v>64</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>59</v>
@@ -5320,15 +5318,15 @@
         <v>31</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="K72" s="10"/>
       <c r="L72" s="12"/>
       <c r="M72" s="13" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5336,10 +5334,10 @@
         <v>65</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>59</v>
@@ -5354,15 +5352,15 @@
         <v>31</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J73" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="K73" s="10"/>
       <c r="L73" s="12"/>
       <c r="M73" s="13" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5370,13 +5368,13 @@
         <v>66</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>29</v>
@@ -5388,15 +5386,15 @@
         <v>31</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K74" s="10"/>
       <c r="L74" s="12"/>
       <c r="M74" s="13" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5404,10 +5402,10 @@
         <v>67</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>59</v>
@@ -5422,15 +5420,15 @@
         <v>31</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J75" s="10" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="K75" s="10"/>
       <c r="L75" s="12"/>
       <c r="M75" s="13" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5438,10 +5436,10 @@
         <v>68</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>59</v>
@@ -5456,15 +5454,15 @@
         <v>31</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K76" s="10"/>
       <c r="L76" s="12"/>
       <c r="M76" s="13" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5472,13 +5470,13 @@
         <v>69</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F77" s="11" t="s">
         <v>29</v>
@@ -5490,15 +5488,15 @@
         <v>31</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="K77" s="10"/>
       <c r="L77" s="12"/>
       <c r="M77" s="13" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5506,13 +5504,13 @@
         <v>70</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>29</v>
@@ -5524,15 +5522,15 @@
         <v>31</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J78" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="K78" s="10"/>
       <c r="L78" s="12"/>
       <c r="M78" s="13" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5540,13 +5538,13 @@
         <v>71</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F79" s="11" t="s">
         <v>29</v>
@@ -5558,15 +5556,15 @@
         <v>31</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="K79" s="10"/>
       <c r="L79" s="12"/>
       <c r="M79" s="13" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5574,13 +5572,13 @@
         <v>72</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F80" s="11" t="s">
         <v>29</v>
@@ -5592,15 +5590,15 @@
         <v>31</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="K80" s="10"/>
       <c r="L80" s="12"/>
       <c r="M80" s="13" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5608,13 +5606,13 @@
         <v>73</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F81" s="11" t="s">
         <v>29</v>
@@ -5626,15 +5624,15 @@
         <v>31</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="K81" s="10"/>
       <c r="L81" s="12"/>
       <c r="M81" s="13" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5642,33 +5640,33 @@
         <v>74</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D82" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I82" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="J82" s="10" t="s">
         <v>341</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="F82" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G82" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H82" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I82" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="J82" s="10" t="s">
-        <v>344</v>
       </c>
       <c r="K82" s="10"/>
       <c r="L82" s="12"/>
       <c r="M82" s="13" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5676,13 +5674,13 @@
         <v>75</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F83" s="11" t="s">
         <v>29</v>
@@ -5694,15 +5692,15 @@
         <v>31</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="K83" s="10"/>
       <c r="L83" s="12"/>
       <c r="M83" s="13" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5710,10 +5708,10 @@
         <v>76</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>59</v>
@@ -5728,32 +5726,32 @@
         <v>31</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="K84" s="10"/>
       <c r="L84" s="12"/>
       <c r="M84" s="13" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="9" t="n">
         <v>77</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G85" s="10" t="s">
         <v>30</v>
@@ -5762,70 +5760,66 @@
         <v>31</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="K85" s="10" t="s">
-        <v>358</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="K85" s="10"/>
       <c r="L85" s="12"/>
       <c r="M85" s="13" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="9" t="n">
         <v>78</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H86" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>31</v>
+        <v>357</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K86" s="10" t="s">
-        <v>361</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="K86" s="10"/>
       <c r="L86" s="12"/>
       <c r="M86" s="13" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B87" s="9" t="n">
         <v>79</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>31</v>
+        <v>360</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G87" s="10" t="s">
         <v>30</v>
@@ -5834,17 +5828,15 @@
         <v>31</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>31</v>
+        <v>346</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K87" s="10" t="s">
-        <v>363</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="K87" s="10"/>
       <c r="L87" s="12"/>
       <c r="M87" s="13" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5852,69 +5844,69 @@
         <v>80</v>
       </c>
       <c r="C88" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="E88" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="D88" s="10" t="s">
+      <c r="F88" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I88" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="J88" s="10" t="s">
         <v>365</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="F88" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G88" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H88" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="I88" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="J88" s="10" t="s">
-        <v>367</v>
       </c>
       <c r="K88" s="10"/>
       <c r="L88" s="12"/>
       <c r="M88" s="13" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="9" t="n">
         <v>81</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D89" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="F89" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I89" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="E89" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F89" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G89" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="I89" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="J89" s="10" t="s">
-        <v>31</v>
+        <v>369</v>
       </c>
       <c r="K89" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L89" s="12"/>
       <c r="M89" s="13" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5922,10 +5914,10 @@
         <v>82</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>59</v>
@@ -5934,21 +5926,21 @@
         <v>29</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H90" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J90" s="10" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="K90" s="10"/>
       <c r="L90" s="12"/>
       <c r="M90" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5956,10 +5948,10 @@
         <v>83</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>59</v>
@@ -5968,21 +5960,21 @@
         <v>29</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K91" s="10"/>
       <c r="L91" s="12"/>
       <c r="M91" s="13" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5990,22 +5982,22 @@
         <v>84</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I92" s="10" t="s">
         <v>31</v>
@@ -6014,47 +6006,45 @@
         <v>31</v>
       </c>
       <c r="K92" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L92" s="12"/>
       <c r="M92" s="13" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="9" t="n">
         <v>85</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="K93" s="10" t="s">
-        <v>382</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="K93" s="10"/>
       <c r="L93" s="12"/>
       <c r="M93" s="13" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6062,10 +6052,10 @@
         <v>86</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>59</v>
@@ -6074,57 +6064,57 @@
         <v>29</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K94" s="10"/>
       <c r="L94" s="12"/>
       <c r="M94" s="13" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="9" t="n">
         <v>87</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>72</v>
+        <v>297</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K95" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L95" s="12"/>
       <c r="M95" s="13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6132,10 +6122,10 @@
         <v>88</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>59</v>
@@ -6150,15 +6140,15 @@
         <v>31</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K96" s="10"/>
       <c r="L96" s="12"/>
       <c r="M96" s="13" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6166,10 +6156,10 @@
         <v>89</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>59</v>
@@ -6184,15 +6174,15 @@
         <v>31</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K97" s="10"/>
       <c r="L97" s="12"/>
       <c r="M97" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6200,13 +6190,13 @@
         <v>90</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F98" s="11" t="s">
         <v>29</v>
@@ -6218,15 +6208,15 @@
         <v>31</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K98" s="10"/>
       <c r="L98" s="12"/>
       <c r="M98" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6234,13 +6224,13 @@
         <v>91</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F99" s="11" t="s">
         <v>29</v>
@@ -6252,15 +6242,15 @@
         <v>31</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K99" s="10"/>
       <c r="L99" s="12"/>
       <c r="M99" s="13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6268,13 +6258,13 @@
         <v>92</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>29</v>
@@ -6286,15 +6276,15 @@
         <v>31</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K100" s="10"/>
       <c r="L100" s="12"/>
       <c r="M100" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6302,13 +6292,13 @@
         <v>93</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F101" s="11" t="s">
         <v>29</v>
@@ -6320,15 +6310,15 @@
         <v>31</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K101" s="10"/>
       <c r="L101" s="12"/>
       <c r="M101" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6336,13 +6326,13 @@
         <v>94</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>29</v>
@@ -6354,15 +6344,15 @@
         <v>31</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K102" s="10"/>
       <c r="L102" s="12"/>
       <c r="M102" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6370,10 +6360,10 @@
         <v>95</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>59</v>
@@ -6388,15 +6378,15 @@
         <v>31</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K103" s="10"/>
       <c r="L103" s="12"/>
       <c r="M103" s="13" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6404,10 +6394,10 @@
         <v>96</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>59</v>
@@ -6422,15 +6412,15 @@
         <v>31</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J104" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K104" s="10"/>
       <c r="L104" s="12"/>
       <c r="M104" s="13" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6438,16 +6428,16 @@
         <v>97</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>59</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="G105" s="10" t="s">
         <v>51</v>
@@ -6456,17 +6446,17 @@
         <v>31</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J105" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K105" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L105" s="12"/>
       <c r="M105" s="13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6474,10 +6464,10 @@
         <v>98</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>59</v>
@@ -6492,15 +6482,15 @@
         <v>31</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K106" s="10"/>
       <c r="L106" s="12"/>
       <c r="M106" s="13" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6508,31 +6498,31 @@
         <v>99</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F107" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H107" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L107" s="12"/>
       <c r="M107" s="13" t="s">
@@ -6544,10 +6534,10 @@
         <v>100</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>59</v>
@@ -6562,15 +6552,15 @@
         <v>31</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K108" s="10"/>
       <c r="L108" s="12"/>
       <c r="M108" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6578,13 +6568,13 @@
         <v>101</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F109" s="11" t="s">
         <v>29</v>
@@ -6596,10 +6586,10 @@
         <v>31</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K109" s="10"/>
       <c r="L109" s="12"/>
@@ -6612,33 +6602,33 @@
         <v>102</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F110" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H110" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K110" s="10"/>
       <c r="L110" s="12"/>
       <c r="M110" s="13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6646,10 +6636,10 @@
         <v>103</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>59</v>
@@ -6664,15 +6654,15 @@
         <v>31</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K111" s="10"/>
       <c r="L111" s="12"/>
       <c r="M111" s="13" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6680,10 +6670,10 @@
         <v>104</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>59</v>
@@ -6698,15 +6688,15 @@
         <v>31</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J112" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K112" s="10"/>
       <c r="L112" s="12"/>
       <c r="M112" s="13" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6714,16 +6704,16 @@
         <v>105</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="G113" s="10" t="s">
         <v>51</v>
@@ -6732,17 +6722,17 @@
         <v>31</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K113" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L113" s="12"/>
       <c r="M113" s="13" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6750,10 +6740,10 @@
         <v>106</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>59</v>
@@ -6768,15 +6758,15 @@
         <v>31</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K114" s="10"/>
       <c r="L114" s="12"/>
       <c r="M114" s="13" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6784,13 +6774,13 @@
         <v>107</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F115" s="11" t="s">
         <v>29</v>
@@ -6802,15 +6792,15 @@
         <v>31</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K115" s="10"/>
       <c r="L115" s="12"/>
       <c r="M115" s="13" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6818,10 +6808,10 @@
         <v>108</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>59</v>
@@ -6836,15 +6826,15 @@
         <v>31</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K116" s="10"/>
       <c r="L116" s="12"/>
       <c r="M116" s="13" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6852,10 +6842,10 @@
         <v>109</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>59</v>
@@ -6870,15 +6860,15 @@
         <v>31</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K117" s="10"/>
       <c r="L117" s="12"/>
       <c r="M117" s="13" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6886,13 +6876,13 @@
         <v>110</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F118" s="11" t="s">
         <v>29</v>
@@ -6904,15 +6894,15 @@
         <v>31</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K118" s="10"/>
       <c r="L118" s="12"/>
       <c r="M118" s="13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6920,13 +6910,13 @@
         <v>111</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F119" s="11" t="s">
         <v>29</v>
@@ -6938,17 +6928,17 @@
         <v>31</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K119" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L119" s="12"/>
       <c r="M119" s="13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6956,13 +6946,13 @@
         <v>112</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F120" s="11" t="s">
         <v>29</v>
@@ -6974,15 +6964,15 @@
         <v>31</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K120" s="10"/>
       <c r="L120" s="12"/>
       <c r="M120" s="13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6990,13 +6980,13 @@
         <v>113</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F121" s="11" t="s">
         <v>29</v>
@@ -7008,15 +6998,15 @@
         <v>31</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J121" s="10" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K121" s="10"/>
       <c r="L121" s="12"/>
       <c r="M121" s="13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7024,13 +7014,13 @@
         <v>114</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F122" s="11" t="s">
         <v>29</v>
@@ -7042,17 +7032,17 @@
         <v>31</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J122" s="10" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K122" s="10" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L122" s="12"/>
       <c r="M122" s="13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7060,13 +7050,13 @@
         <v>115</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F123" s="11" t="s">
         <v>29</v>
@@ -7078,15 +7068,15 @@
         <v>31</v>
       </c>
       <c r="I123" s="10" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K123" s="10"/>
       <c r="L123" s="12"/>
       <c r="M123" s="13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7094,13 +7084,13 @@
         <v>116</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F124" s="11" t="s">
         <v>29</v>
@@ -7112,15 +7102,15 @@
         <v>31</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K124" s="10"/>
       <c r="L124" s="12"/>
       <c r="M124" s="13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7128,10 +7118,10 @@
         <v>117</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>59</v>
@@ -7140,21 +7130,21 @@
         <v>29</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K125" s="10"/>
       <c r="L125" s="12"/>
       <c r="M125" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7162,33 +7152,33 @@
         <v>118</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F126" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G126" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="K126" s="10"/>
       <c r="L126" s="12"/>
       <c r="M126" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7196,33 +7186,33 @@
         <v>119</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F127" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K127" s="10"/>
       <c r="L127" s="12"/>
       <c r="M127" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7230,10 +7220,10 @@
         <v>120</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>59</v>
@@ -7242,21 +7232,21 @@
         <v>29</v>
       </c>
       <c r="G128" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H128" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K128" s="10"/>
       <c r="L128" s="12"/>
       <c r="M128" s="13" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7264,35 +7254,35 @@
         <v>121</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="K129" s="10" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L129" s="12"/>
       <c r="M129" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7300,33 +7290,33 @@
         <v>122</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F130" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G130" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H130" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K130" s="10"/>
       <c r="L130" s="12"/>
       <c r="M130" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7334,33 +7324,33 @@
         <v>123</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F131" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K131" s="10"/>
       <c r="L131" s="12"/>
       <c r="M131" s="13" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7368,33 +7358,33 @@
         <v>124</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F132" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G132" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I132" s="10" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="K132" s="10"/>
       <c r="L132" s="12"/>
       <c r="M132" s="13" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7402,33 +7392,33 @@
         <v>125</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F133" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J133" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K133" s="10"/>
       <c r="L133" s="12"/>
       <c r="M133" s="13" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7436,33 +7426,33 @@
         <v>126</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F134" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G134" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K134" s="10"/>
       <c r="L134" s="12"/>
       <c r="M134" s="13" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7470,10 +7460,10 @@
         <v>127</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>59</v>
@@ -7482,21 +7472,21 @@
         <v>29</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J135" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="K135" s="10"/>
       <c r="L135" s="12"/>
       <c r="M135" s="13" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7504,22 +7494,22 @@
         <v>128</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>86</v>
+        <v>563</v>
       </c>
       <c r="G136" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H136" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I136" s="10" t="s">
         <v>31</v>
@@ -7528,7 +7518,7 @@
         <v>31</v>
       </c>
       <c r="K136" s="10" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L136" s="12"/>
       <c r="M136" s="13" t="s">
@@ -7540,35 +7530,35 @@
         <v>129</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="F137" s="11" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="K137" s="10" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="L137" s="12"/>
       <c r="M137" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7576,35 +7566,35 @@
         <v>130</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="F138" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G138" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H138" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I138" s="10" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="J138" s="10" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K138" s="10" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L138" s="12"/>
       <c r="M138" s="13" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7612,35 +7602,35 @@
         <v>131</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F139" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H139" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="K139" s="10" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L139" s="12"/>
       <c r="M139" s="13" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7648,35 +7638,35 @@
         <v>132</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F140" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G140" s="10" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H140" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I140" s="10" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J140" s="10" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K140" s="10" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="L140" s="12"/>
       <c r="M140" s="13" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7684,33 +7674,33 @@
         <v>133</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F141" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H141" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I141" s="10" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="J141" s="10" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="K141" s="10"/>
       <c r="L141" s="12"/>
       <c r="M141" s="13" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7718,33 +7708,33 @@
         <v>134</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F142" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G142" s="10" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H142" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I142" s="10" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="K142" s="10"/>
       <c r="L142" s="12"/>
       <c r="M142" s="13" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7752,33 +7742,33 @@
         <v>135</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F143" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I143" s="10" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="K143" s="10"/>
       <c r="L143" s="12"/>
       <c r="M143" s="13" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7786,33 +7776,33 @@
         <v>136</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="F144" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G144" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H144" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I144" s="10" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="J144" s="10" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K144" s="10"/>
       <c r="L144" s="12"/>
       <c r="M144" s="13" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7820,10 +7810,10 @@
         <v>137</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>59</v>
@@ -7832,21 +7822,21 @@
         <v>29</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I145" s="10" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="J145" s="10" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K145" s="10"/>
       <c r="L145" s="12"/>
       <c r="M145" s="13" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7854,10 +7844,10 @@
         <v>138</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E146" s="10" t="s">
         <v>59</v>
@@ -7866,21 +7856,21 @@
         <v>29</v>
       </c>
       <c r="G146" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H146" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="J146" s="10" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K146" s="10"/>
       <c r="L146" s="12"/>
       <c r="M146" s="13" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7888,33 +7878,33 @@
         <v>139</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F147" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H147" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I147" s="10" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="J147" s="10" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="K147" s="10"/>
       <c r="L147" s="12"/>
       <c r="M147" s="13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7922,33 +7912,33 @@
         <v>140</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="F148" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H148" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I148" s="10" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J148" s="10" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="K148" s="10"/>
       <c r="L148" s="12"/>
       <c r="M148" s="13" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7956,33 +7946,33 @@
         <v>141</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="F149" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I149" s="10" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="J149" s="10" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="K149" s="10"/>
       <c r="L149" s="12"/>
       <c r="M149" s="13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7990,10 +7980,10 @@
         <v>142</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>59</v>
@@ -8002,21 +7992,21 @@
         <v>29</v>
       </c>
       <c r="G150" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H150" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I150" s="10" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="J150" s="10" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K150" s="10"/>
       <c r="L150" s="12"/>
       <c r="M150" s="13" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8024,35 +8014,35 @@
         <v>143</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="F151" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H151" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I151" s="10" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="J151" s="10" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="K151" s="10" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L151" s="12"/>
       <c r="M151" s="13" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8060,10 +8050,10 @@
         <v>144</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>59</v>
@@ -8072,23 +8062,23 @@
         <v>29</v>
       </c>
       <c r="G152" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H152" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I152" s="10" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="J152" s="10" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K152" s="10" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="L152" s="12"/>
       <c r="M152" s="13" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8096,10 +8086,10 @@
         <v>145</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>59</v>
@@ -8108,21 +8098,21 @@
         <v>29</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H153" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I153" s="10" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="K153" s="10"/>
       <c r="L153" s="12"/>
       <c r="M153" s="13" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8130,33 +8120,33 @@
         <v>146</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E154" s="10" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="F154" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G154" s="10" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H154" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I154" s="10" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K154" s="10"/>
       <c r="L154" s="12"/>
       <c r="M154" s="13" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8164,33 +8154,33 @@
         <v>147</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="F155" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H155" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I155" s="10" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="J155" s="10" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K155" s="10"/>
       <c r="L155" s="12"/>
       <c r="M155" s="13" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8198,10 +8188,10 @@
         <v>148</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E156" s="10" t="s">
         <v>59</v>
@@ -8210,23 +8200,23 @@
         <v>29</v>
       </c>
       <c r="G156" s="10" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H156" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I156" s="10" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="J156" s="10" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K156" s="10" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L156" s="12"/>
       <c r="M156" s="13" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8234,31 +8224,31 @@
         <v>149</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="F157" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H157" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I157" s="10" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="J157" s="10" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="K157" s="10" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="L157" s="12"/>
       <c r="M157" s="13" t="s">
@@ -8270,28 +8260,28 @@
         <v>150</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E158" s="10" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="F158" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G158" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H158" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I158" s="10" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="J158" s="10" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="K158" s="10"/>
       <c r="L158" s="12"/>
@@ -8349,7 +8339,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8357,22 +8347,22 @@
         <v>15</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>86</v>
+        <v>563</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8414,11 +8404,11 @@
       </c>
       <c r="D6" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B6,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B6,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B6,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -8426,16 +8416,16 @@
       </c>
       <c r="G6" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B6,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="19" t="n">
         <f aca="false">IF(C6&gt;0,D6/C6,0)</f>
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C7" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B7)</f>
@@ -8464,7 +8454,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="17" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C8" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B8)</f>
@@ -8493,7 +8483,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="17" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C9" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B9)</f>
@@ -8522,7 +8512,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C10" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B10)</f>
@@ -8551,7 +8541,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="17" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C11" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B11)</f>
@@ -8580,7 +8570,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="17" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C12" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B12)</f>
@@ -8609,7 +8599,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="17" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C13" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B13)</f>
@@ -8638,7 +8628,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="17" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C14" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B14)</f>
@@ -8667,7 +8657,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="17" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C15" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B15)</f>
@@ -8696,7 +8686,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="17" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C16" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B16)</f>
@@ -8725,7 +8715,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B17)</f>
@@ -8754,7 +8744,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="17" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B18)</f>
@@ -8783,7 +8773,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="17" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C19" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B19)</f>
@@ -8812,7 +8802,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="17" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C20" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B20)</f>
@@ -8841,7 +8831,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="17" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B21)</f>
@@ -8849,11 +8839,11 @@
       </c>
       <c r="D21" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B21,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E21" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B21,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B21,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -8861,16 +8851,16 @@
       </c>
       <c r="G21" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B21,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" s="19" t="n">
         <f aca="false">IF(C21&gt;0,D21/C21,0)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="17" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B22)</f>
@@ -8878,7 +8868,7 @@
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B22,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B22,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
@@ -8890,16 +8880,16 @@
       </c>
       <c r="G22" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B22,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="19" t="n">
         <f aca="false">IF(C22&gt;0,D22/C22,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="17" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B23)</f>
@@ -8907,11 +8897,11 @@
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B23,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B23,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B23,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -8923,12 +8913,12 @@
       </c>
       <c r="H23" s="19" t="n">
         <f aca="false">IF(C23&gt;0,D23/C23,0)</f>
-        <v>0.333333333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B24)</f>
@@ -8940,11 +8930,11 @@
       </c>
       <c r="E24" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B24,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B24,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B24,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
@@ -8957,7 +8947,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="17" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C25" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B25)</f>
@@ -8986,7 +8976,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="17" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B26)</f>
@@ -9015,7 +9005,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="17" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C27" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B27)</f>
@@ -9044,7 +9034,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C28" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B28)</f>
@@ -9073,7 +9063,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="17" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C29" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B29)</f>
@@ -9102,7 +9092,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="17" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C30" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B30)</f>
@@ -9131,7 +9121,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="17" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C31" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B31)</f>
@@ -9160,7 +9150,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C32" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B32)</f>
@@ -9189,7 +9179,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="17" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C33" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B33)</f>
@@ -9218,7 +9208,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="17" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C34" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B34)</f>
@@ -9247,7 +9237,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="17" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C35" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B35)</f>
@@ -9276,7 +9266,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="17" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C36" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B36)</f>
@@ -9305,7 +9295,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="17" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C37" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B37)</f>
@@ -9334,7 +9324,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="17" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C38" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B38)</f>
@@ -9363,7 +9353,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="17" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C39" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B39)</f>
@@ -9392,7 +9382,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="17" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C40" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B40)</f>
@@ -9421,7 +9411,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="17" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C41" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B41)</f>
@@ -9450,7 +9440,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="17" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C42" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B42)</f>
@@ -9479,7 +9469,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="17" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C43" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B43)</f>
@@ -9508,7 +9498,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="17" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C44" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B44)</f>
@@ -9537,7 +9527,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="17" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C45" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B45)</f>
@@ -9566,7 +9556,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="17" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C46" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B46)</f>
@@ -9595,7 +9585,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="17" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C47" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B47)</f>
@@ -9624,7 +9614,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="17" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C48" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B48)</f>
@@ -9653,7 +9643,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="17" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C49" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B49)</f>
@@ -9682,7 +9672,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="20" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C50" s="21" t="n">
         <f aca="false">SUM(C5:C49)</f>
@@ -9690,23 +9680,23 @@
       </c>
       <c r="D50" s="21" t="n">
         <f aca="false">SUM(D5:D49)</f>
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">SUM(E5:E49)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F50" s="21" t="n">
         <f aca="false">SUM(F5:F49)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50" s="21" t="n">
         <f aca="false">SUM(G5:G49)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H50" s="22" t="n">
         <f aca="false">IF(C50&gt;0,D50/C50,0)</f>
-        <v>0.866666666666667</v>
+        <v>0.926666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -9737,18 +9727,18 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="23" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>18</v>
@@ -9756,41 +9746,41 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="24" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="24" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>29</v>
@@ -9798,41 +9788,41 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="24" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>29</v>
@@ -9840,44 +9830,44 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>86</v>
+        <v>563</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -9926,15 +9916,15 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="26" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9942,31 +9932,31 @@
         <v>29</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="26" t="s">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="26" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="26" t="s">
-        <v>86</v>
+        <v>563</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9974,7 +9964,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9982,15 +9972,15 @@
         <v>22</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="26" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9998,15 +9988,15 @@
         <v>20</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="26" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
   </sheetData>

--- a/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
+++ b/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="728">
   <si>
     <t xml:space="preserve">Nibbl AI — Master Requirements Tracker</t>
   </si>
@@ -749,72 +749,75 @@
     <t xml:space="preserve">Reserve Offer: prefill email/phone (collect if logged out), two required consents</t>
   </si>
   <si>
-    <t xml:space="preserve">Both consents required.</t>
+    <t xml:space="preserve">Reserve Offer shows email + phone: prefilled when signed in (verified phone read-only), collected when logged out; both consents required. Logged-out shoppers open a deal from its link, then a 6-digit email code signs them in (or creates the account) before Confirm Reservation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → deal link → Continue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a deal link logged out, enter email + phone, enter the code, Confirm &amp; Reserve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile app: same API (documented for the app developer).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm Reservation screen: slot X of 5, exact deadline, Confirm &amp; Reserve (slot consumed only here)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot use shown on Reserve Offer; separate Confirm screen with product, retailer, reward, exact deadline and resulting slot use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → offer → Continue → Confirm &amp; Reserve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim an offer; check the deadline is 7 days out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reservation eligibility checked before a claim slot is consumed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All checks (consent, slots, already claimed, cooldown, dates, capacity, funds) run before the slot is used.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered by automated tests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#17, #18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active claim slots (5) — occupied until approval, final rejection or expiry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → My Rewards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim to the limit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Action Prompt: carousel, Submit Receipt + time left, Save for Later, My Offers badge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → home; header badge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim, then return home.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebate restriction pop-ups (10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All with own code; consent, slots, claimed, cooldown, one-time, not started, paused, capacity, funds; retailer shown on offer.</t>
   </si>
   <si>
     <t xml:space="preserve">Website → offer → Claim</t>
   </si>
   <si>
-    <t xml:space="preserve">Claim without consents → pop-up.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logged-out shoppers must sign in first (Master allows collecting email/phone on this step).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm Reservation screen: slot X of 5, exact deadline, Confirm &amp; Reserve (slot consumed only here)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slot use shown on Reserve Offer; separate Confirm screen with product, retailer, reward, exact deadline and resulting slot use.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → offer → Continue → Confirm &amp; Reserve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim an offer; check the deadline is 7 days out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reservation eligibility checked before a claim slot is consumed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All checks (consent, slots, already claimed, cooldown, dates, capacity, funds) run before the slot is used.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered by automated tests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#17, #18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active claim slots (5) — occupied until approval, final rejection or expiry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → My Rewards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim to the limit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return Action Prompt: carousel, Submit Receipt + time left, Save for Later, My Offers badge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → home; header badge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim, then return home.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebate restriction pop-ups (10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All with own code; consent, slots, claimed, cooldown, one-time, not started, paused, capacity, funds; retailer shown on offer.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trigger each case.</t>
   </si>
   <si>
@@ -1715,358 +1718,361 @@
     <t xml:space="preserve">Passwordless access to My Offers, Wallet and Profile</t>
   </si>
   <si>
-    <t xml:space="preserve">Shoppers sign in with a password.</t>
+    <t xml:space="preserve">Shoppers sign in with a 6-digit email code (no password) — on the sign-in screen and during Reserve Offer; passwords still work for existing shoppers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → Sign in → Email me a sign-in code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign in with a code; open My Offers, Wallet and Profile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile app: same API (documented).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profile &amp; account security: verified phone locked; change via admin with re-verification; history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A verified phone is locked: the shopper requests a change (new number + reason); Nibbl approves or rejects (reason required) from Admin → Shoppers (filter: phone change pending; dashboard Needs Attention tile); approved numbers must be verified by SMS (withdrawals pause 48 h). Phone history (requests, verifications, resets) on the shopper page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → Profile → Phone; Admin → Shoppers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request a change; approve it in Admin; verify the new number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue cards, Needs Attention, Brand Revenue (category/status filter, lowest first), brand-funded rewards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue cards, Needs Attention links, Brand Revenue with category / status / plan filters, lowest first, Total Nibbl Revenue + Last Activity, brand-funded rewards shown separately.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change the date range and the category filter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A brand's category = its most common product category (the sign-up category isn't stored).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Withdrawals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabs: Ready for Batch, Manual Review, Processing, Completed, Failed; batch summary (PayPal fees)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All five tabs with counts; safe requests enter Ready for Batch automatically; live batch summary (count, payouts, est. PayPal fees, total).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Withdrawals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select requests; watch the summary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PayPal fee estimate = $0.25 per payout (configurable on the server).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create batch, download PayPal file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create Batch from selected requests downloads the PayPal Payouts CSV (Reference ID = Withdrawal ID); past batches can be downloaded again; an exported request can't join a second batch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Withdrawals → Create Batch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a batch; upload the file to PayPal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the file against PayPal's current Payouts template on first use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Import PayPal results (Paid / Failed, partial success, idempotent, match by Withdrawal ID)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Import PayPal Results: matches Reference ID; SUCCESS → Paid, failures → Failed (retryable or permanent); partial success; re-import changes nothing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Withdrawals → Import PayPal Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Import a results CSV twice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual review: flag reason + history; approve / reject with customer-facing reason; audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual Review panel: flag reason, shopper history, Approve (→ Ready for Batch) / Reject with required reason; every decision audit-logged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Withdrawals → Manual Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approve and reject a flagged request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#43, #51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Brands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPIs, brand table (category, Nibbl revenue, funds, payment status, activity), filters, sort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPIs (active, pending verification, failed payments, suspended); table with category, plan, Nibbl revenue, wallet funds, payment status, last activity, status; search, filters, sort (lowest revenue first).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Brands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter by category and plan; sort by lowest revenue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin brand access mode ('viewing as Nibbl', every action logged) + brand summary + actions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selected-brand summary (verified, payment connected, wallet funds, promotional credits, Nibbl revenue, active campaigns); Open Brand Dashboard opens the brand app in Nibbl Admin Mode (banner: Viewing &lt;brand&gt;. Every action is logged.), every change made there is audit-logged; Add Promotional Credit; Suspend / Reactivate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Brands → brand → Open Brand Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a brand's dashboard, change a setting, then find it in Settings → View Audit Log.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#45, #46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Campaign Approvals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queue, new vs revisions, review, approve / reject / request changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Campaign Approvals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approve a campaign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Promo Codes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary, create code, add brand credit, table (applies to, dates, usage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Promo Codes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Shoppers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List (status, wallet, redemptions, referrals, brand suspensions, last activity)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Searchable list (name, email, phone, Shopper ID) with account status, wallet, redemptions, referrals, brand suspensions, last activity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Shoppers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search a shopper by email.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detail tabs (overview, wallet ledger, claims &amp; reviews, referrals, suspensions), purchase activity, cooldowns, adjust wallet, internal note, global suspend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selected shopper: identity + status; tabs Overview (account &amp; payout, wallet: available / pending / lifetime paid, purchase activity: brands + retailers, active cooldowns, internal notes), Wallet Ledger, Claims &amp; Reviews (cancel claim), Referrals, Suspensions; Adjust Wallet (credit/debit, reason required, before/after audit), Add Internal Note, Global Suspend / Reactivate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Shoppers → shopper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjust a wallet with a reason; add a note; check the ledger tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#46, #51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Suspensions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary, list, review (remove brand suspension, global suspend), repeated-suspension alert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Suspensions page: summary (active brand suspensions, repeat suspensions, global suspensions), searchable list (brand, reason, date, prior count, status) with date/status filters; detail with View Shopper, Remove Brand Suspension, Globally Suspend; repeated suspensions alert only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Suspensions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove a brand suspension; globally suspend a shopper.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Referrals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary, filters, details, flag review (approve / reject / suspend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Referrals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the Flagged tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Revenue Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources, promo credits used, refunds, processing costs, net revenue, trend chart, brand contribution + export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Analytics page: revenue sources, promotional credits used, refunds, processing costs, net revenue, brand-funded rewards; daily Revenue Trend chart; Brand Revenue Contribution (credits + processing per brand) with category / plan filters and Export CSV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch the date range; export the CSV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processing costs are estimates (Stripe 2.9% + $0.30 per wallet top-up; $0.25 per payout). Refunds = brand wallet cash returned, shown but not deducted from revenue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Receipt Brand Discovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary, filters, leads, brand insight, export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Brand Discovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a lead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand detected from receipt text.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin — Settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Withdrawal review rules · Discovery ranking · device/network limits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change a threshold.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#50, #51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referral flag rules: duplicate payout identity, same device, self-referral, unusual referral volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toggles for the Master rules: duplicate payout identity, same device, self-referral (same name / email / phone, Gmail dots and +tags ignored), unusual referral volume (limit per 7 days); same-network and fraud-signal checks kept as additional toggles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turn a rule off; a matching referral no longer gets flagged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin Users (staff roles) + View Audit Log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin Users: list, + Add User (Administrator / Operations / Analytics; new admins set their password through the emailed code), change role, remove access; Analytics is read-only and only Administrators change Settings or Admin Users; View Audit Log (latest 200 sensitive actions).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Settings → Admin Users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add an Analytics user; they can view pages but can't save changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-cutting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud &amp; abuse: duplicates, velocity, device / IP / browser checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin → Users → user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create 3 accounts on one browser.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App must send X-Device-Id.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt retention / cleanup (full receipt 30 days, then matching line only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled job (every 15 min) deletes receipt images 30 days after submission (pending receipts are skipped) and records when; matching line items and receipt details stay.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend job</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated test: a 31-day-old receipt loses its image and keeps the matching line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ships switched off in production (RECEIPT_IMAGE_PURGE_ENABLED) until the owner approves deleting existing receipt photos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System email via AWS SES with bounce / complaint handling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All system email now goes through Amazon SES as Nibbl &lt;no-reply@joinnibbl.com&gt; (DKIM-signed domain, production access); bounces and complaints go to the SES suppression list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any emailed code or notification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request an email code; check the sender.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progress by Master Document Section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
   </si>
   <si>
     <t xml:space="preserve">Planned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passwordless shopper sign-in not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profile &amp; account security: verified phone locked; change via admin with re-verification; history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phone verify + admin reset.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify a phone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lock verified phone from self-service change; keep change history (client Twilio rules). Retest with approved Twilio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue cards, Needs Attention, Brand Revenue (category/status filter, lowest first), brand-funded rewards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue cards, Needs Attention links, Brand Revenue with category / status / plan filters, lowest first, Total Nibbl Revenue + Last Activity, brand-funded rewards shown separately.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change the date range and the category filter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A brand's category = its most common product category (the sign-up category isn't stored).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Withdrawals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabs: Ready for Batch, Manual Review, Processing, Completed, Failed; batch summary (PayPal fees)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All five tabs with counts; safe requests enter Ready for Batch automatically; live batch summary (count, payouts, est. PayPal fees, total).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Withdrawals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select requests; watch the summary.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PayPal fee estimate = $0.25 per payout (configurable on the server).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create batch, download PayPal file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create Batch from selected requests downloads the PayPal Payouts CSV (Reference ID = Withdrawal ID); past batches can be downloaded again; an exported request can't join a second batch.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Withdrawals → Create Batch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a batch; upload the file to PayPal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check the file against PayPal's current Payouts template on first use.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Import PayPal results (Paid / Failed, partial success, idempotent, match by Withdrawal ID)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Import PayPal Results: matches Reference ID; SUCCESS → Paid, failures → Failed (retryable or permanent); partial success; re-import changes nothing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Withdrawals → Import PayPal Results</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Import a results CSV twice.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manual review: flag reason + history; approve / reject with customer-facing reason; audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manual Review panel: flag reason, shopper history, Approve (→ Ready for Batch) / Reject with required reason; every decision audit-logged.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Withdrawals → Manual Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approve and reject a flagged request.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#43, #51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Brands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPIs, brand table (category, Nibbl revenue, funds, payment status, activity), filters, sort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPIs (active, pending verification, failed payments, suspended); table with category, plan, Nibbl revenue, wallet funds, payment status, last activity, status; search, filters, sort (lowest revenue first).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Brands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter by category and plan; sort by lowest revenue.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin brand access mode ('viewing as Nibbl', every action logged) + brand summary + actions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selected-brand summary (verified, payment connected, wallet funds, promotional credits, Nibbl revenue, active campaigns); Open Brand Dashboard opens the brand app in Nibbl Admin Mode (banner: Viewing &lt;brand&gt;. Every action is logged.), every change made there is audit-logged; Add Promotional Credit; Suspend / Reactivate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Brands → brand → Open Brand Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a brand's dashboard, change a setting, then find it in Settings → View Audit Log.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#45, #46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Campaign Approvals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queue, new vs revisions, review, approve / reject / request changes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Campaign Approvals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approve a campaign.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Promo Codes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary, create code, add brand credit, table (applies to, dates, usage)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Promo Codes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a code.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Shoppers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List (status, wallet, redemptions, referrals, brand suspensions, last activity)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Searchable list (name, email, phone, Shopper ID) with account status, wallet, redemptions, referrals, brand suspensions, last activity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Shoppers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search a shopper by email.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detail tabs (overview, wallet ledger, claims &amp; reviews, referrals, suspensions), purchase activity, cooldowns, adjust wallet, internal note, global suspend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selected shopper: identity + status; tabs Overview (account &amp; payout, wallet: available / pending / lifetime paid, purchase activity: brands + retailers, active cooldowns, internal notes), Wallet Ledger, Claims &amp; Reviews (cancel claim), Referrals, Suspensions; Adjust Wallet (credit/debit, reason required, before/after audit), Add Internal Note, Global Suspend / Reactivate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Shoppers → shopper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjust a wallet with a reason; add a note; check the ledger tab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#46, #51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Suspensions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary, list, review (remove brand suspension, global suspend), repeated-suspension alert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Suspensions page: summary (active brand suspensions, repeat suspensions, global suspensions), searchable list (brand, reason, date, prior count, status) with date/status filters; detail with View Shopper, Remove Brand Suspension, Globally Suspend; repeated suspensions alert only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Suspensions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remove a brand suspension; globally suspend a shopper.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Referrals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary, filters, details, flag review (approve / reject / suspend)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Referrals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open the Flagged tab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Revenue Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sources, promo credits used, refunds, processing costs, net revenue, trend chart, brand contribution + export</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Analytics page: revenue sources, promotional credits used, refunds, processing costs, net revenue, brand-funded rewards; daily Revenue Trend chart; Brand Revenue Contribution (credits + processing per brand) with category / plan filters and Export CSV.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switch the date range; export the CSV.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Processing costs are estimates (Stripe 2.9% + $0.30 per wallet top-up; $0.25 per payout). Refunds = brand wallet cash returned, shown but not deducted from revenue.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Receipt Brand Discovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary, filters, leads, brand insight, export</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Brand Discovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a lead.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand detected from receipt text.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin — Settings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Withdrawal review rules · Discovery ranking · device/network limits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change a threshold.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#50, #51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referral flag rules: duplicate payout identity, same device, self-referral, unusual referral volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toggles for the Master rules: duplicate payout identity, same device, self-referral (same name / email / phone, Gmail dots and +tags ignored), unusual referral volume (limit per 7 days); same-network and fraud-signal checks kept as additional toggles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turn a rule off; a matching referral no longer gets flagged.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin Users (staff roles) + View Audit Log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin Users: list, + Add User (Administrator / Operations / Analytics; new admins set their password through the emailed code), change role, remove access; Analytics is read-only and only Administrators change Settings or Admin Users; View Audit Log (latest 200 sensitive actions).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Settings → Admin Users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add an Analytics user; they can view pages but can't save changes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross-cutting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraud &amp; abuse: duplicates, velocity, device / IP / browser checks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin → Users → user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create 3 accounts on one browser.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App must send X-Device-Id.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipt retention / cleanup (full receipt 30 days, then matching line only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scheduled job (every 15 min) deletes receipt images 30 days after submission (pending receipts are skipped) and records when; matching line items and receipt details stay.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend job</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automated test: a 31-day-old receipt loses its image and keeps the matching line.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ships switched off in production (RECEIPT_IMAGE_PURGE_ENABLED) until the owner approves deleting existing receipt photos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System email via AWS SES with bounce / complaint handling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All system email now goes through Amazon SES as Nibbl &lt;no-reply@joinnibbl.com&gt; (DKIM-signed domain, production access); bounces and complaints go to the SES suppression list.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any emailed code or notification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request an email code; check the sender.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Progress by Master Document Section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
   </si>
   <si>
     <t xml:space="preserve">Completion</t>
@@ -2611,7 +2617,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2662,14 +2668,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF1F3F5"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFFFF4E0"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -2687,14 +2685,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF1E7B3C"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5B6470"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3063,11 +3053,11 @@
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Completed")</f>
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Progress")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Review")</f>
@@ -3075,11 +3065,11 @@
       </c>
       <c r="G5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Planned")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5" t="n">
         <f aca="false">IF(C5&gt;0,D5/C5,0)</f>
-        <v>0.926666666666667</v>
+        <v>0.946666666666667</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4777,7 +4767,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="9" t="n">
         <v>49</v>
       </c>
@@ -4791,7 +4781,7 @@
         <v>240</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>220</v>
+        <v>29</v>
       </c>
       <c r="G57" s="10" t="s">
         <v>205</v>
@@ -4970,13 +4960,13 @@
         <v>206</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L62" s="12"/>
       <c r="M62" s="13" t="s">
@@ -4988,13 +4978,13 @@
         <v>55</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>29</v>
@@ -5006,15 +4996,15 @@
         <v>206</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K63" s="10"/>
       <c r="L63" s="12"/>
       <c r="M63" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5022,10 +5012,10 @@
         <v>56</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>59</v>
@@ -5043,14 +5033,14 @@
         <v>172</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L64" s="12"/>
       <c r="M64" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5058,10 +5048,10 @@
         <v>57</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>59</v>
@@ -5079,12 +5069,12 @@
         <v>172</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K65" s="10"/>
       <c r="L65" s="12"/>
       <c r="M65" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5092,13 +5082,13 @@
         <v>58</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>29</v>
@@ -5110,15 +5100,15 @@
         <v>206</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K66" s="10"/>
       <c r="L66" s="12"/>
       <c r="M66" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5126,13 +5116,13 @@
         <v>59</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>29</v>
@@ -5144,17 +5134,17 @@
         <v>206</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J67" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K67" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L67" s="12"/>
       <c r="M67" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5162,10 +5152,10 @@
         <v>60</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>59</v>
@@ -5180,15 +5170,15 @@
         <v>206</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K68" s="10"/>
       <c r="L68" s="12"/>
       <c r="M68" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5196,13 +5186,13 @@
         <v>61</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>29</v>
@@ -5214,15 +5204,15 @@
         <v>206</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K69" s="10"/>
       <c r="L69" s="12"/>
       <c r="M69" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5230,16 +5220,16 @@
         <v>62</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G70" s="10" t="s">
         <v>171</v>
@@ -5254,7 +5244,7 @@
         <v>31</v>
       </c>
       <c r="K70" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L70" s="12"/>
       <c r="M70" s="13" t="s">
@@ -5266,10 +5256,10 @@
         <v>63</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>59</v>
@@ -5284,15 +5274,15 @@
         <v>31</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J71" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K71" s="10"/>
       <c r="L71" s="12"/>
       <c r="M71" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5300,10 +5290,10 @@
         <v>64</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>59</v>
@@ -5318,15 +5308,15 @@
         <v>31</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K72" s="10"/>
       <c r="L72" s="12"/>
       <c r="M72" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5334,10 +5324,10 @@
         <v>65</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>59</v>
@@ -5352,7 +5342,7 @@
         <v>31</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J73" s="10" t="s">
         <v>111</v>
@@ -5360,7 +5350,7 @@
       <c r="K73" s="10"/>
       <c r="L73" s="12"/>
       <c r="M73" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5368,13 +5358,13 @@
         <v>66</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>29</v>
@@ -5386,15 +5376,15 @@
         <v>31</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K74" s="10"/>
       <c r="L74" s="12"/>
       <c r="M74" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5402,10 +5392,10 @@
         <v>67</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>59</v>
@@ -5420,15 +5410,15 @@
         <v>31</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J75" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K75" s="10"/>
       <c r="L75" s="12"/>
       <c r="M75" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5436,10 +5426,10 @@
         <v>68</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>59</v>
@@ -5454,15 +5444,15 @@
         <v>31</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K76" s="10"/>
       <c r="L76" s="12"/>
       <c r="M76" s="13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5470,13 +5460,13 @@
         <v>69</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F77" s="11" t="s">
         <v>29</v>
@@ -5488,15 +5478,15 @@
         <v>31</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K77" s="10"/>
       <c r="L77" s="12"/>
       <c r="M77" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5504,13 +5494,13 @@
         <v>70</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>29</v>
@@ -5522,7 +5512,7 @@
         <v>31</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J78" s="10" t="s">
         <v>111</v>
@@ -5530,7 +5520,7 @@
       <c r="K78" s="10"/>
       <c r="L78" s="12"/>
       <c r="M78" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5538,13 +5528,13 @@
         <v>71</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F79" s="11" t="s">
         <v>29</v>
@@ -5556,15 +5546,15 @@
         <v>31</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K79" s="10"/>
       <c r="L79" s="12"/>
       <c r="M79" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5572,13 +5562,13 @@
         <v>72</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F80" s="11" t="s">
         <v>29</v>
@@ -5590,15 +5580,15 @@
         <v>31</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K80" s="10"/>
       <c r="L80" s="12"/>
       <c r="M80" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5606,13 +5596,13 @@
         <v>73</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F81" s="11" t="s">
         <v>29</v>
@@ -5624,15 +5614,15 @@
         <v>31</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K81" s="10"/>
       <c r="L81" s="12"/>
       <c r="M81" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5640,13 +5630,13 @@
         <v>74</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F82" s="11" t="s">
         <v>29</v>
@@ -5658,15 +5648,15 @@
         <v>31</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K82" s="10"/>
       <c r="L82" s="12"/>
       <c r="M82" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5674,13 +5664,13 @@
         <v>75</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F83" s="11" t="s">
         <v>29</v>
@@ -5692,15 +5682,15 @@
         <v>31</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K83" s="10"/>
       <c r="L83" s="12"/>
       <c r="M83" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5708,10 +5698,10 @@
         <v>76</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>59</v>
@@ -5726,15 +5716,15 @@
         <v>31</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K84" s="10"/>
       <c r="L84" s="12"/>
       <c r="M84" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5742,13 +5732,13 @@
         <v>77</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F85" s="11" t="s">
         <v>29</v>
@@ -5760,15 +5750,15 @@
         <v>31</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K85" s="10"/>
       <c r="L85" s="12"/>
       <c r="M85" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5776,13 +5766,13 @@
         <v>78</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>29</v>
@@ -5794,15 +5784,15 @@
         <v>31</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K86" s="10"/>
       <c r="L86" s="12"/>
       <c r="M86" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5810,13 +5800,13 @@
         <v>79</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F87" s="11" t="s">
         <v>29</v>
@@ -5828,15 +5818,15 @@
         <v>31</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K87" s="10"/>
       <c r="L87" s="12"/>
       <c r="M87" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5844,13 +5834,13 @@
         <v>80</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F88" s="11" t="s">
         <v>29</v>
@@ -5865,12 +5855,12 @@
         <v>255</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K88" s="10"/>
       <c r="L88" s="12"/>
       <c r="M88" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5878,13 +5868,13 @@
         <v>81</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F89" s="11" t="s">
         <v>29</v>
@@ -5896,17 +5886,17 @@
         <v>206</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K89" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L89" s="12"/>
       <c r="M89" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5914,10 +5904,10 @@
         <v>82</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>59</v>
@@ -5940,7 +5930,7 @@
       <c r="K90" s="10"/>
       <c r="L90" s="12"/>
       <c r="M90" s="13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5948,10 +5938,10 @@
         <v>83</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>59</v>
@@ -5966,15 +5956,15 @@
         <v>206</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K91" s="10"/>
       <c r="L91" s="12"/>
       <c r="M91" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5982,16 +5972,16 @@
         <v>84</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G92" s="10" t="s">
         <v>171</v>
@@ -6006,11 +5996,11 @@
         <v>31</v>
       </c>
       <c r="K92" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L92" s="12"/>
       <c r="M92" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6018,13 +6008,13 @@
         <v>85</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F93" s="11" t="s">
         <v>29</v>
@@ -6036,15 +6026,15 @@
         <v>206</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K93" s="10"/>
       <c r="L93" s="12"/>
       <c r="M93" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6052,10 +6042,10 @@
         <v>86</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>59</v>
@@ -6070,15 +6060,15 @@
         <v>206</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K94" s="10"/>
       <c r="L94" s="12"/>
       <c r="M94" s="13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6086,16 +6076,16 @@
         <v>87</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G95" s="10" t="s">
         <v>205</v>
@@ -6104,17 +6094,17 @@
         <v>206</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K95" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L95" s="12"/>
       <c r="M95" s="13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6122,10 +6112,10 @@
         <v>88</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>59</v>
@@ -6140,15 +6130,15 @@
         <v>31</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K96" s="10"/>
       <c r="L96" s="12"/>
       <c r="M96" s="13" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6156,10 +6146,10 @@
         <v>89</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>59</v>
@@ -6174,15 +6164,15 @@
         <v>31</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K97" s="10"/>
       <c r="L97" s="12"/>
       <c r="M97" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6190,13 +6180,13 @@
         <v>90</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F98" s="11" t="s">
         <v>29</v>
@@ -6208,15 +6198,15 @@
         <v>31</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K98" s="10"/>
       <c r="L98" s="12"/>
       <c r="M98" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6224,13 +6214,13 @@
         <v>91</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F99" s="11" t="s">
         <v>29</v>
@@ -6242,15 +6232,15 @@
         <v>31</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K99" s="10"/>
       <c r="L99" s="12"/>
       <c r="M99" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6258,13 +6248,13 @@
         <v>92</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>29</v>
@@ -6276,15 +6266,15 @@
         <v>31</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K100" s="10"/>
       <c r="L100" s="12"/>
       <c r="M100" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6292,13 +6282,13 @@
         <v>93</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F101" s="11" t="s">
         <v>29</v>
@@ -6310,15 +6300,15 @@
         <v>31</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K101" s="10"/>
       <c r="L101" s="12"/>
       <c r="M101" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6326,13 +6316,13 @@
         <v>94</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>29</v>
@@ -6344,15 +6334,15 @@
         <v>31</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K102" s="10"/>
       <c r="L102" s="12"/>
       <c r="M102" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6360,10 +6350,10 @@
         <v>95</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>59</v>
@@ -6378,15 +6368,15 @@
         <v>31</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K103" s="10"/>
       <c r="L103" s="12"/>
       <c r="M103" s="13" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6394,10 +6384,10 @@
         <v>96</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>59</v>
@@ -6412,15 +6402,15 @@
         <v>31</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J104" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K104" s="10"/>
       <c r="L104" s="12"/>
       <c r="M104" s="13" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6428,10 +6418,10 @@
         <v>97</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>59</v>
@@ -6446,17 +6436,17 @@
         <v>31</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J105" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K105" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L105" s="12"/>
       <c r="M105" s="13" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6464,10 +6454,10 @@
         <v>98</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>59</v>
@@ -6482,15 +6472,15 @@
         <v>31</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K106" s="10"/>
       <c r="L106" s="12"/>
       <c r="M106" s="13" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6498,31 +6488,31 @@
         <v>99</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F107" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H107" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L107" s="12"/>
       <c r="M107" s="13" t="s">
@@ -6534,10 +6524,10 @@
         <v>100</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>59</v>
@@ -6552,15 +6542,15 @@
         <v>31</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K108" s="10"/>
       <c r="L108" s="12"/>
       <c r="M108" s="13" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6568,13 +6558,13 @@
         <v>101</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F109" s="11" t="s">
         <v>29</v>
@@ -6586,10 +6576,10 @@
         <v>31</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K109" s="10"/>
       <c r="L109" s="12"/>
@@ -6602,13 +6592,13 @@
         <v>102</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F110" s="11" t="s">
         <v>29</v>
@@ -6623,12 +6613,12 @@
         <v>172</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K110" s="10"/>
       <c r="L110" s="12"/>
       <c r="M110" s="13" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6636,10 +6626,10 @@
         <v>103</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>59</v>
@@ -6654,15 +6644,15 @@
         <v>31</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K111" s="10"/>
       <c r="L111" s="12"/>
       <c r="M111" s="13" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6670,10 +6660,10 @@
         <v>104</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>59</v>
@@ -6688,15 +6678,15 @@
         <v>31</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J112" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K112" s="10"/>
       <c r="L112" s="12"/>
       <c r="M112" s="13" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6704,13 +6694,13 @@
         <v>105</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F113" s="11" t="s">
         <v>220</v>
@@ -6722,17 +6712,17 @@
         <v>31</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K113" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L113" s="12"/>
       <c r="M113" s="13" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6740,10 +6730,10 @@
         <v>106</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>59</v>
@@ -6758,10 +6748,10 @@
         <v>31</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K114" s="10"/>
       <c r="L114" s="12"/>
@@ -6774,13 +6764,13 @@
         <v>107</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F115" s="11" t="s">
         <v>29</v>
@@ -6792,15 +6782,15 @@
         <v>31</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K115" s="10"/>
       <c r="L115" s="12"/>
       <c r="M115" s="13" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6808,10 +6798,10 @@
         <v>108</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>59</v>
@@ -6826,15 +6816,15 @@
         <v>31</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K116" s="10"/>
       <c r="L116" s="12"/>
       <c r="M116" s="13" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6842,10 +6832,10 @@
         <v>109</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>59</v>
@@ -6860,15 +6850,15 @@
         <v>31</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K117" s="10"/>
       <c r="L117" s="12"/>
       <c r="M117" s="13" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6876,13 +6866,13 @@
         <v>110</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F118" s="11" t="s">
         <v>29</v>
@@ -6894,7 +6884,7 @@
         <v>31</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J118" s="10" t="s">
         <v>228</v>
@@ -6902,7 +6892,7 @@
       <c r="K118" s="10"/>
       <c r="L118" s="12"/>
       <c r="M118" s="13" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6910,13 +6900,13 @@
         <v>111</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F119" s="11" t="s">
         <v>29</v>
@@ -6928,17 +6918,17 @@
         <v>31</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K119" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L119" s="12"/>
       <c r="M119" s="13" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6946,13 +6936,13 @@
         <v>112</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F120" s="11" t="s">
         <v>29</v>
@@ -6964,15 +6954,15 @@
         <v>31</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K120" s="10"/>
       <c r="L120" s="12"/>
       <c r="M120" s="13" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6980,13 +6970,13 @@
         <v>113</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F121" s="11" t="s">
         <v>29</v>
@@ -6998,15 +6988,15 @@
         <v>31</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J121" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K121" s="10"/>
       <c r="L121" s="12"/>
       <c r="M121" s="13" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7014,13 +7004,13 @@
         <v>114</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F122" s="11" t="s">
         <v>29</v>
@@ -7032,17 +7022,17 @@
         <v>31</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J122" s="10" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K122" s="10" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L122" s="12"/>
       <c r="M122" s="13" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7050,13 +7040,13 @@
         <v>115</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F123" s="11" t="s">
         <v>29</v>
@@ -7068,15 +7058,15 @@
         <v>31</v>
       </c>
       <c r="I123" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K123" s="10"/>
       <c r="L123" s="12"/>
       <c r="M123" s="13" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7084,13 +7074,13 @@
         <v>116</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F124" s="11" t="s">
         <v>29</v>
@@ -7102,15 +7092,15 @@
         <v>31</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K124" s="10"/>
       <c r="L124" s="12"/>
       <c r="M124" s="13" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7118,10 +7108,10 @@
         <v>117</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>59</v>
@@ -7136,15 +7126,15 @@
         <v>206</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K125" s="10"/>
       <c r="L125" s="12"/>
       <c r="M125" s="13" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7152,13 +7142,13 @@
         <v>118</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F126" s="11" t="s">
         <v>29</v>
@@ -7170,7 +7160,7 @@
         <v>206</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J126" s="10" t="s">
         <v>111</v>
@@ -7178,7 +7168,7 @@
       <c r="K126" s="10"/>
       <c r="L126" s="12"/>
       <c r="M126" s="13" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7186,13 +7176,13 @@
         <v>119</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F127" s="11" t="s">
         <v>29</v>
@@ -7204,15 +7194,15 @@
         <v>206</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K127" s="10"/>
       <c r="L127" s="12"/>
       <c r="M127" s="13" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7220,10 +7210,10 @@
         <v>120</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>59</v>
@@ -7238,15 +7228,15 @@
         <v>206</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K128" s="10"/>
       <c r="L128" s="12"/>
       <c r="M128" s="13" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7254,13 +7244,13 @@
         <v>121</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F129" s="11" t="s">
         <v>220</v>
@@ -7272,17 +7262,17 @@
         <v>206</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K129" s="10" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L129" s="12"/>
       <c r="M129" s="13" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7290,13 +7280,13 @@
         <v>122</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F130" s="11" t="s">
         <v>29</v>
@@ -7308,15 +7298,15 @@
         <v>206</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="K130" s="10"/>
       <c r="L130" s="12"/>
       <c r="M130" s="13" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7324,33 +7314,33 @@
         <v>123</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F131" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H131" s="10" t="s">
         <v>206</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K131" s="10"/>
       <c r="L131" s="12"/>
       <c r="M131" s="13" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7358,13 +7348,13 @@
         <v>124</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F132" s="11" t="s">
         <v>29</v>
@@ -7376,15 +7366,15 @@
         <v>206</v>
       </c>
       <c r="I132" s="10" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K132" s="10"/>
       <c r="L132" s="12"/>
       <c r="M132" s="13" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7392,13 +7382,13 @@
         <v>125</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F133" s="11" t="s">
         <v>29</v>
@@ -7410,15 +7400,15 @@
         <v>206</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J133" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K133" s="10"/>
       <c r="L133" s="12"/>
       <c r="M133" s="13" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7426,13 +7416,13 @@
         <v>126</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F134" s="11" t="s">
         <v>29</v>
@@ -7444,15 +7434,15 @@
         <v>206</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K134" s="10"/>
       <c r="L134" s="12"/>
       <c r="M134" s="13" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7460,10 +7450,10 @@
         <v>127</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>59</v>
@@ -7478,32 +7468,32 @@
         <v>206</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J135" s="10" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="K135" s="10"/>
       <c r="L135" s="12"/>
       <c r="M135" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B136" s="9" t="n">
         <v>128</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>563</v>
+        <v>29</v>
       </c>
       <c r="G136" s="10" t="s">
         <v>205</v>
@@ -7512,34 +7502,34 @@
         <v>206</v>
       </c>
       <c r="I136" s="10" t="s">
-        <v>31</v>
+        <v>564</v>
       </c>
       <c r="J136" s="10" t="s">
-        <v>31</v>
+        <v>565</v>
       </c>
       <c r="K136" s="10" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L136" s="12"/>
       <c r="M136" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B137" s="9" t="n">
         <v>129</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F137" s="11" t="s">
-        <v>220</v>
+        <v>29</v>
       </c>
       <c r="G137" s="10" t="s">
         <v>205</v>
@@ -7548,17 +7538,15 @@
         <v>206</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>568</v>
-      </c>
-      <c r="K137" s="10" t="s">
-        <v>569</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="K137" s="10"/>
       <c r="L137" s="12"/>
       <c r="M137" s="13" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7566,35 +7554,35 @@
         <v>130</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F138" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G138" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H138" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I138" s="10" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J138" s="10" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K138" s="10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L138" s="12"/>
       <c r="M138" s="13" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7602,13 +7590,13 @@
         <v>131</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F139" s="11" t="s">
         <v>29</v>
@@ -7620,17 +7608,17 @@
         <v>31</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="K139" s="10" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L139" s="12"/>
       <c r="M139" s="13" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7638,13 +7626,13 @@
         <v>132</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F140" s="11" t="s">
         <v>29</v>
@@ -7656,17 +7644,17 @@
         <v>31</v>
       </c>
       <c r="I140" s="10" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="J140" s="10" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K140" s="10" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L140" s="12"/>
       <c r="M140" s="13" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7674,13 +7662,13 @@
         <v>133</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F141" s="11" t="s">
         <v>29</v>
@@ -7692,15 +7680,15 @@
         <v>31</v>
       </c>
       <c r="I141" s="10" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J141" s="10" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K141" s="10"/>
       <c r="L141" s="12"/>
       <c r="M141" s="13" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7708,13 +7696,13 @@
         <v>134</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F142" s="11" t="s">
         <v>29</v>
@@ -7726,15 +7714,15 @@
         <v>31</v>
       </c>
       <c r="I142" s="10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K142" s="10"/>
       <c r="L142" s="12"/>
       <c r="M142" s="13" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7742,33 +7730,33 @@
         <v>135</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F143" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I143" s="10" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="K143" s="10"/>
       <c r="L143" s="12"/>
       <c r="M143" s="13" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7776,33 +7764,33 @@
         <v>136</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F144" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G144" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H144" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I144" s="10" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="J144" s="10" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K144" s="10"/>
       <c r="L144" s="12"/>
       <c r="M144" s="13" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7810,10 +7798,10 @@
         <v>137</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>59</v>
@@ -7822,21 +7810,21 @@
         <v>29</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I145" s="10" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J145" s="10" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="K145" s="10"/>
       <c r="L145" s="12"/>
       <c r="M145" s="13" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7844,10 +7832,10 @@
         <v>138</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E146" s="10" t="s">
         <v>59</v>
@@ -7856,21 +7844,21 @@
         <v>29</v>
       </c>
       <c r="G146" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H146" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="J146" s="10" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K146" s="10"/>
       <c r="L146" s="12"/>
       <c r="M146" s="13" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7878,33 +7866,33 @@
         <v>139</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F147" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H147" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I147" s="10" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J147" s="10" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="K147" s="10"/>
       <c r="L147" s="12"/>
       <c r="M147" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7912,33 +7900,33 @@
         <v>140</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F148" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H148" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I148" s="10" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="J148" s="10" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="K148" s="10"/>
       <c r="L148" s="12"/>
       <c r="M148" s="13" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7946,33 +7934,33 @@
         <v>141</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F149" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I149" s="10" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="J149" s="10" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K149" s="10"/>
       <c r="L149" s="12"/>
       <c r="M149" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7980,10 +7968,10 @@
         <v>142</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>59</v>
@@ -7992,21 +7980,21 @@
         <v>29</v>
       </c>
       <c r="G150" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H150" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I150" s="10" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="J150" s="10" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K150" s="10"/>
       <c r="L150" s="12"/>
       <c r="M150" s="13" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8014,35 +8002,35 @@
         <v>143</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F151" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H151" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I151" s="10" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="J151" s="10" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="K151" s="10" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L151" s="12"/>
       <c r="M151" s="13" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8050,10 +8038,10 @@
         <v>144</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>59</v>
@@ -8062,23 +8050,23 @@
         <v>29</v>
       </c>
       <c r="G152" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H152" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I152" s="10" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="J152" s="10" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="K152" s="10" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L152" s="12"/>
       <c r="M152" s="13" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8086,10 +8074,10 @@
         <v>145</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>59</v>
@@ -8098,7 +8086,7 @@
         <v>29</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H153" s="10" t="s">
         <v>31</v>
@@ -8107,12 +8095,12 @@
         <v>215</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="K153" s="10"/>
       <c r="L153" s="12"/>
       <c r="M153" s="13" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8120,13 +8108,13 @@
         <v>146</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E154" s="10" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F154" s="11" t="s">
         <v>29</v>
@@ -8141,12 +8129,12 @@
         <v>215</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="K154" s="10"/>
       <c r="L154" s="12"/>
       <c r="M154" s="13" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8154,33 +8142,33 @@
         <v>147</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F155" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H155" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I155" s="10" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J155" s="10" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="K155" s="10"/>
       <c r="L155" s="12"/>
       <c r="M155" s="13" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8188,10 +8176,10 @@
         <v>148</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D156" s="10" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E156" s="10" t="s">
         <v>59</v>
@@ -8206,17 +8194,17 @@
         <v>206</v>
       </c>
       <c r="I156" s="10" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J156" s="10" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="K156" s="10" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L156" s="12"/>
       <c r="M156" s="13" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8224,13 +8212,13 @@
         <v>149</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F157" s="11" t="s">
         <v>29</v>
@@ -8242,13 +8230,13 @@
         <v>31</v>
       </c>
       <c r="I157" s="10" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="J157" s="10" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K157" s="10" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L157" s="12"/>
       <c r="M157" s="13" t="s">
@@ -8260,13 +8248,13 @@
         <v>150</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E158" s="10" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F158" s="11" t="s">
         <v>29</v>
@@ -8278,10 +8266,10 @@
         <v>31</v>
       </c>
       <c r="I158" s="10" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="J158" s="10" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="K158" s="10"/>
       <c r="L158" s="12"/>
@@ -8292,16 +8280,16 @@
   </sheetData>
   <autoFilter ref="B8:M158"/>
   <conditionalFormatting sqref="F9:F158">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>"Completed"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>"In Review"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>"Planned"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8339,7 +8327,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8347,7 +8335,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>29</v>
@@ -8356,13 +8344,13 @@
         <v>220</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>563</v>
+        <v>681</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8607,11 +8595,11 @@
       </c>
       <c r="D13" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B13,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B13,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B13,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -8623,12 +8611,12 @@
       </c>
       <c r="H13" s="19" t="n">
         <f aca="false">IF(C13&gt;0,D13/C13,0)</f>
-        <v>0.714285714285714</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C14" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B14)</f>
@@ -8657,7 +8645,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C15" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B15)</f>
@@ -8686,7 +8674,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C16" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B16)</f>
@@ -8715,7 +8703,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B17)</f>
@@ -8744,7 +8732,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="17" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B18)</f>
@@ -8773,7 +8761,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C19" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B19)</f>
@@ -8802,7 +8790,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C20" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B20)</f>
@@ -8831,7 +8819,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="17" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B21)</f>
@@ -8860,7 +8848,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B22)</f>
@@ -8889,7 +8877,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B23)</f>
@@ -8918,7 +8906,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="17" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B24)</f>
@@ -8947,7 +8935,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="17" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C25" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B25)</f>
@@ -8976,7 +8964,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="17" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B26)</f>
@@ -9005,7 +8993,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C27" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B27)</f>
@@ -9034,7 +9022,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="17" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C28" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B28)</f>
@@ -9063,7 +9051,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="17" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C29" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B29)</f>
@@ -9092,7 +9080,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C30" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B30)</f>
@@ -9121,7 +9109,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="17" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C31" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B31)</f>
@@ -9150,7 +9138,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="17" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C32" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B32)</f>
@@ -9179,7 +9167,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="17" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C33" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B33)</f>
@@ -9208,7 +9196,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="17" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C34" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B34)</f>
@@ -9237,7 +9225,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="17" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C35" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B35)</f>
@@ -9266,7 +9254,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="17" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C36" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B36)</f>
@@ -9295,7 +9283,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="17" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C37" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B37)</f>
@@ -9303,11 +9291,11 @@
       </c>
       <c r="D37" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B37,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B37,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B37,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9315,16 +9303,16 @@
       </c>
       <c r="G37" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B37,'Master Requirements Tracker'!$F$9:$F$158,"Planned")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="19" t="n">
         <f aca="false">IF(C37&gt;0,D37/C37,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="17" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C38" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B38)</f>
@@ -9353,7 +9341,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C39" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B39)</f>
@@ -9382,7 +9370,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="17" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C40" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B40)</f>
@@ -9411,7 +9399,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="17" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C41" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B41)</f>
@@ -9440,7 +9428,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="17" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C42" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B42)</f>
@@ -9469,7 +9457,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="17" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C43" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B43)</f>
@@ -9498,7 +9486,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="17" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C44" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B44)</f>
@@ -9527,7 +9515,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="17" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C45" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B45)</f>
@@ -9556,7 +9544,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="17" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C46" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B46)</f>
@@ -9585,7 +9573,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="17" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C47" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B47)</f>
@@ -9614,7 +9602,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="17" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C48" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B48)</f>
@@ -9643,7 +9631,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="17" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C49" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B49)</f>
@@ -9672,7 +9660,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="20" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C50" s="21" t="n">
         <f aca="false">SUM(C5:C49)</f>
@@ -9680,11 +9668,11 @@
       </c>
       <c r="D50" s="21" t="n">
         <f aca="false">SUM(D5:D49)</f>
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">SUM(E5:E49)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F50" s="21" t="n">
         <f aca="false">SUM(F5:F49)</f>
@@ -9692,11 +9680,11 @@
       </c>
       <c r="G50" s="21" t="n">
         <f aca="false">SUM(G5:G49)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" s="22" t="n">
         <f aca="false">IF(C50&gt;0,D50/C50,0)</f>
-        <v>0.926666666666667</v>
+        <v>0.946666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -9727,18 +9715,18 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="23" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>18</v>
@@ -9746,13 +9734,13 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>220</v>
@@ -9760,13 +9748,13 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="24" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>220</v>
@@ -9774,13 +9762,13 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="24" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>29</v>
@@ -9788,27 +9776,27 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="24" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>220</v>
@@ -9816,13 +9804,13 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>29</v>
@@ -9830,58 +9818,58 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>563</v>
+        <v>681</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E5:E13">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>"Completed"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>"In Review"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>"Planned"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9916,15 +9904,15 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="26" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9932,7 +9920,7 @@
         <v>29</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9940,23 +9928,23 @@
         <v>220</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="26" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="26" t="s">
-        <v>563</v>
+        <v>681</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9964,7 +9952,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9972,15 +9960,15 @@
         <v>22</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="26" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9988,15 +9976,15 @@
         <v>20</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="26" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
   </sheetData>

--- a/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
+++ b/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="727">
   <si>
     <t xml:space="preserve">Nibbl AI — Master Requirements Tracker</t>
   </si>
@@ -686,648 +686,648 @@
     <t xml:space="preserve">Campaign cards on For You (not product cards), category tabs, up to 24 per category</t>
   </si>
   <si>
-    <t xml:space="preserve">Campaign cards with category tabs.</t>
+    <t xml:space="preserve">For You: campaign cards only (brand, headline, description, reward badge, Going fast, Buy at, 'N eligible products · View Products'), no campaign-level rating (each product shows its own on the deal page), category tabs starting with For You, up to 24 per category in one vertical list. Logged-out shoppers browse after Allow Location / Enter ZIP (kept in their browser).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → Browse Offers Nearby / Offer tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the site logged out, enter a ZIP, switch tabs, open a deal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile app: same API (documented).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retailer match = ranking boost; Any Retailer / Retailer Required verification (eligible / unclear → manual / ineligible)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload receipts from different stores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#10, #19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct entry: QR / Meta ad / URL bypasses geography only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open in a private window.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign-level suppression (never brand-wide)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim one campaign of a brand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper Rebate Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign details: products + ratings, Where to Buy, receipt eligibility, max rebate, offer eligibility, Going fast, share, save, Claim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offer page with all items.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper Website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → offer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open an offer; share and save.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#5, #10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserve Offer: prefill email/phone (collect if logged out), two required consents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserve Offer shows email + phone: prefilled when signed in (verified phone read-only), collected when logged out; both consents required. Logged-out shoppers open a deal from its link, then a 6-digit email code signs them in (or creates the account) before Confirm Reservation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → deal link → Continue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a deal link logged out, enter email + phone, enter the code, Confirm &amp; Reserve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile app: same API (documented for the app developer).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm Reservation screen: slot X of 5, exact deadline, Confirm &amp; Reserve (slot consumed only here)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot use shown on Reserve Offer; separate Confirm screen with product, retailer, reward, exact deadline and resulting slot use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → offer → Continue → Confirm &amp; Reserve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim an offer; check the deadline is 7 days out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reservation eligibility checked before a claim slot is consumed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All checks (consent, slots, already claimed, cooldown, dates, capacity, funds) run before the slot is used.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered by automated tests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#17, #18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active claim slots (5) — occupied until approval, final rejection or expiry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → My Rewards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim to the limit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Action Prompt: carousel, Submit Receipt + time left, Save for Later, My Offers badge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → home; header badge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim, then return home.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebate restriction pop-ups (10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 10 Master pop-ups (RB-33) with Master titles, messages, notes and buttons: Consent required (Review &amp; Accept), All 5 claim slots in use / Already claimed (View My Offers), Please wait — N days remaining, One-time redeemed, Not started (date), Paused or ended, Today's rebates claimed (Explore + View My Offers), Receipt from an eligible retailer required (View Eligible Retailers), Offer no longer available. The API returns the copy (title, message, note, days_remaining, starts_at).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → deal → Continue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger consent, already-claimed and cooldown cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt Submission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit inside the active campaign: requirements list, take/choose photo, review before submit, submitted state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-claim flow: Receipt Requirements (from the claim's locked terms), Take / Choose Photo, Review Your Receipt, Receipt submitted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → My Rewards → Upload receipt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload a receipt for a claim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt Validation &amp; Routing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture date/time, retailer, transaction no., item, qty, net price, tax, total; clear date/retailer fail → reject; uncertain → manual; unreadable → new photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload clear / unclear / wrong-date receipts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCR = AI service.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#19, #21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplicate receipt + quantity allocation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload the same receipt twice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt Outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One resubmission before the original deadline (deadline never restarts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First clear date/retailer rejection keeps the claim open with one resubmission; the second is final (claim closed, slot released). Purchase must be on or after the claim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload a receipt dated before the claim, then another.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outcome messages: accepted, manual review, unreadable, date, retailer, final rejection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master outcome screens: Purchase verified, Manual review, We couldn't read it, Date / Retailer does not qualify (with one resubmission), Final rejection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → after submitting a receipt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger each outcome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-app + email decision notifications are tracked in Notifications &amp; Reminders.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notifications &amp; Reminders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receipt reminders 48h and 12h before the exact deadline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheduled job sends both reminders.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reservation confirmation, receipt submitted, approval/rejection (in-app + email), claim expiration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All five sent immediately in-app; approval and rejection also emailed (SES).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → notifications; email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim, upload, get approved/rejected, let a claim expire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push notification delivery (FCM / APNs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push is a placeholder today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting on client Firebase Workload Identity setup (EC2 role sent).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Manual Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① Claim &amp; customer (email visible on every plan) · ② Full receipt viewer (zoom/rotate/download) · ③ Locked requirements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redemptions → Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a pending receipt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">④ Select line · ⑤ Confirm mapping + corrections (audit) · ⑥ Optional alias · ⑦ Calculated reward, rejection reasons, internal note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approve with alias; reject with reason.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Redemptions Page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① Summary (pending, approved, rejected, total paid) · ② Status tabs · ⑤ Priority queue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redemptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#21, #22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">③ Search &amp; filters (campaign, product, status, submitted date)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search, campaign, product (via campaign products), status tabs, date range.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter by campaign and product.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑥ Pagination &amp; Export CSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redemptions → Export CSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Export.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven-day automatic approval (max reward, labelled, no alias, slot released)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check countdown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPIs: total, pending 1–3★ response, average rating, review spend, cost per review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All five KPIs; spend from the wallet ledger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviews → Review Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare spend with the Wallet ledger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabs (All, Published, 7-Day Hold, Flagged, Removed) + date range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabs with counts + date range + keyword search.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filters: rating, retailer, product, region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All four (retailer from the receipt, region from the shopper's state).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter by retailer and region.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review details: answers, final text, receipt evidence + gating summary, customer contact for service recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side panel with answers, receipt, gating summary, masked email + copy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Management → review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#26, #33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low-rating response: countdown, Contact Customer, Add Brand Response, Flag for Removal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live countdown, Contact Customer (email), response, flag.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a 2★ held review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flag reasons per Master (wrong product, unrelated, spam/fraud, PII, profanity, prohibited claim, other) + audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master's 7 reasons, 500-char details, audit log.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Management → Flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flag a review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Export: Download CSV + Download Reviews; API integration Coming Soon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSV + readable reviews file, both with disclosure; API Coming Soon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Management → Export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Download both.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create Review Campaign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basics (required image), eligible products, controls, locked rules &amp; cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviews → Create</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a review campaign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand question pool: add, suggest, Test Review Chat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Question pool: add, remove, ✨ Suggest Questions, and Test Review Chat (the same planned questions with answer chips and the AI draft; nothing saved or paid).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Campaigns → Create / campaign page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run Test Review Chat to the draft.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save Draft / Submit for Nibbl Review (published after review)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save Draft / Submit for Nibbl Review; Admin → Campaign Approvals → Review campaigns tab: Approve / Request changes / Reject (comment required); brand sees status + Nibbl's comment and resubmits. Approved campaigns can be paused and resumed. Campaigns live before this release were grandfathered as approved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review Campaigns; Admin → Campaign Approvals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit a campaign, request changes in Admin, resubmit, approve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live shopper preview (mobile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live mobile preview of the shopper's review card (campaign image, Share your voice, $1 reward, 30 days left, Purchase verified, Claim $1) updates as the brand edits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change the image / products; the preview updates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopper Review Opportunity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Offers: Review Rewards card (Claim $1, Save for Later)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review cards in the carousel and My Rewards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get a receipt verified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Confirmed · Multiple Matches · Missing Consent · Share Your Voice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website: review card (Share your voice · $1 · days left · Claim $1) → Product Confirmed (or This isn't my product) → Multiple Matches when receipt wording fits several variants → Missing Consent only when missing → Share Your Voice → chat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → My Offers → review card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy a product sold in two flavors under one name; pick the right one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile app screens are the app developer's.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer rules: scan all lines, 0/1/many opportunities, cooldown per shopper+product, $1 reserve, no second verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Chat Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product context loaded; rotating brand question; generated title &amp; review; edit; regenerate; final approval; $1 at any rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → review chat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete a review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five adaptive product questions with suggested answer chips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed AI questions today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adaptive questions wait on the AI service endpoint; suggested-answer chips not built.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separate 'recommend' and 'purchase again' questions; title 100 / body 500 limits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separate recommend and buy-again questions with Yes, definitely / Maybe / No chips (answers saved as would-recommend / would-buy-again); title ≤ 100 and body ≤ 500 with counters, AI drafts trimmed to fit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete a review; check the counters and chips.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratings &amp; Reviews Display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratings per product in campaign details; all reviews with sorting; review details + brand response; helpful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website → offer → reviews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort and mark helpful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviews overview: rating, breakdown, % recommend, % would buy again, AI summary (positives + improvement)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rating, star breakdown, % recommend and % would buy again on the product reviews overview.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open an offer with reviews.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI summary (positives + improvement) waits on the AI service's summary endpoint; the backend hook is ready.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost &amp; Results · Customer &amp; Conversion · Campaign Performance (25-hour cycles)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare cost with the ledger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary, search &amp; filters, download opted-in, integrations Coming Soon, consent withdrawal rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter and download.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table: brand activity, site activity, open claims, cooldowns, last active, status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columns per Master: Customer, Contact, Brand Activity (claims / rebates / reviews), Site Activity (total claims / % completion / reviews), Open Claims, Cooldowns (days left), Last Active, Status (Active / Banned), View. Tabs: All, Open Claim, Active Cooldown, Completed Rebate, Banned, Inactive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Customers; check each column and tab against a shopper with an open claim and a cooldown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header (opt-in badges, status) + Ban Customer with reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header: name, contact, customer since, last active, Nibbl Opt-In + brand Opt-In badges, Active/Banned. Ban modal with reason (suspicious activity, altered receipts, abuse, other); banned shoppers can't claim or get review opportunities from the brand; existing claims stay valid. Lift Ban.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers → View → Ban Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ban with a reason; status shows Banned with the reason; Lift Ban restores it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relationship with brand · Nibbl activity totals · Recent activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relationship tiles (claims, completed rebates, conversion, rewards, reviews, open claims); Nibbl totals only (claims, completion, reviews, rewards) — other brands' data never shown; recent activity timeline for this brand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers → View</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a profile; totals match the shopper's history.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open claims · Cooldowns with Remove (confirmation + audit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open claims with days left. Rebate and review cooldowns with Remove → confirmation → cooldown cleared and an audit-log entry (who, when, which). Managers only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers → View → Cooldowns → Remove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove a cooldown; the shopper can claim/review again; the audit log shows the removal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redemption history: full receipt 30 days, then matching line only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redemption history with View receipt + days left for 30 days; afterwards only the matching line item(s) are shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers → View → Redemption History</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recent receipt shows View receipt; one older than 30 days shows Matching line only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Wallet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balances: Available, Reserved, Promotional (definitions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check balances.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign Funding: 7-day need vs Available, funded status, reservations split</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet → Campaign Funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activate a campaign.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatic refill (Stripe): trigger 25%, fixed amount, recommendation, failure alert</t>
   </si>
   <si>
     <t xml:space="preserve">In Progress</t>
   </si>
   <si>
-    <t xml:space="preserve">Browse a category.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-per-category cap and 'N eligible products' line to confirm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retailer match = ranking boost; Any Retailer / Retailer Required verification (eligible / unclear → manual / ineligible)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload receipts from different stores.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#10, #19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct entry: QR / Meta ad / URL bypasses geography only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open in a private window.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign-level suppression (never brand-wide)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim one campaign of a brand.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper Rebate Flow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign details: products + ratings, Where to Buy, receipt eligibility, max rebate, offer eligibility, Going fast, share, save, Claim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Offer page with all items.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper Website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → offer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open an offer; share and save.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#5, #10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserve Offer: prefill email/phone (collect if logged out), two required consents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserve Offer shows email + phone: prefilled when signed in (verified phone read-only), collected when logged out; both consents required. Logged-out shoppers open a deal from its link, then a 6-digit email code signs them in (or creates the account) before Confirm Reservation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → deal link → Continue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a deal link logged out, enter email + phone, enter the code, Confirm &amp; Reserve.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile app: same API (documented for the app developer).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm Reservation screen: slot X of 5, exact deadline, Confirm &amp; Reserve (slot consumed only here)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slot use shown on Reserve Offer; separate Confirm screen with product, retailer, reward, exact deadline and resulting slot use.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → offer → Continue → Confirm &amp; Reserve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim an offer; check the deadline is 7 days out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reservation eligibility checked before a claim slot is consumed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All checks (consent, slots, already claimed, cooldown, dates, capacity, funds) run before the slot is used.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered by automated tests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#17, #18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active claim slots (5) — occupied until approval, final rejection or expiry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → My Rewards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim to the limit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return Action Prompt: carousel, Submit Receipt + time left, Save for Later, My Offers badge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → home; header badge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim, then return home.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebate restriction pop-ups (10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All with own code; consent, slots, claimed, cooldown, one-time, not started, paused, capacity, funds; retailer shown on offer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → offer → Claim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger each case.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align titles/buttons exactly with the Master pop-up mockup (e.g. 'Review &amp; Accept', 'N days remaining', 'View Eligible Retailers').</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipt Submission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit inside the active campaign: requirements list, take/choose photo, review before submit, submitted state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-claim flow: Receipt Requirements (from the claim's locked terms), Take / Choose Photo, Review Your Receipt, Receipt submitted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → My Rewards → Upload receipt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload a receipt for a claim.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipt Validation &amp; Routing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capture date/time, retailer, transaction no., item, qty, net price, tax, total; clear date/retailer fail → reject; uncertain → manual; unreadable → new photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload clear / unclear / wrong-date receipts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OCR = AI service.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#19, #21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duplicate receipt + quantity allocation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload the same receipt twice.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipt Outcomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One resubmission before the original deadline (deadline never restarts)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First clear date/retailer rejection keeps the claim open with one resubmission; the second is final (claim closed, slot released). Purchase must be on or after the claim.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload a receipt dated before the claim, then another.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outcome messages: accepted, manual review, unreadable, date, retailer, final rejection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master outcome screens: Purchase verified, Manual review, We couldn't read it, Date / Retailer does not qualify (with one resubmission), Final rejection.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → after submitting a receipt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger each outcome.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-app + email decision notifications are tracked in Notifications &amp; Reminders.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications &amp; Reminders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receipt reminders 48h and 12h before the exact deadline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scheduled job sends both reminders.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reservation confirmation, receipt submitted, approval/rejection (in-app + email), claim expiration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All five sent immediately in-app; approval and rejection also emailed (SES).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → notifications; email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim, upload, get approved/rejected, let a claim expire.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Push notification delivery (FCM / APNs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Push is a placeholder today.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting on client Firebase Workload Identity setup (EC2 role sent).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Manual Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① Claim &amp; customer (email visible on every plan) · ② Full receipt viewer (zoom/rotate/download) · ③ Locked requirements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redemptions → Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a pending receipt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">④ Select line · ⑤ Confirm mapping + corrections (audit) · ⑥ Optional alias · ⑦ Calculated reward, rejection reasons, internal note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approve with alias; reject with reason.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Redemptions Page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① Summary (pending, approved, rejected, total paid) · ② Status tabs · ⑤ Priority queue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redemptions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#21, #22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">③ Search &amp; filters (campaign, product, status, submitted date)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search, campaign, product (via campaign products), status tabs, date range.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter by campaign and product.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⑥ Pagination &amp; Export CSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redemptions → Export CSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Export.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven-day automatic approval (max reward, labelled, no alias, slot released)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check countdown.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPIs: total, pending 1–3★ response, average rating, review spend, cost per review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All five KPIs; spend from the wallet ledger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviews → Review Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare spend with the Wallet ledger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabs (All, Published, 7-Day Hold, Flagged, Removed) + date range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabs with counts + date range + keyword search.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filters: rating, retailer, product, region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All four (retailer from the receipt, region from the shopper's state).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter by retailer and region.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review details: answers, final text, receipt evidence + gating summary, customer contact for service recovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Side panel with answers, receipt, gating summary, masked email + copy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Management → review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#26, #33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low-rating response: countdown, Contact Customer, Add Brand Response, Flag for Removal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live countdown, Contact Customer (email), response, flag.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a 2★ held review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flag reasons per Master (wrong product, unrelated, spam/fraud, PII, profanity, prohibited claim, other) + audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master's 7 reasons, 500-char details, audit log.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Management → Flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flag a review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Export: Download CSV + Download Reviews; API integration Coming Soon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSV + readable reviews file, both with disclosure; API Coming Soon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Management → Export</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Download both.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create Review Campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basics (required image), eligible products, controls, locked rules &amp; cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviews → Create</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create a review campaign.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand question pool: add, suggest, Test Review Chat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Question pool: add, remove, ✨ Suggest Questions, and Test Review Chat (the same planned questions with answer chips and the AI draft; nothing saved or paid).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Campaigns → Create / campaign page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run Test Review Chat to the draft.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save Draft / Submit for Nibbl Review (published after review)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save Draft / Submit for Nibbl Review; Admin → Campaign Approvals → Review campaigns tab: Approve / Request changes / Reject (comment required); brand sees status + Nibbl's comment and resubmits. Approved campaigns can be paused and resumed. Campaigns live before this release were grandfathered as approved.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Campaigns; Admin → Campaign Approvals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit a campaign, request changes in Admin, resubmit, approve.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live shopper preview (mobile)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live mobile preview of the shopper's review card (campaign image, Share your voice, $1 reward, 30 days left, Purchase verified, Claim $1) updates as the brand edits.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change the image / products; the preview updates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopper Review Opportunity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Offers: Review Rewards card (Claim $1, Save for Later)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review cards in the carousel and My Rewards.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Get a receipt verified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Confirmed · Multiple Matches · Missing Consent · Share Your Voice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website: review card (Share your voice · $1 · days left · Claim $1) → Product Confirmed (or This isn't my product) → Multiple Matches when receipt wording fits several variants → Missing Consent only when missing → Share Your Voice → chat.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → My Offers → review card</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy a product sold in two flavors under one name; pick the right one.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile app screens are the app developer's.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer rules: scan all lines, 0/1/many opportunities, cooldown per shopper+product, $1 reserve, no second verification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Chat Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product context loaded; rotating brand question; generated title &amp; review; edit; regenerate; final approval; $1 at any rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → review chat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete a review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Five adaptive product questions with suggested answer chips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed AI questions today.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adaptive questions wait on the AI service endpoint; suggested-answer chips not built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Separate 'recommend' and 'purchase again' questions; title 100 / body 500 limits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Separate recommend and buy-again questions with Yes, definitely / Maybe / No chips (answers saved as would-recommend / would-buy-again); title ≤ 100 and body ≤ 500 with counters, AI drafts trimmed to fit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete a review; check the counters and chips.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratings &amp; Reviews Display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratings per product in campaign details; all reviews with sorting; review details + brand response; helpful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website → offer → reviews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sort and mark helpful.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reviews overview: rating, breakdown, % recommend, % would buy again, AI summary (positives + improvement)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rating, star breakdown, % recommend and % would buy again on the product reviews overview.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open an offer with reviews.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI summary (positives + improvement) waits on the AI service's summary endpoint; the backend hook is ready.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost &amp; Results · Customer &amp; Conversion · Campaign Performance (25-hour cycles)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compare cost with the ledger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary, search &amp; filters, download opted-in, integrations Coming Soon, consent withdrawal rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter and download.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table: brand activity, site activity, open claims, cooldowns, last active, status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columns per Master: Customer, Contact, Brand Activity (claims / rebates / reviews), Site Activity (total claims / % completion / reviews), Open Claims, Cooldowns (days left), Last Active, Status (Active / Banned), View. Tabs: All, Open Claim, Active Cooldown, Completed Rebate, Banned, Inactive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Customers; check each column and tab against a shopper with an open claim and a cooldown.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header (opt-in badges, status) + Ban Customer with reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Header: name, contact, customer since, last active, Nibbl Opt-In + brand Opt-In badges, Active/Banned. Ban modal with reason (suspicious activity, altered receipts, abuse, other); banned shoppers can't claim or get review opportunities from the brand; existing claims stay valid. Lift Ban.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customers → View → Ban Customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ban with a reason; status shows Banned with the reason; Lift Ban restores it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relationship with brand · Nibbl activity totals · Recent activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relationship tiles (claims, completed rebates, conversion, rewards, reviews, open claims); Nibbl totals only (claims, completion, reviews, rewards) — other brands' data never shown; recent activity timeline for this brand.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customers → View</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open a profile; totals match the shopper's history.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open claims · Cooldowns with Remove (confirmation + audit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open claims with days left. Rebate and review cooldowns with Remove → confirmation → cooldown cleared and an audit-log entry (who, when, which). Managers only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customers → View → Cooldowns → Remove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remove a cooldown; the shopper can claim/review again; the audit log shows the removal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redemption history: full receipt 30 days, then matching line only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redemption history with View receipt + days left for 30 days; afterwards only the matching line item(s) are shown.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customers → View → Redemption History</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recent receipt shows View receipt; one older than 30 days shows Matching line only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Wallet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balances: Available, Reserved, Promotional (definitions)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check balances.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campaign Funding: 7-day need vs Available, funded status, reservations split</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet → Campaign Funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activate a campaign.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatic refill (Stripe): trigger 25%, fixed amount, recommendation, failure alert</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wallet → Auto-refill</t>
   </si>
   <si>
@@ -1725,9 +1725,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sign in with a code; open My Offers, Wallet and Profile.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile app: same API (documented).</t>
   </si>
   <si>
     <t xml:space="preserve">Profile &amp; account security: verified phone locked; change via admin with re-verification; history</t>
@@ -3053,11 +3050,11 @@
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Completed")</f>
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Progress")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Review")</f>
@@ -3069,7 +3066,7 @@
       </c>
       <c r="H5" s="5" t="n">
         <f aca="false">IF(C5&gt;0,D5/C5,0)</f>
-        <v>0.946666666666667</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4595,7 +4592,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="9" t="n">
         <v>44</v>
       </c>
@@ -4609,7 +4606,7 @@
         <v>219</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>220</v>
+        <v>29</v>
       </c>
       <c r="G52" s="10" t="s">
         <v>205</v>
@@ -4618,7 +4615,7 @@
         <v>206</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="J52" s="10" t="s">
         <v>221</v>
@@ -4937,7 +4934,7 @@
       <c r="L61" s="12"/>
       <c r="M61" s="13"/>
     </row>
-    <row r="62" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="159.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="9" t="n">
         <v>54</v>
       </c>
@@ -4951,7 +4948,7 @@
         <v>261</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>220</v>
+        <v>29</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>205</v>
@@ -4965,9 +4962,7 @@
       <c r="J62" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="K62" s="10" t="s">
-        <v>264</v>
-      </c>
+      <c r="K62" s="10"/>
       <c r="L62" s="12"/>
       <c r="M62" s="13" t="s">
         <v>253</v>
@@ -4978,13 +4973,13 @@
         <v>55</v>
       </c>
       <c r="C63" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="D63" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="E63" s="10" t="s">
         <v>266</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>267</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>29</v>
@@ -4996,15 +4991,15 @@
         <v>206</v>
       </c>
       <c r="I63" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="J63" s="10" t="s">
         <v>268</v>
-      </c>
-      <c r="J63" s="10" t="s">
-        <v>269</v>
       </c>
       <c r="K63" s="10"/>
       <c r="L63" s="12"/>
       <c r="M63" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5012,10 +5007,10 @@
         <v>56</v>
       </c>
       <c r="C64" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D64" s="10" t="s">
         <v>271</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>272</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>59</v>
@@ -5033,14 +5028,14 @@
         <v>172</v>
       </c>
       <c r="J64" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="K64" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="K64" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="L64" s="12"/>
       <c r="M64" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5048,10 +5043,10 @@
         <v>57</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>59</v>
@@ -5069,12 +5064,12 @@
         <v>172</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K65" s="10"/>
       <c r="L65" s="12"/>
       <c r="M65" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5082,13 +5077,13 @@
         <v>58</v>
       </c>
       <c r="C66" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D66" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="E66" s="10" t="s">
         <v>279</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>280</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>29</v>
@@ -5100,15 +5095,15 @@
         <v>206</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K66" s="10"/>
       <c r="L66" s="12"/>
       <c r="M66" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5116,13 +5111,13 @@
         <v>59</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D67" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="E67" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>283</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>29</v>
@@ -5134,17 +5129,17 @@
         <v>206</v>
       </c>
       <c r="I67" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="J67" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="J67" s="10" t="s">
+      <c r="K67" s="10" t="s">
         <v>285</v>
-      </c>
-      <c r="K67" s="10" t="s">
-        <v>286</v>
       </c>
       <c r="L67" s="12"/>
       <c r="M67" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5152,10 +5147,10 @@
         <v>60</v>
       </c>
       <c r="C68" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="D68" s="10" t="s">
         <v>287</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>59</v>
@@ -5170,15 +5165,15 @@
         <v>206</v>
       </c>
       <c r="I68" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J68" s="10" t="s">
         <v>289</v>
-      </c>
-      <c r="J68" s="10" t="s">
-        <v>290</v>
       </c>
       <c r="K68" s="10"/>
       <c r="L68" s="12"/>
       <c r="M68" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5186,13 +5181,13 @@
         <v>61</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D69" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="E69" s="10" t="s">
         <v>292</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>293</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>29</v>
@@ -5204,15 +5199,15 @@
         <v>206</v>
       </c>
       <c r="I69" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="J69" s="10" t="s">
         <v>294</v>
-      </c>
-      <c r="J69" s="10" t="s">
-        <v>295</v>
       </c>
       <c r="K69" s="10"/>
       <c r="L69" s="12"/>
       <c r="M69" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5220,16 +5215,16 @@
         <v>62</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D70" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="E70" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="E70" s="10" t="s">
+      <c r="F70" s="11" t="s">
         <v>297</v>
-      </c>
-      <c r="F70" s="11" t="s">
-        <v>298</v>
       </c>
       <c r="G70" s="10" t="s">
         <v>171</v>
@@ -5244,7 +5239,7 @@
         <v>31</v>
       </c>
       <c r="K70" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L70" s="12"/>
       <c r="M70" s="13" t="s">
@@ -5256,10 +5251,10 @@
         <v>63</v>
       </c>
       <c r="C71" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="D71" s="10" t="s">
         <v>300</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>301</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>59</v>
@@ -5274,15 +5269,15 @@
         <v>31</v>
       </c>
       <c r="I71" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="J71" s="10" t="s">
         <v>302</v>
-      </c>
-      <c r="J71" s="10" t="s">
-        <v>303</v>
       </c>
       <c r="K71" s="10"/>
       <c r="L71" s="12"/>
       <c r="M71" s="13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5290,10 +5285,10 @@
         <v>64</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>59</v>
@@ -5308,15 +5303,15 @@
         <v>31</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K72" s="10"/>
       <c r="L72" s="12"/>
       <c r="M72" s="13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5324,10 +5319,10 @@
         <v>65</v>
       </c>
       <c r="C73" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="D73" s="10" t="s">
         <v>307</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>308</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>59</v>
@@ -5342,7 +5337,7 @@
         <v>31</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J73" s="10" t="s">
         <v>111</v>
@@ -5350,7 +5345,7 @@
       <c r="K73" s="10"/>
       <c r="L73" s="12"/>
       <c r="M73" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5358,13 +5353,13 @@
         <v>66</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D74" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="E74" s="10" t="s">
         <v>311</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>312</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>29</v>
@@ -5376,15 +5371,15 @@
         <v>31</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K74" s="10"/>
       <c r="L74" s="12"/>
       <c r="M74" s="13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5392,10 +5387,10 @@
         <v>67</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>59</v>
@@ -5410,15 +5405,15 @@
         <v>31</v>
       </c>
       <c r="I75" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="J75" s="10" t="s">
         <v>315</v>
-      </c>
-      <c r="J75" s="10" t="s">
-        <v>316</v>
       </c>
       <c r="K75" s="10"/>
       <c r="L75" s="12"/>
       <c r="M75" s="13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5426,10 +5421,10 @@
         <v>68</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>59</v>
@@ -5444,15 +5439,15 @@
         <v>31</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="K76" s="10"/>
       <c r="L76" s="12"/>
       <c r="M76" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5460,13 +5455,13 @@
         <v>69</v>
       </c>
       <c r="C77" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="D77" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="D77" s="10" t="s">
+      <c r="E77" s="10" t="s">
         <v>321</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>322</v>
       </c>
       <c r="F77" s="11" t="s">
         <v>29</v>
@@ -5478,15 +5473,15 @@
         <v>31</v>
       </c>
       <c r="I77" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="J77" s="10" t="s">
         <v>323</v>
-      </c>
-      <c r="J77" s="10" t="s">
-        <v>324</v>
       </c>
       <c r="K77" s="10"/>
       <c r="L77" s="12"/>
       <c r="M77" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5494,13 +5489,13 @@
         <v>70</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D78" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="E78" s="10" t="s">
         <v>326</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>327</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>29</v>
@@ -5512,7 +5507,7 @@
         <v>31</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J78" s="10" t="s">
         <v>111</v>
@@ -5520,7 +5515,7 @@
       <c r="K78" s="10"/>
       <c r="L78" s="12"/>
       <c r="M78" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5528,13 +5523,13 @@
         <v>71</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D79" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="E79" s="10" t="s">
         <v>328</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>329</v>
       </c>
       <c r="F79" s="11" t="s">
         <v>29</v>
@@ -5546,15 +5541,15 @@
         <v>31</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K79" s="10"/>
       <c r="L79" s="12"/>
       <c r="M79" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5562,13 +5557,13 @@
         <v>72</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D80" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="E80" s="10" t="s">
         <v>331</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>332</v>
       </c>
       <c r="F80" s="11" t="s">
         <v>29</v>
@@ -5580,15 +5575,15 @@
         <v>31</v>
       </c>
       <c r="I80" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="J80" s="10" t="s">
         <v>333</v>
-      </c>
-      <c r="J80" s="10" t="s">
-        <v>334</v>
       </c>
       <c r="K80" s="10"/>
       <c r="L80" s="12"/>
       <c r="M80" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5596,13 +5591,13 @@
         <v>73</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D81" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="E81" s="10" t="s">
         <v>336</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>337</v>
       </c>
       <c r="F81" s="11" t="s">
         <v>29</v>
@@ -5614,15 +5609,15 @@
         <v>31</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K81" s="10"/>
       <c r="L81" s="12"/>
       <c r="M81" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5630,13 +5625,13 @@
         <v>74</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D82" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="E82" s="10" t="s">
         <v>339</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>340</v>
       </c>
       <c r="F82" s="11" t="s">
         <v>29</v>
@@ -5648,15 +5643,15 @@
         <v>31</v>
       </c>
       <c r="I82" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="J82" s="10" t="s">
         <v>341</v>
-      </c>
-      <c r="J82" s="10" t="s">
-        <v>342</v>
       </c>
       <c r="K82" s="10"/>
       <c r="L82" s="12"/>
       <c r="M82" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5664,13 +5659,13 @@
         <v>75</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D83" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="E83" s="10" t="s">
         <v>343</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>344</v>
       </c>
       <c r="F83" s="11" t="s">
         <v>29</v>
@@ -5682,15 +5677,15 @@
         <v>31</v>
       </c>
       <c r="I83" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="J83" s="10" t="s">
         <v>345</v>
-      </c>
-      <c r="J83" s="10" t="s">
-        <v>346</v>
       </c>
       <c r="K83" s="10"/>
       <c r="L83" s="12"/>
       <c r="M83" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5698,10 +5693,10 @@
         <v>76</v>
       </c>
       <c r="C84" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="D84" s="10" t="s">
         <v>347</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>348</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>59</v>
@@ -5716,15 +5711,15 @@
         <v>31</v>
       </c>
       <c r="I84" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="J84" s="10" t="s">
         <v>349</v>
-      </c>
-      <c r="J84" s="10" t="s">
-        <v>350</v>
       </c>
       <c r="K84" s="10"/>
       <c r="L84" s="12"/>
       <c r="M84" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5732,13 +5727,13 @@
         <v>77</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D85" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="E85" s="10" t="s">
         <v>352</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>353</v>
       </c>
       <c r="F85" s="11" t="s">
         <v>29</v>
@@ -5750,15 +5745,15 @@
         <v>31</v>
       </c>
       <c r="I85" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="J85" s="10" t="s">
         <v>354</v>
-      </c>
-      <c r="J85" s="10" t="s">
-        <v>355</v>
       </c>
       <c r="K85" s="10"/>
       <c r="L85" s="12"/>
       <c r="M85" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5766,13 +5761,13 @@
         <v>78</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D86" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="E86" s="10" t="s">
         <v>356</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>357</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>29</v>
@@ -5784,15 +5779,15 @@
         <v>31</v>
       </c>
       <c r="I86" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="J86" s="10" t="s">
         <v>358</v>
-      </c>
-      <c r="J86" s="10" t="s">
-        <v>359</v>
       </c>
       <c r="K86" s="10"/>
       <c r="L86" s="12"/>
       <c r="M86" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5800,13 +5795,13 @@
         <v>79</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D87" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="E87" s="10" t="s">
         <v>360</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>361</v>
       </c>
       <c r="F87" s="11" t="s">
         <v>29</v>
@@ -5818,15 +5813,15 @@
         <v>31</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K87" s="10"/>
       <c r="L87" s="12"/>
       <c r="M87" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5834,13 +5829,13 @@
         <v>80</v>
       </c>
       <c r="C88" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="D88" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="D88" s="10" t="s">
+      <c r="E88" s="10" t="s">
         <v>364</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>365</v>
       </c>
       <c r="F88" s="11" t="s">
         <v>29</v>
@@ -5855,12 +5850,12 @@
         <v>255</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K88" s="10"/>
       <c r="L88" s="12"/>
       <c r="M88" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5868,13 +5863,13 @@
         <v>81</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D89" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="E89" s="10" t="s">
         <v>367</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>368</v>
       </c>
       <c r="F89" s="11" t="s">
         <v>29</v>
@@ -5886,17 +5881,17 @@
         <v>206</v>
       </c>
       <c r="I89" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="J89" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J89" s="10" t="s">
+      <c r="K89" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="K89" s="10" t="s">
-        <v>371</v>
       </c>
       <c r="L89" s="12"/>
       <c r="M89" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5904,10 +5899,10 @@
         <v>82</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>59</v>
@@ -5930,7 +5925,7 @@
       <c r="K90" s="10"/>
       <c r="L90" s="12"/>
       <c r="M90" s="13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5938,10 +5933,10 @@
         <v>83</v>
       </c>
       <c r="C91" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="D91" s="10" t="s">
         <v>374</v>
-      </c>
-      <c r="D91" s="10" t="s">
-        <v>375</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>59</v>
@@ -5956,15 +5951,15 @@
         <v>206</v>
       </c>
       <c r="I91" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="J91" s="10" t="s">
         <v>376</v>
-      </c>
-      <c r="J91" s="10" t="s">
-        <v>377</v>
       </c>
       <c r="K91" s="10"/>
       <c r="L91" s="12"/>
       <c r="M91" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5972,16 +5967,16 @@
         <v>84</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D92" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="E92" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="E92" s="10" t="s">
-        <v>380</v>
-      </c>
       <c r="F92" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G92" s="10" t="s">
         <v>171</v>
@@ -5996,11 +5991,11 @@
         <v>31</v>
       </c>
       <c r="K92" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L92" s="12"/>
       <c r="M92" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6008,13 +6003,13 @@
         <v>85</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D93" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="E93" s="10" t="s">
         <v>382</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="F93" s="11" t="s">
         <v>29</v>
@@ -6026,15 +6021,15 @@
         <v>206</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K93" s="10"/>
       <c r="L93" s="12"/>
       <c r="M93" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6042,10 +6037,10 @@
         <v>86</v>
       </c>
       <c r="C94" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="D94" s="10" t="s">
         <v>385</v>
-      </c>
-      <c r="D94" s="10" t="s">
-        <v>386</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>59</v>
@@ -6060,15 +6055,15 @@
         <v>206</v>
       </c>
       <c r="I94" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="J94" s="10" t="s">
         <v>387</v>
-      </c>
-      <c r="J94" s="10" t="s">
-        <v>388</v>
       </c>
       <c r="K94" s="10"/>
       <c r="L94" s="12"/>
       <c r="M94" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6076,16 +6071,16 @@
         <v>87</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D95" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="E95" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="E95" s="10" t="s">
-        <v>391</v>
-      </c>
       <c r="F95" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G95" s="10" t="s">
         <v>205</v>
@@ -6094,17 +6089,17 @@
         <v>206</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J95" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="K95" s="10" t="s">
         <v>392</v>
-      </c>
-      <c r="K95" s="10" t="s">
-        <v>393</v>
       </c>
       <c r="L95" s="12"/>
       <c r="M95" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6112,10 +6107,10 @@
         <v>88</v>
       </c>
       <c r="C96" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="D96" s="10" t="s">
         <v>394</v>
-      </c>
-      <c r="D96" s="10" t="s">
-        <v>395</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>59</v>
@@ -6130,15 +6125,15 @@
         <v>31</v>
       </c>
       <c r="I96" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="J96" s="10" t="s">
         <v>396</v>
-      </c>
-      <c r="J96" s="10" t="s">
-        <v>397</v>
       </c>
       <c r="K96" s="10"/>
       <c r="L96" s="12"/>
       <c r="M96" s="13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6146,10 +6141,10 @@
         <v>89</v>
       </c>
       <c r="C97" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D97" s="10" t="s">
         <v>399</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>400</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>59</v>
@@ -6164,15 +6159,15 @@
         <v>31</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K97" s="10"/>
       <c r="L97" s="12"/>
       <c r="M97" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6180,13 +6175,13 @@
         <v>90</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D98" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="E98" s="10" t="s">
         <v>403</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>404</v>
       </c>
       <c r="F98" s="11" t="s">
         <v>29</v>
@@ -6198,15 +6193,15 @@
         <v>31</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K98" s="10"/>
       <c r="L98" s="12"/>
       <c r="M98" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6214,13 +6209,13 @@
         <v>91</v>
       </c>
       <c r="C99" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="D99" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="D99" s="10" t="s">
+      <c r="E99" s="10" t="s">
         <v>407</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>408</v>
       </c>
       <c r="F99" s="11" t="s">
         <v>29</v>
@@ -6232,15 +6227,15 @@
         <v>31</v>
       </c>
       <c r="I99" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="J99" s="10" t="s">
         <v>409</v>
-      </c>
-      <c r="J99" s="10" t="s">
-        <v>410</v>
       </c>
       <c r="K99" s="10"/>
       <c r="L99" s="12"/>
       <c r="M99" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6248,13 +6243,13 @@
         <v>92</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D100" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="E100" s="10" t="s">
         <v>412</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>413</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>29</v>
@@ -6266,15 +6261,15 @@
         <v>31</v>
       </c>
       <c r="I100" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="J100" s="10" t="s">
         <v>414</v>
-      </c>
-      <c r="J100" s="10" t="s">
-        <v>415</v>
       </c>
       <c r="K100" s="10"/>
       <c r="L100" s="12"/>
       <c r="M100" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6282,13 +6277,13 @@
         <v>93</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D101" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="E101" s="10" t="s">
         <v>416</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>417</v>
       </c>
       <c r="F101" s="11" t="s">
         <v>29</v>
@@ -6300,15 +6295,15 @@
         <v>31</v>
       </c>
       <c r="I101" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="J101" s="10" t="s">
         <v>418</v>
-      </c>
-      <c r="J101" s="10" t="s">
-        <v>419</v>
       </c>
       <c r="K101" s="10"/>
       <c r="L101" s="12"/>
       <c r="M101" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6316,13 +6311,13 @@
         <v>94</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D102" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="E102" s="10" t="s">
         <v>420</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>421</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>29</v>
@@ -6334,15 +6329,15 @@
         <v>31</v>
       </c>
       <c r="I102" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="J102" s="10" t="s">
         <v>422</v>
-      </c>
-      <c r="J102" s="10" t="s">
-        <v>423</v>
       </c>
       <c r="K102" s="10"/>
       <c r="L102" s="12"/>
       <c r="M102" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6350,10 +6345,10 @@
         <v>95</v>
       </c>
       <c r="C103" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="D103" s="10" t="s">
         <v>424</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>425</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>59</v>
@@ -6368,15 +6363,15 @@
         <v>31</v>
       </c>
       <c r="I103" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="J103" s="10" t="s">
         <v>426</v>
-      </c>
-      <c r="J103" s="10" t="s">
-        <v>427</v>
       </c>
       <c r="K103" s="10"/>
       <c r="L103" s="12"/>
       <c r="M103" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6384,10 +6379,10 @@
         <v>96</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>59</v>
@@ -6402,15 +6397,15 @@
         <v>31</v>
       </c>
       <c r="I104" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="J104" s="10" t="s">
         <v>430</v>
-      </c>
-      <c r="J104" s="10" t="s">
-        <v>431</v>
       </c>
       <c r="K104" s="10"/>
       <c r="L104" s="12"/>
       <c r="M104" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6418,16 +6413,16 @@
         <v>97</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>59</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>220</v>
+        <v>432</v>
       </c>
       <c r="G105" s="10" t="s">
         <v>51</v>
@@ -6454,7 +6449,7 @@
         <v>98</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>437</v>
@@ -6472,7 +6467,7 @@
         <v>31</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J106" s="10" t="s">
         <v>438</v>
@@ -6488,7 +6483,7 @@
         <v>99</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>440</v>
@@ -6703,7 +6698,7 @@
         <v>467</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>220</v>
+        <v>432</v>
       </c>
       <c r="G113" s="10" t="s">
         <v>51</v>
@@ -7129,7 +7124,7 @@
         <v>517</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K125" s="10"/>
       <c r="L125" s="12"/>
@@ -7253,7 +7248,7 @@
         <v>531</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>220</v>
+        <v>432</v>
       </c>
       <c r="G129" s="10" t="s">
         <v>205</v>
@@ -7508,7 +7503,7 @@
         <v>565</v>
       </c>
       <c r="K136" s="10" t="s">
-        <v>566</v>
+        <v>222</v>
       </c>
       <c r="L136" s="12"/>
       <c r="M136" s="13" t="s">
@@ -7523,10 +7518,10 @@
         <v>561</v>
       </c>
       <c r="D137" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="E137" s="10" t="s">
         <v>567</v>
-      </c>
-      <c r="E137" s="10" t="s">
-        <v>568</v>
       </c>
       <c r="F137" s="11" t="s">
         <v>29</v>
@@ -7538,10 +7533,10 @@
         <v>206</v>
       </c>
       <c r="I137" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="J137" s="10" t="s">
         <v>569</v>
-      </c>
-      <c r="J137" s="10" t="s">
-        <v>570</v>
       </c>
       <c r="K137" s="10"/>
       <c r="L137" s="12"/>
@@ -7554,35 +7549,35 @@
         <v>130</v>
       </c>
       <c r="C138" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D138" s="10" t="s">
         <v>571</v>
       </c>
-      <c r="D138" s="10" t="s">
+      <c r="E138" s="10" t="s">
         <v>572</v>
       </c>
-      <c r="E138" s="10" t="s">
+      <c r="F138" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G138" s="10" t="s">
         <v>573</v>
       </c>
-      <c r="F138" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G138" s="10" t="s">
+      <c r="H138" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I138" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="H138" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I138" s="10" t="s">
+      <c r="J138" s="10" t="s">
         <v>575</v>
       </c>
-      <c r="J138" s="10" t="s">
+      <c r="K138" s="10" t="s">
         <v>576</v>
-      </c>
-      <c r="K138" s="10" t="s">
-        <v>577</v>
       </c>
       <c r="L138" s="12"/>
       <c r="M138" s="13" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7590,13 +7585,13 @@
         <v>131</v>
       </c>
       <c r="C139" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="D139" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="D139" s="10" t="s">
+      <c r="E139" s="10" t="s">
         <v>580</v>
-      </c>
-      <c r="E139" s="10" t="s">
-        <v>581</v>
       </c>
       <c r="F139" s="11" t="s">
         <v>29</v>
@@ -7608,13 +7603,13 @@
         <v>31</v>
       </c>
       <c r="I139" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="J139" s="10" t="s">
         <v>582</v>
       </c>
-      <c r="J139" s="10" t="s">
+      <c r="K139" s="10" t="s">
         <v>583</v>
-      </c>
-      <c r="K139" s="10" t="s">
-        <v>584</v>
       </c>
       <c r="L139" s="12"/>
       <c r="M139" s="13" t="s">
@@ -7626,13 +7621,13 @@
         <v>132</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D140" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="E140" s="10" t="s">
         <v>585</v>
-      </c>
-      <c r="E140" s="10" t="s">
-        <v>586</v>
       </c>
       <c r="F140" s="11" t="s">
         <v>29</v>
@@ -7644,13 +7639,13 @@
         <v>31</v>
       </c>
       <c r="I140" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="J140" s="10" t="s">
         <v>587</v>
       </c>
-      <c r="J140" s="10" t="s">
+      <c r="K140" s="10" t="s">
         <v>588</v>
-      </c>
-      <c r="K140" s="10" t="s">
-        <v>589</v>
       </c>
       <c r="L140" s="12"/>
       <c r="M140" s="13" t="s">
@@ -7662,13 +7657,13 @@
         <v>133</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D141" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="E141" s="10" t="s">
         <v>590</v>
-      </c>
-      <c r="E141" s="10" t="s">
-        <v>591</v>
       </c>
       <c r="F141" s="11" t="s">
         <v>29</v>
@@ -7680,10 +7675,10 @@
         <v>31</v>
       </c>
       <c r="I141" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="J141" s="10" t="s">
         <v>592</v>
-      </c>
-      <c r="J141" s="10" t="s">
-        <v>593</v>
       </c>
       <c r="K141" s="10"/>
       <c r="L141" s="12"/>
@@ -7696,13 +7691,13 @@
         <v>134</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D142" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="E142" s="10" t="s">
         <v>594</v>
-      </c>
-      <c r="E142" s="10" t="s">
-        <v>595</v>
       </c>
       <c r="F142" s="11" t="s">
         <v>29</v>
@@ -7714,15 +7709,15 @@
         <v>31</v>
       </c>
       <c r="I142" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="J142" s="10" t="s">
         <v>596</v>
-      </c>
-      <c r="J142" s="10" t="s">
-        <v>597</v>
       </c>
       <c r="K142" s="10"/>
       <c r="L142" s="12"/>
       <c r="M142" s="13" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7730,33 +7725,33 @@
         <v>135</v>
       </c>
       <c r="C143" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="D143" s="10" t="s">
         <v>599</v>
       </c>
-      <c r="D143" s="10" t="s">
+      <c r="E143" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="E143" s="10" t="s">
+      <c r="F143" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G143" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="H143" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I143" s="10" t="s">
         <v>601</v>
       </c>
-      <c r="F143" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G143" s="10" t="s">
-        <v>574</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I143" s="10" t="s">
+      <c r="J143" s="10" t="s">
         <v>602</v>
-      </c>
-      <c r="J143" s="10" t="s">
-        <v>603</v>
       </c>
       <c r="K143" s="10"/>
       <c r="L143" s="12"/>
       <c r="M143" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7764,33 +7759,33 @@
         <v>136</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D144" s="10" t="s">
+        <v>604</v>
+      </c>
+      <c r="E144" s="10" t="s">
         <v>605</v>
       </c>
-      <c r="E144" s="10" t="s">
+      <c r="F144" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G144" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="H144" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I144" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="F144" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G144" s="10" t="s">
-        <v>574</v>
-      </c>
-      <c r="H144" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I144" s="10" t="s">
+      <c r="J144" s="10" t="s">
         <v>607</v>
-      </c>
-      <c r="J144" s="10" t="s">
-        <v>608</v>
       </c>
       <c r="K144" s="10"/>
       <c r="L144" s="12"/>
       <c r="M144" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7798,10 +7793,10 @@
         <v>137</v>
       </c>
       <c r="C145" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="D145" s="10" t="s">
         <v>610</v>
-      </c>
-      <c r="D145" s="10" t="s">
-        <v>611</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>59</v>
@@ -7810,21 +7805,21 @@
         <v>29</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I145" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="J145" s="10" t="s">
         <v>612</v>
-      </c>
-      <c r="J145" s="10" t="s">
-        <v>613</v>
       </c>
       <c r="K145" s="10"/>
       <c r="L145" s="12"/>
       <c r="M145" s="13" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7832,10 +7827,10 @@
         <v>138</v>
       </c>
       <c r="C146" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="D146" s="10" t="s">
         <v>615</v>
-      </c>
-      <c r="D146" s="10" t="s">
-        <v>616</v>
       </c>
       <c r="E146" s="10" t="s">
         <v>59</v>
@@ -7844,21 +7839,21 @@
         <v>29</v>
       </c>
       <c r="G146" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H146" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I146" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="J146" s="10" t="s">
         <v>617</v>
-      </c>
-      <c r="J146" s="10" t="s">
-        <v>618</v>
       </c>
       <c r="K146" s="10"/>
       <c r="L146" s="12"/>
       <c r="M146" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7866,33 +7861,33 @@
         <v>139</v>
       </c>
       <c r="C147" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="D147" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="D147" s="10" t="s">
+      <c r="E147" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="E147" s="10" t="s">
+      <c r="F147" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G147" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="H147" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I147" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="F147" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G147" s="10" t="s">
-        <v>574</v>
-      </c>
-      <c r="H147" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I147" s="10" t="s">
+      <c r="J147" s="10" t="s">
         <v>622</v>
-      </c>
-      <c r="J147" s="10" t="s">
-        <v>623</v>
       </c>
       <c r="K147" s="10"/>
       <c r="L147" s="12"/>
       <c r="M147" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7900,33 +7895,33 @@
         <v>140</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D148" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="E148" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="E148" s="10" t="s">
+      <c r="F148" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G148" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="H148" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I148" s="10" t="s">
         <v>625</v>
       </c>
-      <c r="F148" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G148" s="10" t="s">
-        <v>574</v>
-      </c>
-      <c r="H148" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I148" s="10" t="s">
+      <c r="J148" s="10" t="s">
         <v>626</v>
-      </c>
-      <c r="J148" s="10" t="s">
-        <v>627</v>
       </c>
       <c r="K148" s="10"/>
       <c r="L148" s="12"/>
       <c r="M148" s="13" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7934,33 +7929,33 @@
         <v>141</v>
       </c>
       <c r="C149" s="10" t="s">
+        <v>628</v>
+      </c>
+      <c r="D149" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="D149" s="10" t="s">
+      <c r="E149" s="10" t="s">
         <v>630</v>
       </c>
-      <c r="E149" s="10" t="s">
+      <c r="F149" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G149" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="H149" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I149" s="10" t="s">
         <v>631</v>
       </c>
-      <c r="F149" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G149" s="10" t="s">
-        <v>574</v>
-      </c>
-      <c r="H149" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I149" s="10" t="s">
+      <c r="J149" s="10" t="s">
         <v>632</v>
-      </c>
-      <c r="J149" s="10" t="s">
-        <v>633</v>
       </c>
       <c r="K149" s="10"/>
       <c r="L149" s="12"/>
       <c r="M149" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7968,10 +7963,10 @@
         <v>142</v>
       </c>
       <c r="C150" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="D150" s="10" t="s">
         <v>634</v>
-      </c>
-      <c r="D150" s="10" t="s">
-        <v>635</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>59</v>
@@ -7980,21 +7975,21 @@
         <v>29</v>
       </c>
       <c r="G150" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H150" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I150" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="J150" s="10" t="s">
         <v>636</v>
-      </c>
-      <c r="J150" s="10" t="s">
-        <v>637</v>
       </c>
       <c r="K150" s="10"/>
       <c r="L150" s="12"/>
       <c r="M150" s="13" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8002,35 +7997,35 @@
         <v>143</v>
       </c>
       <c r="C151" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="D151" s="10" t="s">
         <v>639</v>
       </c>
-      <c r="D151" s="10" t="s">
+      <c r="E151" s="10" t="s">
         <v>640</v>
       </c>
-      <c r="E151" s="10" t="s">
+      <c r="F151" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G151" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="H151" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I151" s="10" t="s">
         <v>641</v>
       </c>
-      <c r="F151" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G151" s="10" t="s">
-        <v>574</v>
-      </c>
-      <c r="H151" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I151" s="10" t="s">
+      <c r="J151" s="10" t="s">
         <v>642</v>
       </c>
-      <c r="J151" s="10" t="s">
+      <c r="K151" s="10" t="s">
         <v>643</v>
-      </c>
-      <c r="K151" s="10" t="s">
-        <v>644</v>
       </c>
       <c r="L151" s="12"/>
       <c r="M151" s="13" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8038,10 +8033,10 @@
         <v>144</v>
       </c>
       <c r="C152" s="10" t="s">
+        <v>645</v>
+      </c>
+      <c r="D152" s="10" t="s">
         <v>646</v>
-      </c>
-      <c r="D152" s="10" t="s">
-        <v>647</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>59</v>
@@ -8050,23 +8045,23 @@
         <v>29</v>
       </c>
       <c r="G152" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H152" s="10" t="s">
         <v>31</v>
       </c>
       <c r="I152" s="10" t="s">
+        <v>647</v>
+      </c>
+      <c r="J152" s="10" t="s">
         <v>648</v>
       </c>
-      <c r="J152" s="10" t="s">
+      <c r="K152" s="10" t="s">
         <v>649</v>
-      </c>
-      <c r="K152" s="10" t="s">
-        <v>650</v>
       </c>
       <c r="L152" s="12"/>
       <c r="M152" s="13" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8074,10 +8069,10 @@
         <v>145</v>
       </c>
       <c r="C153" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="D153" s="10" t="s">
         <v>652</v>
-      </c>
-      <c r="D153" s="10" t="s">
-        <v>653</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>59</v>
@@ -8086,7 +8081,7 @@
         <v>29</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H153" s="10" t="s">
         <v>31</v>
@@ -8095,12 +8090,12 @@
         <v>215</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K153" s="10"/>
       <c r="L153" s="12"/>
       <c r="M153" s="13" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8108,13 +8103,13 @@
         <v>146</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D154" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="E154" s="10" t="s">
         <v>656</v>
-      </c>
-      <c r="E154" s="10" t="s">
-        <v>657</v>
       </c>
       <c r="F154" s="11" t="s">
         <v>29</v>
@@ -8129,12 +8124,12 @@
         <v>215</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K154" s="10"/>
       <c r="L154" s="12"/>
       <c r="M154" s="13" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8142,33 +8137,33 @@
         <v>147</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D155" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="E155" s="10" t="s">
         <v>659</v>
       </c>
-      <c r="E155" s="10" t="s">
+      <c r="F155" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G155" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="H155" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I155" s="10" t="s">
         <v>660</v>
       </c>
-      <c r="F155" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G155" s="10" t="s">
-        <v>574</v>
-      </c>
-      <c r="H155" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I155" s="10" t="s">
+      <c r="J155" s="10" t="s">
         <v>661</v>
-      </c>
-      <c r="J155" s="10" t="s">
-        <v>662</v>
       </c>
       <c r="K155" s="10"/>
       <c r="L155" s="12"/>
       <c r="M155" s="13" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8176,10 +8171,10 @@
         <v>148</v>
       </c>
       <c r="C156" s="10" t="s">
+        <v>663</v>
+      </c>
+      <c r="D156" s="10" t="s">
         <v>664</v>
-      </c>
-      <c r="D156" s="10" t="s">
-        <v>665</v>
       </c>
       <c r="E156" s="10" t="s">
         <v>59</v>
@@ -8194,17 +8189,17 @@
         <v>206</v>
       </c>
       <c r="I156" s="10" t="s">
+        <v>665</v>
+      </c>
+      <c r="J156" s="10" t="s">
         <v>666</v>
       </c>
-      <c r="J156" s="10" t="s">
+      <c r="K156" s="10" t="s">
         <v>667</v>
-      </c>
-      <c r="K156" s="10" t="s">
-        <v>668</v>
       </c>
       <c r="L156" s="12"/>
       <c r="M156" s="13" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8212,13 +8207,13 @@
         <v>149</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D157" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="E157" s="10" t="s">
         <v>670</v>
-      </c>
-      <c r="E157" s="10" t="s">
-        <v>671</v>
       </c>
       <c r="F157" s="11" t="s">
         <v>29</v>
@@ -8230,13 +8225,13 @@
         <v>31</v>
       </c>
       <c r="I157" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="J157" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="J157" s="10" t="s">
+      <c r="K157" s="10" t="s">
         <v>673</v>
-      </c>
-      <c r="K157" s="10" t="s">
-        <v>674</v>
       </c>
       <c r="L157" s="12"/>
       <c r="M157" s="13" t="s">
@@ -8248,13 +8243,13 @@
         <v>150</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D158" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="E158" s="10" t="s">
         <v>675</v>
-      </c>
-      <c r="E158" s="10" t="s">
-        <v>676</v>
       </c>
       <c r="F158" s="11" t="s">
         <v>29</v>
@@ -8266,10 +8261,10 @@
         <v>31</v>
       </c>
       <c r="I158" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="J158" s="10" t="s">
         <v>677</v>
-      </c>
-      <c r="J158" s="10" t="s">
-        <v>678</v>
       </c>
       <c r="K158" s="10"/>
       <c r="L158" s="12"/>
@@ -8327,7 +8322,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8335,22 +8330,22 @@
         <v>15</v>
       </c>
       <c r="C4" s="16" t="s">
+        <v>679</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="G4" s="16" t="s">
         <v>680</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="G4" s="16" t="s">
+      <c r="H4" s="16" t="s">
         <v>681</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8566,11 +8561,11 @@
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B12,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B12,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B12,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -8582,7 +8577,7 @@
       </c>
       <c r="H12" s="19" t="n">
         <f aca="false">IF(C12&gt;0,D12/C12,0)</f>
-        <v>0.857142857142857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8595,11 +8590,11 @@
       </c>
       <c r="D13" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B13,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B13,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B13,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -8611,12 +8606,12 @@
       </c>
       <c r="H13" s="19" t="n">
         <f aca="false">IF(C13&gt;0,D13/C13,0)</f>
-        <v>0.857142857142857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C14" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B14)</f>
@@ -8645,7 +8640,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C15" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B15)</f>
@@ -8674,7 +8669,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C16" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B16)</f>
@@ -8703,7 +8698,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B17)</f>
@@ -8732,7 +8727,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B18)</f>
@@ -8761,7 +8756,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C19" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B19)</f>
@@ -8790,7 +8785,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C20" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B20)</f>
@@ -8819,7 +8814,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B21)</f>
@@ -8848,7 +8843,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B22)</f>
@@ -8877,7 +8872,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B23)</f>
@@ -8906,7 +8901,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C24" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B24)</f>
@@ -8935,7 +8930,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="17" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C25" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B25)</f>
@@ -8964,7 +8959,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="17" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C26" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B26)</f>
@@ -8993,7 +8988,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C27" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B27)</f>
@@ -9022,7 +9017,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="17" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C28" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B28)</f>
@@ -9312,7 +9307,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="17" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C38" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B38)</f>
@@ -9341,7 +9336,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="17" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C39" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B39)</f>
@@ -9370,7 +9365,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C40" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B40)</f>
@@ -9399,7 +9394,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C41" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B41)</f>
@@ -9428,7 +9423,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="17" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C42" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B42)</f>
@@ -9457,7 +9452,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="17" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C43" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B43)</f>
@@ -9486,7 +9481,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="17" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C44" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B44)</f>
@@ -9515,7 +9510,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="17" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C45" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B45)</f>
@@ -9544,7 +9539,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="17" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C46" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B46)</f>
@@ -9573,7 +9568,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="17" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C47" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B47)</f>
@@ -9602,7 +9597,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="17" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C48" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B48)</f>
@@ -9631,7 +9626,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="17" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C49" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B49)</f>
@@ -9660,7 +9655,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="20" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C50" s="21" t="n">
         <f aca="false">SUM(C5:C49)</f>
@@ -9668,11 +9663,11 @@
       </c>
       <c r="D50" s="21" t="n">
         <f aca="false">SUM(D5:D49)</f>
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">SUM(E5:E49)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F50" s="21" t="n">
         <f aca="false">SUM(F5:F49)</f>
@@ -9684,7 +9679,7 @@
       </c>
       <c r="H50" s="22" t="n">
         <f aca="false">IF(C50&gt;0,D50/C50,0)</f>
-        <v>0.946666666666667</v>
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
@@ -9715,18 +9710,18 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="23" t="s">
+        <v>683</v>
+      </c>
+      <c r="C4" s="23" t="s">
         <v>684</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="D4" s="23" t="s">
         <v>685</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>686</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>18</v>
@@ -9734,41 +9729,41 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="24" t="s">
+        <v>686</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>687</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="D5" s="24" t="s">
         <v>688</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>689</v>
-      </c>
       <c r="E5" s="25" t="s">
-        <v>220</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="24" t="s">
+        <v>689</v>
+      </c>
+      <c r="C6" s="24" t="s">
         <v>690</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="D6" s="24" t="s">
         <v>691</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>692</v>
-      </c>
       <c r="E6" s="25" t="s">
-        <v>220</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="24" t="s">
+        <v>692</v>
+      </c>
+      <c r="C7" s="24" t="s">
         <v>693</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="D7" s="24" t="s">
         <v>694</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>695</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>29</v>
@@ -9776,41 +9771,41 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="24" t="s">
+        <v>695</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>696</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="D8" s="24" t="s">
         <v>697</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>698</v>
-      </c>
       <c r="E8" s="25" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="24" t="s">
+        <v>698</v>
+      </c>
+      <c r="C9" s="24" t="s">
         <v>699</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="D9" s="24" t="s">
         <v>700</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>701</v>
-      </c>
       <c r="E9" s="25" t="s">
-        <v>220</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="24" t="s">
+        <v>701</v>
+      </c>
+      <c r="C10" s="24" t="s">
         <v>702</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="D10" s="24" t="s">
         <v>703</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>704</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>29</v>
@@ -9818,44 +9813,44 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="24" t="s">
+        <v>704</v>
+      </c>
+      <c r="C11" s="24" t="s">
         <v>705</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="D11" s="24" t="s">
         <v>706</v>
       </c>
-      <c r="D11" s="24" t="s">
-        <v>707</v>
-      </c>
       <c r="E11" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
+        <v>707</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>708</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="D12" s="24" t="s">
         <v>709</v>
       </c>
-      <c r="D12" s="24" t="s">
-        <v>710</v>
-      </c>
       <c r="E12" s="25" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="24" t="s">
+        <v>710</v>
+      </c>
+      <c r="C13" s="24" t="s">
         <v>711</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="D13" s="24" t="s">
         <v>712</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>713</v>
-      </c>
       <c r="E13" s="25" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -9904,15 +9899,15 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="26" t="s">
+        <v>714</v>
+      </c>
+      <c r="C4" s="27" t="s">
         <v>715</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9920,31 +9915,31 @@
         <v>29</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="26" t="s">
-        <v>220</v>
+        <v>432</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="26" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="26" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9952,7 +9947,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9960,15 +9955,15 @@
         <v>22</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="26" t="s">
+        <v>722</v>
+      </c>
+      <c r="C11" s="27" t="s">
         <v>723</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9976,15 +9971,15 @@
         <v>20</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="26" t="s">
+        <v>725</v>
+      </c>
+      <c r="C13" s="27" t="s">
         <v>726</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>727</v>
       </c>
     </row>
   </sheetData>

--- a/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
+++ b/docs/client-requirements/Nibbl_Master_Requirements_Tracker.xlsx
@@ -1325,114 +1325,114 @@
     <t xml:space="preserve">Automatic refill (Stripe): trigger 25%, fixed amount, recommendation, failure alert</t>
   </si>
   <si>
+    <t xml:space="preserve">Wallet → Auto-refill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable auto-refill.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tested on production 13 Oct 2026 in Stripe test mode: $10 top-up with card 4242 credited by webhook; auto-refill enabled in the UI; the auto-refill charge to the saved card credited the wallet; the job skips brands with no recent spend. Live keys are swapped in at go-live (client decision: keep sandbox for testing).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending Overview + Weekly Statements + detailed ledger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Download a statement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request Refund (Available Cash refundable; reserved/promo not)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Owner requests up to Available Cash; Nibbl reviews in Admin → Refunds, refunds in Stripe, marks refunded (ledger refund entry) or rejects with a note.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Dashboard + Admin Dashboard + Backend / API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallet → Request Refund; Admin → Refunds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request, then mark refunded in Admin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money is returned manually in Stripe, then recorded here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current plan, recommendation, plan options, scheduled changes, downgrade campaign choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedule and cancel a change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#33, #35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feature comparison table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side-by-side table (capacity, fees, review cost, identity, CSV, integrations, account manager, early access).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plans → Feature Comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Plans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan entitlement enforcement (campaign limits, customer identity, CSV, review cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limits, fees, CSV and identity enforced; Starter reviews show first name + last initial and email only on 1–3★.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered by tests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#33, #34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand Profile (name, website, support email, time zone)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings → Brand Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change time zone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team &amp; Permissions (Owner / Admin / Viewer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Settings → Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invite a Viewer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notifications per member (Email + SMS): wallet below 25%, auto-refill failed, campaign paused, exhausted early, new negative review, weekly summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master's six notifications (+ campaign approvals, receipts to review) all sent in-app + email per member preference.</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Progress</t>
   </si>
   <si>
-    <t xml:space="preserve">Wallet → Auto-refill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enable auto-refill.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production still on Stripe test keys — switch to the live keys received from the client, then retest.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending Overview + Weekly Statements + detailed ledger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Download a statement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request Refund (Available Cash refundable; reserved/promo not)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Owner requests up to Available Cash; Nibbl reviews in Admin → Refunds, refunds in Stripe, marks refunded (ledger refund entry) or rejects with a note.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Dashboard + Admin Dashboard + Backend / API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallet → Request Refund; Admin → Refunds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request, then mark refunded in Admin.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Money is returned manually in Stripe, then recorded here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current plan, recommendation, plan options, scheduled changes, downgrade campaign choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schedule and cancel a change.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#33, #35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feature comparison table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Side-by-side table (capacity, fees, review cost, identity, CSV, integrations, account manager, early access).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plans → Feature Comparison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Plans.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan entitlement enforcement (campaign limits, customer identity, CSV, review cost)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limits, fees, CSV and identity enforced; Starter reviews show first name + last initial and email only on 1–3★.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered by tests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#33, #34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand Profile (name, website, support email, time zone)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings → Brand Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change time zone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team &amp; Permissions (Owner / Admin / Viewer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settings → Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invite a Viewer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications per member (Email + SMS): wallet below 25%, auto-refill failed, campaign paused, exhausted early, new negative review, weekly summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master's six notifications (+ campaign approvals, receipts to review) all sent in-app + email per member preference.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Settings → Notifications</t>
   </si>
   <si>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">Withdraw a small amount.</t>
   </si>
   <si>
-    <t xml:space="preserve">SMS verification works on production (12 Oct). Do one real website withdrawal with the SMS step, then Completed.</t>
+    <t xml:space="preserve">Tested on production 13 Oct 2026: $1 website withdrawal — amount → locked PayPal → SMS code to a real phone → confirm → Requested (Ready for Batch).</t>
   </si>
   <si>
     <t xml:space="preserve">'Additional review needed' popup; status stays Processing</t>
@@ -2090,10 +2090,10 @@
     <t xml:space="preserve">Our team — Stripe</t>
   </si>
   <si>
-    <t xml:space="preserve">Switch production to the live Stripe keys the client sent; retest checkout, top-up and auto-refill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client moved Stripe to live production (live keys + webhook secret received)</t>
+    <t xml:space="preserve">Keep Stripe in test mode for testing; swap to the client's live keys at go-live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top-up and auto-refill tested on production in test mode 13 Oct 2026. Client sandbox keys have no sandbox webhook secret; live keys + live webhook secret received</t>
   </si>
   <si>
     <t xml:space="preserve">Our team — Twilio</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">Retest SMS-verified withdrawals; lock verified phones (change via admin + history)</t>
   </si>
   <si>
-    <t xml:space="preserve">Twilio SMS verified on production 12 Oct 2026 (code sent to a Bangladesh number, delivered, approved). Remaining: one real website withdrawal with the SMS step</t>
+    <t xml:space="preserve">Twilio SMS verified on production 12 Oct 2026; real website withdrawal with the SMS step completed 13 Oct 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Client — DNS</t>
@@ -3050,11 +3050,11 @@
       </c>
       <c r="D5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"Completed")</f>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Progress")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">COUNTIF(F9:F158,"In Review")</f>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H5" s="5" t="n">
         <f aca="false">IF(C5&gt;0,D5/C5,0)</f>
-        <v>0.96</v>
+        <v>0.973333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6408,7 +6408,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B105" s="9" t="n">
         <v>97</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>59</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>432</v>
+        <v>29</v>
       </c>
       <c r="G105" s="10" t="s">
         <v>51</v>
@@ -6431,17 +6431,17 @@
         <v>31</v>
       </c>
       <c r="I105" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="J105" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="J105" s="10" t="s">
+      <c r="K105" s="10" t="s">
         <v>434</v>
-      </c>
-      <c r="K105" s="10" t="s">
-        <v>435</v>
       </c>
       <c r="L105" s="12"/>
       <c r="M105" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6452,7 +6452,7 @@
         <v>423</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>59</v>
@@ -6470,12 +6470,12 @@
         <v>425</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K106" s="10"/>
       <c r="L106" s="12"/>
       <c r="M106" s="13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6486,28 +6486,28 @@
         <v>423</v>
       </c>
       <c r="D107" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="E107" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="E107" s="10" t="s">
+      <c r="F107" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G107" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="F107" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G107" s="10" t="s">
+      <c r="H107" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I107" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="H107" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I107" s="10" t="s">
+      <c r="J107" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="J107" s="10" t="s">
+      <c r="K107" s="10" t="s">
         <v>444</v>
-      </c>
-      <c r="K107" s="10" t="s">
-        <v>445</v>
       </c>
       <c r="L107" s="12"/>
       <c r="M107" s="13" t="s">
@@ -6519,10 +6519,10 @@
         <v>100</v>
       </c>
       <c r="C108" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="D108" s="10" t="s">
         <v>446</v>
-      </c>
-      <c r="D108" s="10" t="s">
-        <v>447</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>59</v>
@@ -6537,15 +6537,15 @@
         <v>31</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="K108" s="10"/>
       <c r="L108" s="12"/>
       <c r="M108" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6553,13 +6553,13 @@
         <v>101</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D109" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="E109" s="10" t="s">
         <v>450</v>
-      </c>
-      <c r="E109" s="10" t="s">
-        <v>451</v>
       </c>
       <c r="F109" s="11" t="s">
         <v>29</v>
@@ -6571,10 +6571,10 @@
         <v>31</v>
       </c>
       <c r="I109" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="J109" s="10" t="s">
         <v>452</v>
-      </c>
-      <c r="J109" s="10" t="s">
-        <v>453</v>
       </c>
       <c r="K109" s="10"/>
       <c r="L109" s="12"/>
@@ -6587,13 +6587,13 @@
         <v>102</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D110" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="E110" s="10" t="s">
         <v>454</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>455</v>
       </c>
       <c r="F110" s="11" t="s">
         <v>29</v>
@@ -6608,12 +6608,12 @@
         <v>172</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K110" s="10"/>
       <c r="L110" s="12"/>
       <c r="M110" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6621,10 +6621,10 @@
         <v>103</v>
       </c>
       <c r="C111" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="D111" s="10" t="s">
         <v>458</v>
-      </c>
-      <c r="D111" s="10" t="s">
-        <v>459</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>59</v>
@@ -6639,15 +6639,15 @@
         <v>31</v>
       </c>
       <c r="I111" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="J111" s="10" t="s">
         <v>460</v>
-      </c>
-      <c r="J111" s="10" t="s">
-        <v>461</v>
       </c>
       <c r="K111" s="10"/>
       <c r="L111" s="12"/>
       <c r="M111" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6655,10 +6655,10 @@
         <v>104</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>59</v>
@@ -6673,15 +6673,15 @@
         <v>31</v>
       </c>
       <c r="I112" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="J112" s="10" t="s">
         <v>464</v>
-      </c>
-      <c r="J112" s="10" t="s">
-        <v>465</v>
       </c>
       <c r="K112" s="10"/>
       <c r="L112" s="12"/>
       <c r="M112" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6689,16 +6689,16 @@
         <v>105</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D113" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="E113" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="E113" s="10" t="s">
+      <c r="F113" s="11" t="s">
         <v>467</v>
-      </c>
-      <c r="F113" s="11" t="s">
-        <v>432</v>
       </c>
       <c r="G113" s="10" t="s">
         <v>51</v>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="L113" s="12"/>
       <c r="M113" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6725,7 +6725,7 @@
         <v>106</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D114" s="10" t="s">
         <v>471</v>
@@ -6759,7 +6759,7 @@
         <v>107</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>474</v>
@@ -6785,7 +6785,7 @@
       <c r="K115" s="10"/>
       <c r="L115" s="12"/>
       <c r="M115" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6793,7 +6793,7 @@
         <v>108</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>478</v>
@@ -6819,7 +6819,7 @@
       <c r="K116" s="10"/>
       <c r="L116" s="12"/>
       <c r="M116" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7248,7 +7248,7 @@
         <v>531</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>432</v>
+        <v>29</v>
       </c>
       <c r="G129" s="10" t="s">
         <v>205</v>
@@ -7398,7 +7398,7 @@
         <v>553</v>
       </c>
       <c r="J133" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K133" s="10"/>
       <c r="L133" s="12"/>
@@ -8336,7 +8336,7 @@
         <v>29</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>432</v>
+        <v>467</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>297</v>
@@ -9025,11 +9025,11 @@
       </c>
       <c r="D28" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B28,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B28,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B28,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9041,12 +9041,12 @@
       </c>
       <c r="H28" s="19" t="n">
         <f aca="false">IF(C28&gt;0,D28/C28,0)</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="17" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C29" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B29)</f>
@@ -9075,7 +9075,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C30" s="18" t="n">
         <f aca="false">COUNTIF('Master Requirements Tracker'!$C$9:$C$158,B30)</f>
@@ -9199,11 +9199,11 @@
       </c>
       <c r="D34" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B34,'Master Requirements Tracker'!$F$9:$F$158,"Completed")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B34,'Master Requirements Tracker'!$F$9:$F$158,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="18" t="n">
         <f aca="false">COUNTIFS('Master Requirements Tracker'!$C$9:$C$158,B34,'Master Requirements Tracker'!$F$9:$F$158,"In Review")</f>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="H34" s="19" t="n">
         <f aca="false">IF(C34&gt;0,D34/C34,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9663,11 +9663,11 @@
       </c>
       <c r="D50" s="21" t="n">
         <f aca="false">SUM(D5:D49)</f>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">SUM(E5:E49)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" s="21" t="n">
         <f aca="false">SUM(F5:F49)</f>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="H50" s="22" t="n">
         <f aca="false">IF(C50&gt;0,D50/C50,0)</f>
-        <v>0.96</v>
+        <v>0.973333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -9738,7 +9738,7 @@
         <v>688</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>432</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9752,7 +9752,7 @@
         <v>691</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>432</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9794,7 +9794,7 @@
         <v>700</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>432</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9920,7 +9920,7 @@
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="26" t="s">
-        <v>432</v>
+        <v>467</v>
       </c>
       <c r="C6" s="27" t="s">
         <v>717</v>
